--- a/dados_produtos_corrigidos.xlsx
+++ b/dados_produtos_corrigidos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E524"/>
+  <dimension ref="A1:E530"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11578,9 +11578,7 @@
           <t>TIRINHAS DE TILÁPIA COSTA SUL 300G EMPANADO</t>
         </is>
       </c>
-      <c r="E522" t="n">
-        <v>10.99</v>
-      </c>
+      <c r="E522" t="inlineStr"/>
     </row>
     <row r="523">
       <c r="A523" t="n">
@@ -11601,9 +11599,7 @@
           <t>BISTECA DO CONTRA FILE KG</t>
         </is>
       </c>
-      <c r="E523" t="n">
-        <v>31.99</v>
-      </c>
+      <c r="E523" t="inlineStr"/>
     </row>
     <row r="524">
       <c r="A524" t="n">
@@ -11624,8 +11620,140 @@
           <t>FILE MIGNON KG</t>
         </is>
       </c>
-      <c r="E524" t="n">
-        <v>40.99</v>
+      <c r="E524" t="inlineStr"/>
+    </row>
+    <row r="525">
+      <c r="A525" t="n">
+        <v>174010</v>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - DESTILADOS</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>CACHACA SELETA 600ML</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>CACHAÇA SELETA 600ML</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr"/>
+    </row>
+    <row r="526">
+      <c r="A526" t="n">
+        <v>177250</v>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - CERVEJA</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>CERV DEVASSA PURO MALTE 269ML C/ 12UND</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>CERVEJA DEVASSA 12 X 269ML PURO MALTE</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr"/>
+    </row>
+    <row r="527">
+      <c r="A527" t="n">
+        <v>303283</v>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - CERVEJA</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>CERVEJA HEINEKEN 350ML SLEEK LT C/12 UNI</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>CERVEJA HEINEKEN 12 X 350ML SLEEK</t>
+        </is>
+      </c>
+      <c r="E527" t="n">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="n">
+        <v>286362</v>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - CERVEJA</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>CERVEJA SPATEN 600ML PURO MALTE LN</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>CERVEJA SPATEN 600ML PURO MALTE LONG NECK</t>
+        </is>
+      </c>
+      <c r="E528" t="n">
+        <v>9.49</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="n">
+        <v>108686</v>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>REFRIG SODA LIMONADA ANTARCTICA PET 2 LT</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>REFRIGERANTE ANTARCTICA SODA LIMONADA 2L</t>
+        </is>
+      </c>
+      <c r="E529" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="n">
+        <v>248750</v>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - DESTILADOS</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>WHISKY NATU NOBILIS  APERITIVO 1L</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>WHISKY NATU NOBILIS 1L APERITIVO</t>
+        </is>
+      </c>
+      <c r="E530" t="n">
+        <v>55.99</v>
       </c>
     </row>
   </sheetData>

--- a/dados_produtos_corrigidos.xlsx
+++ b/dados_produtos_corrigidos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E530"/>
+  <dimension ref="A1:E532"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11756,6 +11756,52 @@
         <v>55.99</v>
       </c>
     </row>
+    <row r="531">
+      <c r="A531" t="n">
+        <v>105450</v>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>BOVINO - ALCATRA KG</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>ALCATRA BOVINA KG</t>
+        </is>
+      </c>
+      <c r="E531" t="n">
+        <v>37.99</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="n">
+        <v>105456</v>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>BOVINO - CARNE DE SOL KG SEGUNDA</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>CARNE DE SOL KG SEGUNDA</t>
+        </is>
+      </c>
+      <c r="E532" t="n">
+        <v>26.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dados_produtos_corrigidos.xlsx
+++ b/dados_produtos_corrigidos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E532"/>
+  <dimension ref="A1:E544"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11802,6 +11802,282 @@
         <v>26.99</v>
       </c>
     </row>
+    <row r="533">
+      <c r="A533" t="n">
+        <v>105460</v>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>BOVINA - BISTECA PALETA KG</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>BISTECA BOVINA KG  PALETA</t>
+        </is>
+      </c>
+      <c r="E533" t="n">
+        <v>19.99</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="n">
+        <v>158997</v>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>BOVINO - BISTECA DO ACEM KG</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>BISTECA BOVINA KG ACEM</t>
+        </is>
+      </c>
+      <c r="E534" t="n">
+        <v>14.99</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="n">
+        <v>115278</v>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>BOVINO - MIOLO DA PALETA KG</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>MIOLO DA PALETA KG BOVINA</t>
+        </is>
+      </c>
+      <c r="E535" t="n">
+        <v>26.99</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="n">
+        <v>298736</v>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>ACHOCOLATADO ITALAKINHO 200ML CHOCOLATE</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>ACHOCOLATADO ITALAKINHO 200ML CHOCOLATE</t>
+        </is>
+      </c>
+      <c r="E536" t="n">
+        <v>1.69</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="n">
+        <v>111378</v>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>AZEITONA VERDE LA VIOLETERA 160GR FATIAD</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>AZEITONAS LA VIOLETERA 160GR VERDES FATIADAS</t>
+        </is>
+      </c>
+      <c r="E537" t="n">
+        <v>12.99</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="n">
+        <v>298701</v>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - CERVEJA</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>CERVEJA AMSTEL 350ML LAGER SLEEK C/12 UN</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>CERVEJA AMSTEL 12 X 350ML LAGER SLEEK</t>
+        </is>
+      </c>
+      <c r="E538" t="n">
+        <v>4.09</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="n">
+        <v>184034</v>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - CERVEJA</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>CERVEJA HEINEKEN 250ML LN LAGER UNID</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>CERVEJA HEINEKEN 250ML LONG NECK LAGER</t>
+        </is>
+      </c>
+      <c r="E539" t="n">
+        <v>5.69</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="n">
+        <v>101063</v>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>CREME LEITE PIRACANJUBA 200GR UHT</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>CREME DE LEITE PIRACANJUBA 200G UHT</t>
+        </is>
+      </c>
+      <c r="E540" t="n">
+        <v>4.69</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="n">
+        <v>102282</v>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>ENERG RED BULL 250ML TRAD</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>ENERGETICO RED BULL 250ML TRADICIONAL</t>
+        </is>
+      </c>
+      <c r="E541" t="n">
+        <v>8.69</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="n">
+        <v>100024</v>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>FARINHA TRIGO DONA BENTA 1KG SEM FERMENT</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>FARINHA DE TRIGO DONA BENTA 1KG SEM FERMENTO</t>
+        </is>
+      </c>
+      <c r="E542" t="n">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="n">
+        <v>279573</v>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>FEIJAO DONA MARIA 1KG CARIOCA</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>FEIJÃO DONA MARIA 1KG CARIOCA</t>
+        </is>
+      </c>
+      <c r="E543" t="n">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="n">
+        <v>102237</v>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - #00 SUCO</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>SUCO UVA INTEGRAL TINTO AURORA 1,5L VD</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>SUCO DE UVA AURORA VIDRO 1,5L  INTEGRAL TINTO</t>
+        </is>
+      </c>
+      <c r="E544" t="n">
+        <v>27.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dados_produtos_corrigidos.xlsx
+++ b/dados_produtos_corrigidos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E587"/>
+  <dimension ref="A1:E593"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -788,7 +788,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>279573</v>
+        <v>200178</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>FEIJAO DONA MARIA 1KG CARIOCA</t>
+          <t>FEIJAO CARIOCA DONA DE 1KG</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FEIJÃO DONA MARIA 1KG CARIOCA</t>
+          <t>FEIJÃO DONA DE 1KG CARIOCA</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5.99</v>
+        <v>6.19</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>100014</v>
+        <v>279573</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -820,12 +820,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>FEIJAO GOL CORES 1KG</t>
+          <t>FEIJAO DONA MARIA 1KG CARIOCA</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">FEIJÃO GOL 1KG CORES </t>
+          <t>FEIJÃO DONA MARIA 1KG CARIOCA</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -834,7 +834,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>200178</v>
+        <v>100014</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -843,16 +843,16 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>FEIJAO CARIOCA DONA DE 1KG</t>
+          <t>FEIJAO GOL CORES 1KG</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FEIJÃO DONA DE 1KG CARIOCA</t>
+          <t xml:space="preserve">FEIJÃO GOL 1KG CORES </t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6.19</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="20">
@@ -6863,7 +6863,7 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>211157</v>
+        <v>168527</v>
       </c>
       <c r="B300" t="inlineStr">
         <is>
@@ -6872,19 +6872,19 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>CR PENT SALON L SUPER OLEOS 1L</t>
+          <t>CR.PEN.S.LINE RE.V.REC.INT.1K</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>CREME DE PENTEAR SALON LINE 1L SUPER OLEOS</t>
+          <t xml:space="preserve">CREME DE PENTEAR SALON LINE 1K RECONSTRUÇÃO INTENSA </t>
         </is>
       </c>
       <c r="E300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>168527</v>
+        <v>262566</v>
       </c>
       <c r="B301" t="inlineStr">
         <is>
@@ -6893,19 +6893,19 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>CR.PEN.S.LINE RE.V.REC.INT.1K</t>
+          <t>CREME DE PENTEAR SALON LINE 1KG AZEITE D</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t xml:space="preserve">CREME DE PENTEAR SALON LINE 1K RECONSTRUÇÃO INTENSA </t>
+          <t xml:space="preserve">CREME DE PENTEAR SALON LINE 1KG AZEITE DE OLIVA </t>
         </is>
       </c>
       <c r="E301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>262566</v>
+        <v>167527</v>
       </c>
       <c r="B302" t="inlineStr">
         <is>
@@ -6914,19 +6914,19 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>CREME DE PENTEAR SALON LINE 1KG AZEITE D</t>
+          <t>CR.PEN.S.LINE RE.V.BR.MAX.1KG</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t xml:space="preserve">CREME DE PENTEAR SALON LINE 1KG AZEITE DE OLIVA </t>
+          <t xml:space="preserve">CREME DE PENTEAR SALON LINE 1KG BRILHO MAXIMO </t>
         </is>
       </c>
       <c r="E302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>167527</v>
+        <v>206737</v>
       </c>
       <c r="B303" t="inlineStr">
         <is>
@@ -6935,19 +6935,19 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>CR.PEN.S.LINE RE.V.BR.MAX.1KG</t>
+          <t>CR PENT SALON L BRILHO UMIDIF 1KG</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t xml:space="preserve">CREME DE PENTEAR SALON LINE 1KG BRILHO MAXIMO </t>
+          <t xml:space="preserve">CREME DE PENTEAR SALON LINE 1KG BRILHO UMIDIFICADOR </t>
         </is>
       </c>
       <c r="E303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>206737</v>
+        <v>303583</v>
       </c>
       <c r="B304" t="inlineStr">
         <is>
@@ -6956,19 +6956,19 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>CR PENT SALON L BRILHO UMIDIF 1KG</t>
+          <t>CREME DE PENTEAR SALON LINE 1KG CACHINHO</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t xml:space="preserve">CREME DE PENTEAR SALON LINE 1KG BRILHO UMIDIFICADOR </t>
+          <t xml:space="preserve">CREME DE PENTEAR SALON LINE 1KG CACHINHOS BRILHANTES </t>
         </is>
       </c>
       <c r="E304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>303583</v>
+        <v>313924</v>
       </c>
       <c r="B305" t="inlineStr">
         <is>
@@ -6977,19 +6977,19 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>CREME DE PENTEAR SALON LINE 1KG CACHINHO</t>
+          <t>CREME P/PENTEAR SALON LINE 1KG CACH KIDS</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t xml:space="preserve">CREME DE PENTEAR SALON LINE 1KG CACHINHOS BRILHANTES </t>
+          <t xml:space="preserve">CREME DE PENTEAR SALON LINE 1KG CACHOS KIDS </t>
         </is>
       </c>
       <c r="E305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>313924</v>
+        <v>269629</v>
       </c>
       <c r="B306" t="inlineStr">
         <is>
@@ -6998,19 +6998,19 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>CREME P/PENTEAR SALON LINE 1KG CACH KIDS</t>
+          <t>CREME PENTEAR SALON LINE 1KG DEFINICAO A</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t xml:space="preserve">CREME DE PENTEAR SALON LINE 1KG CACHOS KIDS </t>
+          <t xml:space="preserve">CREME DE PENTEAR SALON LINE 1KG DEFINICAO ANTIFRIZZ </t>
         </is>
       </c>
       <c r="E306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>269629</v>
+        <v>295312</v>
       </c>
       <c r="B307" t="inlineStr">
         <is>
@@ -7019,19 +7019,19 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>CREME PENTEAR SALON LINE 1KG DEFINICAO A</t>
+          <t>CREME PENTEAR SALON LINE 1KG DEF EXTRAOR</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t xml:space="preserve">CREME DE PENTEAR SALON LINE 1KG DEFINICAO ANTIFRIZZ </t>
+          <t xml:space="preserve">CREME DE PENTEAR SALON LINE 1KG DEFINIÇÃO EXTRAORDINARIA </t>
         </is>
       </c>
       <c r="E307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>295312</v>
+        <v>171341</v>
       </c>
       <c r="B308" t="inlineStr">
         <is>
@@ -7040,19 +7040,19 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>CREME PENTEAR SALON LINE 1KG DEF EXTRAOR</t>
+          <t>CR.PEN.S.LINE DEFI.INTENSA 1KG</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t xml:space="preserve">CREME DE PENTEAR SALON LINE 1KG DEFINIÇÃO EXTRAORDINARIA </t>
+          <t xml:space="preserve">CREME DE PENTEAR SALON LINE 1KG DEFINIÇÃO INTENSA </t>
         </is>
       </c>
       <c r="E308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>171341</v>
+        <v>219054</v>
       </c>
       <c r="B309" t="inlineStr">
         <is>
@@ -7061,19 +7061,19 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>CR.PEN.S.LINE DEFI.INTENSA 1KG</t>
+          <t>CR PENT SALON L DEFINICAO MAXIMA LIB 1KG</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t xml:space="preserve">CREME DE PENTEAR SALON LINE 1KG DEFINIÇÃO INTENSA </t>
+          <t xml:space="preserve">CREME DE PENTEAR SALON LINE 1KG DEFINICAO MAXIMA LIBERADO </t>
         </is>
       </c>
       <c r="E309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>219054</v>
+        <v>274185</v>
       </c>
       <c r="B310" t="inlineStr">
         <is>
@@ -7082,19 +7082,19 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>CR PENT SALON L DEFINICAO MAXIMA LIB 1KG</t>
+          <t>CREME DE PENTEAR SALONLINE 1KG DEFINICAO</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t xml:space="preserve">CREME DE PENTEAR SALON LINE 1KG DEFINICAO MAXIMA LIBERADO </t>
+          <t xml:space="preserve">CREME DE PENTEAR SALON LINE 1KG DEFINICAO NATURAL </t>
         </is>
       </c>
       <c r="E310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>274185</v>
+        <v>316174</v>
       </c>
       <c r="B311" t="inlineStr">
         <is>
@@ -7103,19 +7103,19 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>CREME DE PENTEAR SALONLINE 1KG DEFINICAO</t>
+          <t>CREME PENTEAR SALON LINE 1KG DEFINICAO N</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t xml:space="preserve">CREME DE PENTEAR SALON LINE 1KG DEFINICAO NATURAL </t>
+          <t xml:space="preserve">CREME DE PENTEAR SALON LINE 1KG DEFINICAO NUTRITIVA </t>
         </is>
       </c>
       <c r="E311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>316174</v>
+        <v>303582</v>
       </c>
       <c r="B312" t="inlineStr">
         <is>
@@ -7124,19 +7124,19 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>CREME PENTEAR SALON LINE 1KG DEFINICAO N</t>
+          <t>CREME DE PENTEAR SALON LINE 1KG LINHACA</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t xml:space="preserve">CREME DE PENTEAR SALON LINE 1KG DEFINICAO NUTRITIVA </t>
+          <t xml:space="preserve">CREME DE PENTEAR SALON LINE 1KG DEFINIÇÃO ULTRA VOLUME </t>
         </is>
       </c>
       <c r="E312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>303582</v>
+        <v>167528</v>
       </c>
       <c r="B313" t="inlineStr">
         <is>
@@ -7145,19 +7145,19 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>CREME DE PENTEAR SALON LINE 1KG LINHACA</t>
+          <t>CREME PENTEAR SALON LINE 1KG HIDRATACAO</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t xml:space="preserve">CREME DE PENTEAR SALON LINE 1KG DEFINIÇÃO ULTRA VOLUME </t>
+          <t xml:space="preserve">CREME DE PENTEAR SALON LINE 1KG HIDRATACAO PROFUNDA </t>
         </is>
       </c>
       <c r="E313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>167528</v>
+        <v>280872</v>
       </c>
       <c r="B314" t="inlineStr">
         <is>
@@ -7166,19 +7166,19 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>CREME PENTEAR SALON LINE 1KG HIDRATACAO</t>
+          <t>CREME PENTEAR SALON LINE 1KG KIDS CACHIN</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t xml:space="preserve">CREME DE PENTEAR SALON LINE 1KG HIDRATACAO PROFUNDA </t>
+          <t xml:space="preserve">CREME DE PENTEAR SALON LINE 1KG KIDS CACHINHOS </t>
         </is>
       </c>
       <c r="E314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>280872</v>
+        <v>316170</v>
       </c>
       <c r="B315" t="inlineStr">
         <is>
@@ -7187,19 +7187,19 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>CREME PENTEAR SALON LINE 1KG KIDS CACHIN</t>
+          <t>CREME PENTEAR SALON LINE 1KG KIDS CHOCOL</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t xml:space="preserve">CREME DE PENTEAR SALON LINE 1KG KIDS CACHINHOS </t>
+          <t xml:space="preserve">CREME DE PENTEAR SALON LINE 1KG KIDS CHOCOLATE </t>
         </is>
       </c>
       <c r="E315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>316170</v>
+        <v>171343</v>
       </c>
       <c r="B316" t="inlineStr">
         <is>
@@ -7208,19 +7208,19 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>CREME PENTEAR SALON LINE 1KG KIDS CHOCOL</t>
+          <t>CR.PEN.S.LINE NUTR.REPARAD.1KG</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t xml:space="preserve">CREME DE PENTEAR SALON LINE 1KG KIDS CHOCOLATE </t>
+          <t xml:space="preserve">CREME DE PENTEAR SALON LINE 1KG NUTRIÇÃO REPARADORA </t>
         </is>
       </c>
       <c r="E316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>171343</v>
+        <v>224567</v>
       </c>
       <c r="B317" t="inlineStr">
         <is>
@@ -7229,19 +7229,19 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>CR.PEN.S.LINE NUTR.REPARAD.1KG</t>
+          <t>CR PENTEAR INF SL SOS KIDS C DEFINIDOS 1</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t xml:space="preserve">CREME DE PENTEAR SALON LINE 1KG NUTRIÇÃO REPARADORA </t>
+          <t xml:space="preserve">CREME DE PENTEAR SALON LINE 1KG SOS KIDS CAIXOS DEFINIDOS </t>
         </is>
       </c>
       <c r="E317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>224567</v>
+        <v>294213</v>
       </c>
       <c r="B318" t="inlineStr">
         <is>
@@ -7250,19 +7250,19 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>CR PENTEAR INF SL SOS KIDS C DEFINIDOS 1</t>
+          <t>CREME PENTEAR SALONLINE 1KG TRAT PROLONG</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t xml:space="preserve">CREME DE PENTEAR SALON LINE 1KG SOS KIDS CAIXOS DEFINIDOS </t>
+          <t xml:space="preserve">CREME DE PENTEAR SALON LINE 1KG TRATAMENTO PROLONGADO </t>
         </is>
       </c>
       <c r="E318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>294213</v>
+        <v>211157</v>
       </c>
       <c r="B319" t="inlineStr">
         <is>
@@ -7271,12 +7271,12 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>CREME PENTEAR SALONLINE 1KG TRAT PROLONG</t>
+          <t>CR PENT SALON L SUPER OLEOS 1L</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t xml:space="preserve">CREME DE PENTEAR SALON LINE 1KG TRATAMENTO PROLONGADO </t>
+          <t>CREME DE PENTEAR SALON LINE 1L SUPER OLEOS</t>
         </is>
       </c>
       <c r="E319" t="inlineStr"/>
@@ -7304,7 +7304,7 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>163627</v>
+        <v>284786</v>
       </c>
       <c r="B321" t="inlineStr">
         <is>
@@ -7313,19 +7313,19 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>NIELY GOLD CCT 430G NUTRICAO PODEROSA</t>
+          <t>CREME DE TRATAMENTO NIELY GOLD 430G CACH</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t xml:space="preserve">CREME DE TRATAMENTO CAPILAR NIELY GOLD 430G NUTRICAO PODEROSA </t>
+          <t xml:space="preserve">CREME DE TRATAMENTO CAPILAR NIELY GOLD 430G CACHOS </t>
         </is>
       </c>
       <c r="E321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>284786</v>
+        <v>255028</v>
       </c>
       <c r="B322" t="inlineStr">
         <is>
@@ -7334,19 +7334,19 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>CREME DE TRATAMENTO NIELY GOLD 430G CACH</t>
+          <t>NIELY GOLD - CR TRAT 430G DETOX</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t xml:space="preserve">CREME DE TRATAMENTO CAPILAR NIELY GOLD 430G CACHOS </t>
+          <t xml:space="preserve">CREME DE TRATAMENTO CAPILAR NIELY GOLD 430G DETOX </t>
         </is>
       </c>
       <c r="E322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>255028</v>
+        <v>213094</v>
       </c>
       <c r="B323" t="inlineStr">
         <is>
@@ -7355,19 +7355,19 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>NIELY GOLD - CR TRAT 430G DETOX</t>
+          <t>CR TRAT NIELY GOLD 430G HIDR AGUA COCO</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t xml:space="preserve">CREME DE TRATAMENTO CAPILAR NIELY GOLD 430G DETOX </t>
+          <t xml:space="preserve">CREME DE TRATAMENTO CAPILAR NIELY GOLD 430G HIDR AGUA COCO </t>
         </is>
       </c>
       <c r="E323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>213094</v>
+        <v>165646</v>
       </c>
       <c r="B324" t="inlineStr">
         <is>
@@ -7376,19 +7376,19 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>CR TRAT NIELY GOLD 430G HIDR AGUA COCO</t>
+          <t>CREME HIDRATANTE NIELY 430GR GOLD LISO P</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t xml:space="preserve">CREME DE TRATAMENTO CAPILAR NIELY GOLD 430G HIDR AGUA COCO </t>
+          <t xml:space="preserve">CREME DE TRATAMENTO CAPILAR NIELY GOLD 430G LISO PROLONGADO </t>
         </is>
       </c>
       <c r="E324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>165646</v>
+        <v>163627</v>
       </c>
       <c r="B325" t="inlineStr">
         <is>
@@ -7397,12 +7397,12 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>CREME HIDRATANTE NIELY 430GR GOLD LISO P</t>
+          <t>NIELY GOLD CCT 430G NUTRICAO PODEROSA</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t xml:space="preserve">CREME DE TRATAMENTO CAPILAR NIELY GOLD 430G LISO PROLONGADO </t>
+          <t xml:space="preserve">CREME DE TRATAMENTO CAPILAR NIELY GOLD 430G NUTRICAO PODEROSA </t>
         </is>
       </c>
       <c r="E325" t="inlineStr"/>
@@ -8841,7 +8841,7 @@
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>196735</v>
+        <v>308560</v>
       </c>
       <c r="B394" t="inlineStr">
         <is>
@@ -8850,19 +8850,19 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>NIELY GOLD - CR TRAT 430G COMPRIDOS+FORT</t>
+          <t>KIT SHAMP+COND NIELY GOLD 275ML/175ML SA</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>KIT SHAMPOO + CONDICONADOR NIELY GOLD 430G COMPRIDOS + FORTES</t>
+          <t xml:space="preserve">KIT SHAMPOO + CONDICONADOR NIELY GOLD 275ML / 175ML SALVA FIOS </t>
         </is>
       </c>
       <c r="E394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>277148</v>
+        <v>214327</v>
       </c>
       <c r="B395" t="inlineStr">
         <is>
@@ -8871,19 +8871,19 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>KIT SHAMPOO + CONDICONADOR NIELY GOLD CACHOS 450ML DEF</t>
+          <t>KIT SHAMPOO + CONDICONADOR NIELY GOLD HIDRA AGUA COCO</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>KIT SHAMPOO + CONDICONADOR NIELY GOLD 450ML DEFESA PROLONGADA</t>
+          <t xml:space="preserve">KIT SHAMPOO + CONDICONADOR NIELY GOLD 300ML / 200ML HIDRATANTE AGUA COCO </t>
         </is>
       </c>
       <c r="E395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>308560</v>
+        <v>110941</v>
       </c>
       <c r="B396" t="inlineStr">
         <is>
@@ -8892,19 +8892,19 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>KIT SHAMP+COND NIELY GOLD 275ML/175ML SA</t>
+          <t>KIT SHAMPOO + CONDICONADOR NIELY GOLD QUERATINAQUERATIN</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t xml:space="preserve">KIT SHAMPOO + CONDICONADOR NIELY GOLD 275ML / 175ML SALVA FIOS </t>
+          <t xml:space="preserve">KIT SHAMPOO + CONDICONADOR NIELY GOLD 300ML / 200ML QUERATINA REPARAÇÃO </t>
         </is>
       </c>
       <c r="E396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>214327</v>
+        <v>110487</v>
       </c>
       <c r="B397" t="inlineStr">
         <is>
@@ -8913,19 +8913,19 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>KIT SHAMPOO + CONDICONADOR NIELY GOLD HIDRA AGUA COCO</t>
+          <t>KIT SH+CONDIC NIELY GOLD. LISO PROLONGAD</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t xml:space="preserve">KIT SHAMPOO + CONDICONADOR NIELY GOLD 300ML / 200ML HIDRATANTE AGUA COCO </t>
+          <t xml:space="preserve">KIT SHAMPOO + CONDICONADOR NIELY GOLD 300ML / 500ML LISO PROLONGADADO </t>
         </is>
       </c>
       <c r="E397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>110941</v>
+        <v>122533</v>
       </c>
       <c r="B398" t="inlineStr">
         <is>
@@ -8934,19 +8934,19 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>KIT SHAMPOO + CONDICONADOR NIELY GOLD QUERATINAQUERATIN</t>
+          <t>KIT SH+CONDIC NIELY GOLD. OLEO DE ARGAN</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t xml:space="preserve">KIT SHAMPOO + CONDICONADOR NIELY GOLD 300ML / 200ML QUERATINA REPARAÇÃO </t>
+          <t xml:space="preserve">KIT SHAMPOO + CONDICONADOR NIELY GOLD 300ML OLEO DE ARGAN </t>
         </is>
       </c>
       <c r="E398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>110487</v>
+        <v>196735</v>
       </c>
       <c r="B399" t="inlineStr">
         <is>
@@ -8955,19 +8955,19 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>KIT SH+CONDIC NIELY GOLD. LISO PROLONGAD</t>
+          <t>NIELY GOLD - CR TRAT 430G COMPRIDOS+FORT</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t xml:space="preserve">KIT SHAMPOO + CONDICONADOR NIELY GOLD 300ML / 500ML LISO PROLONGADADO </t>
+          <t>KIT SHAMPOO + CONDICONADOR NIELY GOLD 430G COMPRIDOS + FORTES</t>
         </is>
       </c>
       <c r="E399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>122533</v>
+        <v>277148</v>
       </c>
       <c r="B400" t="inlineStr">
         <is>
@@ -8976,12 +8976,12 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>KIT SH+CONDIC NIELY GOLD. OLEO DE ARGAN</t>
+          <t>KIT SHAMPOO + CONDICONADOR NIELY GOLD CACHOS 450ML DEF</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t xml:space="preserve">KIT SHAMPOO + CONDICONADOR NIELY GOLD 300ML OLEO DE ARGAN </t>
+          <t>KIT SHAMPOO + CONDICONADOR NIELY GOLD 450ML DEFESA PROLONGADA</t>
         </is>
       </c>
       <c r="E400" t="inlineStr"/>
@@ -9701,7 +9701,7 @@
     </row>
     <row r="434">
       <c r="A434" t="n">
-        <v>253878</v>
+        <v>320467</v>
       </c>
       <c r="B434" t="inlineStr">
         <is>
@@ -9710,19 +9710,19 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENERG BALY ENERGY DRINK 2L </t>
+          <t>ENERGETICO BALY 2L CITRUS PET</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENERGETICO BALY 2L ENERGY DRINK </t>
+          <t xml:space="preserve">ENERGETICO BALY 2L CITRUS </t>
         </is>
       </c>
       <c r="E434" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" t="n">
-        <v>253880</v>
+        <v>303008</v>
       </c>
       <c r="B435" t="inlineStr">
         <is>
@@ -9731,19 +9731,21 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENERG BALY MACA VERDE PET 2L </t>
+          <t>ENERGETICO BALY ENERGY 2L CRANBERRY PET</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENERGETICO BALY 2L MAÇÃ VERDE </t>
-        </is>
-      </c>
-      <c r="E435" t="inlineStr"/>
+          <t>ENERGETICO BALY 2L ENERGY CRANBERRY</t>
+        </is>
+      </c>
+      <c r="E435" t="n">
+        <v>15.99</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
-        <v>320467</v>
+        <v>253878</v>
       </c>
       <c r="B436" t="inlineStr">
         <is>
@@ -9752,19 +9754,19 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>ENERGETICO BALY 2L CITRUS PET</t>
+          <t xml:space="preserve">ENERG BALY ENERGY DRINK 2L </t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENERGETICO BALY 2L CITRUS </t>
+          <t xml:space="preserve">ENERGETICO BALY 2L ENERGY DRINK </t>
         </is>
       </c>
       <c r="E436" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" t="n">
-        <v>303008</v>
+        <v>253877</v>
       </c>
       <c r="B437" t="inlineStr">
         <is>
@@ -9773,21 +9775,19 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>ENERGETICO BALY ENERGY 2L CRANBERRY PET</t>
+          <t>ENERG BALY DRINK 2L COCO E ACAI PET</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>ENERGETICO BALY 2L ENERGY CRANBERRY</t>
-        </is>
-      </c>
-      <c r="E437" t="n">
-        <v>15.99</v>
-      </c>
+          <t xml:space="preserve">ENERGETICO BALY 2L ENERGY DRINK COCO E ACAI </t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" t="n">
-        <v>253877</v>
+        <v>244424</v>
       </c>
       <c r="B438" t="inlineStr">
         <is>
@@ -9796,19 +9796,19 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>ENERG BALY DRINK 2L COCO E ACAI PET</t>
+          <t>ENERG BALY 2L ENERGY DRINK MELANCIA</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENERGETICO BALY 2L ENERGY DRINK COCO E ACAI </t>
+          <t xml:space="preserve">ENERGETICO BALY 2L ENERGY DRINK MELANCIA </t>
         </is>
       </c>
       <c r="E438" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" t="n">
-        <v>244424</v>
+        <v>244426</v>
       </c>
       <c r="B439" t="inlineStr">
         <is>
@@ -9817,19 +9817,19 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>ENERG BALY 2L ENERGY DRINK MELANCIA</t>
+          <t>ENERGETICO BALY 2L FRUTAS TROPICAIS PET</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENERGETICO BALY 2L ENERGY DRINK MELANCIA </t>
+          <t xml:space="preserve">ENERGETICO BALY 2L FRUTAS TROPICAIS </t>
         </is>
       </c>
       <c r="E439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" t="n">
-        <v>244426</v>
+        <v>253880</v>
       </c>
       <c r="B440" t="inlineStr">
         <is>
@@ -9838,12 +9838,12 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>ENERGETICO BALY 2L FRUTAS TROPICAIS PET</t>
+          <t xml:space="preserve">ENERG BALY MACA VERDE PET 2L </t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENERGETICO BALY 2L FRUTAS TROPICAIS </t>
+          <t xml:space="preserve">ENERGETICO BALY 2L MAÇÃ VERDE </t>
         </is>
       </c>
       <c r="E440" t="inlineStr"/>
@@ -10005,7 +10005,7 @@
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>286589</v>
+        <v>229014</v>
       </c>
       <c r="B448" t="inlineStr">
         <is>
@@ -10014,21 +10014,21 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>BEBIDA ENGOV AFTER 250ML BERRY VIBES</t>
+          <t>AGUA DE COCO MAIS COCO 1L</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>BEBIDA ENGOV AFTER 250ML BERRY VIBES</t>
+          <t>AGUA DE COCO MAIS COCO 1L</t>
         </is>
       </c>
       <c r="E448" t="n">
-        <v>9.99</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>287184</v>
+        <v>286589</v>
       </c>
       <c r="B449" t="inlineStr">
         <is>
@@ -10037,12 +10037,12 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>BEBIDA ENGOV AFTER 250ML CITRUS</t>
+          <t>BEBIDA ENGOV AFTER 250ML BERRY VIBES</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>BEBIDA ENGOV AFTER 250ML CITRUS</t>
+          <t>BEBIDA ENGOV AFTER 250ML BERRY VIBES</t>
         </is>
       </c>
       <c r="E449" t="n">
@@ -10051,7 +10051,7 @@
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>287177</v>
+        <v>287184</v>
       </c>
       <c r="B450" t="inlineStr">
         <is>
@@ -10060,12 +10060,12 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>BEBIDA ENGOV AFTER 250ML TANGERINA</t>
+          <t>BEBIDA ENGOV AFTER 250ML CITRUS</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>BEBIDA ENGOV AFTER 250ML TANGERINA</t>
+          <t>BEBIDA ENGOV AFTER 250ML CITRUS</t>
         </is>
       </c>
       <c r="E450" t="n">
@@ -10074,7 +10074,7 @@
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>161871</v>
+        <v>287177</v>
       </c>
       <c r="B451" t="inlineStr">
         <is>
@@ -10083,21 +10083,21 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>REFRIG GUARANA TUCHAUA 2LT</t>
+          <t>BEBIDA ENGOV AFTER 250ML TANGERINA</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t xml:space="preserve">REFRIGANTE TUCHAUA 2L GUARANA </t>
+          <t>BEBIDA ENGOV AFTER 250ML TANGERINA</t>
         </is>
       </c>
       <c r="E451" t="n">
-        <v>7.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
-        <v>108686</v>
+        <v>161871</v>
       </c>
       <c r="B452" t="inlineStr">
         <is>
@@ -10106,12 +10106,12 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>REFRIG SODA LIMONADA ANTARCTICA PET 2 LT</t>
+          <t>REFRIG GUARANA TUCHAUA 2LT</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>REFRIGERANTE ANTARCTICA SODA LIMONADA 2L</t>
+          <t xml:space="preserve">REFRIGANTE TUCHAUA 2L GUARANA </t>
         </is>
       </c>
       <c r="E452" t="n">
@@ -10120,7 +10120,7 @@
     </row>
     <row r="453">
       <c r="A453" t="n">
-        <v>104406</v>
+        <v>108686</v>
       </c>
       <c r="B453" t="inlineStr">
         <is>
@@ -10129,19 +10129,21 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>REFRIGERANTE COCA COLA 2L</t>
+          <t>REFRIG SODA LIMONADA ANTARCTICA PET 2 LT</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>REFRIGERANTE COCA COLA 2L</t>
-        </is>
-      </c>
-      <c r="E453" t="inlineStr"/>
+          <t>REFRIGERANTE ANTARCTICA SODA LIMONADA 2L</t>
+        </is>
+      </c>
+      <c r="E453" t="n">
+        <v>7.99</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
-        <v>104404</v>
+        <v>104406</v>
       </c>
       <c r="B454" t="inlineStr">
         <is>
@@ -10150,19 +10152,19 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>REFRIG FANTA LARANJA 2L</t>
+          <t>REFRIGERANTE COCA COLA 2L</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t xml:space="preserve">REFRIGERANTE FANTA 2L LARANJA </t>
+          <t>REFRIGERANTE COCA COLA 2L</t>
         </is>
       </c>
       <c r="E454" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" t="n">
-        <v>104410</v>
+        <v>104404</v>
       </c>
       <c r="B455" t="inlineStr">
         <is>
@@ -10171,19 +10173,19 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>REFRIG GUARANA ANTARCTICA 2L PET ORIG</t>
+          <t>REFRIG FANTA LARANJA 2L</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>REFRIGERANTE GUARANA ANTARCTICA 2L</t>
+          <t xml:space="preserve">REFRIGERANTE FANTA 2L LARANJA </t>
         </is>
       </c>
       <c r="E455" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" t="n">
-        <v>104405</v>
+        <v>104410</v>
       </c>
       <c r="B456" t="inlineStr">
         <is>
@@ -10192,63 +10194,63 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>REFRIG SUKITA 2L LARANJA</t>
+          <t>REFRIG GUARANA ANTARCTICA 2L PET ORIG</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t xml:space="preserve">REFRIGERANTE SUKITA 2L LARANJA </t>
+          <t>REFRIGERANTE GUARANA ANTARCTICA 2L</t>
         </is>
       </c>
       <c r="E456" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" t="n">
-        <v>102237</v>
+        <v>104405</v>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 SUCO</t>
+          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>SUCO UVA INTEGRAL TINTO AURORA 1,5L VD</t>
+          <t>REFRIG SUKITA 2L LARANJA</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>SUCO DE UVA AURORA VIDRO 1,5L INTEGRAL TINTO</t>
-        </is>
-      </c>
-      <c r="E457" t="n">
-        <v>27.99</v>
-      </c>
+          <t xml:space="preserve">REFRIGERANTE SUKITA 2L LARANJA </t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" t="n">
-        <v>239446</v>
+        <v>102237</v>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA</t>
+          <t>#05 BEBIDA - #00 SUCO</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>CERVEJA AMSTEL 269ML LAGER LT C/ 12UNID</t>
+          <t>SUCO UVA INTEGRAL TINTO AURORA 1,5L VD</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t xml:space="preserve">CERVEJA AMSTEL 12 X 269ML LAGER </t>
-        </is>
-      </c>
-      <c r="E458" t="inlineStr"/>
+          <t>SUCO DE UVA AURORA VIDRO 1,5L INTEGRAL TINTO</t>
+        </is>
+      </c>
+      <c r="E458" t="n">
+        <v>27.99</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
-        <v>298701</v>
+        <v>247800</v>
       </c>
       <c r="B459" t="inlineStr">
         <is>
@@ -10257,21 +10259,19 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>CERVEJA AMSTEL 350ML LAGER SLEEK C/12 UN</t>
+          <t>CERV BUDWEISER 330ML LAGER LN UNID</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>CERVEJA AMSTEL 12 X 350ML LAGER SLEEK</t>
-        </is>
-      </c>
-      <c r="E459" t="n">
-        <v>4.09</v>
-      </c>
+          <t>CERVEJA BUDWEISER 330ML LARGER LONG NECK</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" t="n">
-        <v>287369</v>
+        <v>267604</v>
       </c>
       <c r="B460" t="inlineStr">
         <is>
@@ -10280,19 +10280,21 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>CERV ANTARCTICA ORIGINAL 269ML LT C/15UN</t>
+          <t>CERVEJA BUDWEISER 330ML ZERO ALCOOL LN U</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t xml:space="preserve">CERVEJA ANTARCTICA 15 X 269ML ORIGINAL </t>
-        </is>
-      </c>
-      <c r="E460" t="inlineStr"/>
+          <t>CERVEJA BUDWEISER 330ML ZERO ALCOOL LONG NECK</t>
+        </is>
+      </c>
+      <c r="E460" t="n">
+        <v>5.99</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
-        <v>168712</v>
+        <v>239382</v>
       </c>
       <c r="B461" t="inlineStr">
         <is>
@@ -10301,21 +10303,21 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>CERV ANTARCTICA 269ML C/ 15UND</t>
+          <t>CERV DEVASSA PURO MALTE 269ML UNID</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>CERVEJA ANTARCTICA 15 X 269ML PILSEN</t>
+          <t>CERVEJA DEVASSA 269ML PURO MALTE</t>
         </is>
       </c>
       <c r="E461" t="n">
-        <v>2.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
-        <v>170451</v>
+        <v>184034</v>
       </c>
       <c r="B462" t="inlineStr">
         <is>
@@ -10324,19 +10326,21 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>CERV BRAHMA CHOPP LATA 269ML C/ 15 UNID</t>
+          <t>CERVEJA HEINEKEN 250ML LN LAGER UNID</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>CERVEJA BRAHMA CHOPP 15 X 269ML</t>
-        </is>
-      </c>
-      <c r="E462" t="inlineStr"/>
+          <t>CERVEJA HEINEKEN 250ML LONG NECK LAGER</t>
+        </is>
+      </c>
+      <c r="E462" t="n">
+        <v>5.69</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
-        <v>247800</v>
+        <v>242930</v>
       </c>
       <c r="B463" t="inlineStr">
         <is>
@@ -10345,19 +10349,19 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>CERV BUDWEISER 330ML LAGER LN UNID</t>
+          <t>CERVEJA HEINEKEN 330ML UND</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>CERVEJA BUDWEISER 330ML LARGER LONG NECK</t>
+          <t>CERVEJA HEINEKEN 330ML</t>
         </is>
       </c>
       <c r="E463" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" t="n">
-        <v>177250</v>
+        <v>303282</v>
       </c>
       <c r="B464" t="inlineStr">
         <is>
@@ -10366,19 +10370,21 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>CERV DEVASSA PURO MALTE 269ML C/ 12UND</t>
+          <t>CERVEJA HEINEKEN 350ML SLEEK LT UNID</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>CERVEJA DEVASSA 12 X 269ML PURO MALTE</t>
-        </is>
-      </c>
-      <c r="E464" t="inlineStr"/>
+          <t>CERVEJA HEINEKEN 350ML SLEEK</t>
+        </is>
+      </c>
+      <c r="E464" t="n">
+        <v>6.19</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
-        <v>239382</v>
+        <v>298123</v>
       </c>
       <c r="B465" t="inlineStr">
         <is>
@@ -10387,21 +10393,21 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>CERV DEVASSA PURO MALTE 269ML UNID</t>
+          <t>CERVEJA HEINEKEN 350ML ZERO SLEEK UNID</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>CERVEJA DEVASSA 269ML PURO MALTE</t>
+          <t>CERVEJA HEINEKEN 350ML ZERO SLEEK</t>
         </is>
       </c>
       <c r="E465" t="n">
-        <v>2.69</v>
+        <v>6.19</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
-        <v>303283</v>
+        <v>286362</v>
       </c>
       <c r="B466" t="inlineStr">
         <is>
@@ -10410,287 +10416,287 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 350ML SLEEK LT C/12 UNI</t>
+          <t>CERVEJA SPATEN 600ML PURO MALTE LN</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 12 X 350ML SLEEK</t>
+          <t>CERVEJA SPATEN 600ML PURO MALTE LONG NECK</t>
         </is>
       </c>
       <c r="E466" t="n">
-        <v>5.99</v>
+        <v>9.49</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
-        <v>184034</v>
+        <v>239446</v>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA</t>
+          <t>#05 BEBIDA - CERVEJA CX</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 250ML LN LAGER UNID</t>
+          <t>CERVEJA AMSTEL 269ML LAGER LT C/ 12UNID</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 250ML LONG NECK LAGER</t>
-        </is>
-      </c>
-      <c r="E467" t="n">
-        <v>5.69</v>
-      </c>
+          <t xml:space="preserve">CERVEJA AMSTEL 12 X 269ML LAGER </t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" t="n">
-        <v>242930</v>
+        <v>298701</v>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA</t>
+          <t>#05 BEBIDA - CERVEJA CX</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 330ML UND</t>
+          <t>CERVEJA AMSTEL 350ML LAGER SLEEK C/12 UN</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 330ML</t>
-        </is>
-      </c>
-      <c r="E468" t="inlineStr"/>
+          <t>CERVEJA AMSTEL 12 X 350ML LAGER SLEEK</t>
+        </is>
+      </c>
+      <c r="E468" t="n">
+        <v>4.09</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
-        <v>303282</v>
+        <v>287369</v>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA</t>
+          <t>#05 BEBIDA - CERVEJA CX</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 350ML SLEEK LT UNID</t>
+          <t>CERV ANTARCTICA ORIGINAL 269ML LT C/15UN</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 350ML SLEEK</t>
-        </is>
-      </c>
-      <c r="E469" t="n">
-        <v>6.19</v>
-      </c>
+          <t xml:space="preserve">CERVEJA ANTARCTICA 15 X 269ML ORIGINAL </t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" t="n">
-        <v>108423</v>
+        <v>168712</v>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA</t>
+          <t>#05 BEBIDA - CERVEJA CX</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 330ML C/ 6UNID</t>
+          <t>CERV ANTARCTICA 269ML C/ 15UND</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 6 X 330ML</t>
+          <t>CERVEJA ANTARCTICA 15 X 269ML PILSEN</t>
         </is>
       </c>
       <c r="E470" t="n">
-        <v>6.99</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
-        <v>324556</v>
+        <v>170451</v>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA</t>
+          <t>#05 BEBIDA - CERVEJA CX</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>CERVEJA SKOL PILSEN 269ML CAIXA C/15 MUL</t>
+          <t>CERV BRAHMA CHOPP LATA 269ML C/ 15 UNID</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>CERVEJA SKOL 15 X 269ML PILSEN</t>
-        </is>
-      </c>
-      <c r="E471" t="n">
-        <v>44.89</v>
-      </c>
+          <t>CERVEJA BRAHMA CHOPP 15 X 269ML</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" t="n">
-        <v>107376</v>
+        <v>177250</v>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA</t>
+          <t>#05 BEBIDA - CERVEJA CX</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>CERVEJA SKOL 269ML PILSEN LT C/15 UNID</t>
+          <t>CERV DEVASSA PURO MALTE 269ML C/ 12UND</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t xml:space="preserve">CERVEJA SKOL 15 X 269ML PILSEN </t>
+          <t>CERVEJA DEVASSA 12 X 269ML PURO MALTE</t>
         </is>
       </c>
       <c r="E472" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" t="n">
-        <v>259153</v>
+        <v>303283</v>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA</t>
+          <t>#05 BEBIDA - CERVEJA CX</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>CERVEJA SPATEN PURO MALTE LT 350ML C/12U</t>
+          <t>CERVEJA HEINEKEN 350ML SLEEK LT C/12 UNI</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>CERVEJA SPATEN 12 X 350ML PURO MALTE</t>
+          <t>CERVEJA HEINEKEN 12 X 350ML SLEEK</t>
         </is>
       </c>
       <c r="E473" t="n">
-        <v>4.79</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
-        <v>286362</v>
+        <v>309102</v>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJA</t>
+          <t>#05 BEBIDA - CERVEJA CX</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>CERVEJA SPATEN 600ML PURO MALTE LN</t>
+          <t>CERVEJA HEINEKEN 350ML ZERO SLEEK C/12UN</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>CERVEJA SPATEN 600ML PURO MALTE LONG NECK</t>
+          <t>CERVEJA HEINEKEN 12 X 350ML ZERO SLEEK</t>
         </is>
       </c>
       <c r="E474" t="n">
-        <v>9.49</v>
+        <v>6.19</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
-        <v>102242</v>
+        <v>108423</v>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
+          <t>#05 BEBIDA - CERVEJA CX</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>AGUARD VELHO BARREIRO 910ML</t>
+          <t>CERVEJA HEINEKEN 330ML C/ 6UNID</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>AGUARDENTE VELHO BARREIRO 910ML</t>
+          <t>CERVEJA HEINEKEN 6 X 330ML</t>
         </is>
       </c>
       <c r="E475" t="n">
-        <v>14.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
-        <v>293188</v>
+        <v>324556</v>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
+          <t>#05 BEBIDA - CERVEJA CX</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>CACHACA PIRASSUNUNGA 51 RAIZ 600ML</t>
+          <t>CERVEJA SKOL PILSEN 269ML CAIXA C/15 MUL</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t xml:space="preserve">CACHACA 51 600ML RAIZ </t>
-        </is>
-      </c>
-      <c r="E476" t="inlineStr"/>
+          <t>CERVEJA SKOL 15 X 269ML PILSEN</t>
+        </is>
+      </c>
+      <c r="E476" t="n">
+        <v>44.89</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
-        <v>102085</v>
+        <v>107376</v>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
+          <t>#05 BEBIDA - CERVEJA CX</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>CACHACA 51 PIRASSUNUNGA 965ML TRAD</t>
+          <t>CERVEJA SKOL 269ML PILSEN LT C/15 UNID</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>CACHACA 51 965ML</t>
+          <t xml:space="preserve">CERVEJA SKOL 15 X 269ML PILSEN </t>
         </is>
       </c>
       <c r="E477" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" t="n">
-        <v>215568</v>
+        <v>259153</v>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
+          <t>#05 BEBIDA - CERVEJA CX</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>CACHACA BANANAZINHA 900ML</t>
+          <t>CERVEJA SPATEN PURO MALTE LT 350ML C/12U</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>CACHACA BANANAZINHA 900ML</t>
-        </is>
-      </c>
-      <c r="E478" t="inlineStr"/>
+          <t>CERVEJA SPATEN 12 X 350ML PURO MALTE</t>
+        </is>
+      </c>
+      <c r="E478" t="n">
+        <v>4.79</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
-        <v>174010</v>
+        <v>102242</v>
       </c>
       <c r="B479" t="inlineStr">
         <is>
@@ -10699,19 +10705,21 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>CACHACA SELETA 600ML</t>
+          <t>AGUARD VELHO BARREIRO 910ML</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>CACHAÇA SELETA 600ML</t>
-        </is>
-      </c>
-      <c r="E479" t="inlineStr"/>
+          <t>AGUARDENTE VELHO BARREIRO 910ML</t>
+        </is>
+      </c>
+      <c r="E479" t="n">
+        <v>14.99</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
-        <v>301843</v>
+        <v>293188</v>
       </c>
       <c r="B480" t="inlineStr">
         <is>
@@ -10720,19 +10728,19 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>APERITIVO BITER CAMPARI 998ML</t>
+          <t>CACHACA PIRASSUNUNGA 51 RAIZ 600ML</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>CAMPARI 998ML</t>
+          <t xml:space="preserve">CACHACA 51 600ML RAIZ </t>
         </is>
       </c>
       <c r="E480" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" t="n">
-        <v>219274</v>
+        <v>102085</v>
       </c>
       <c r="B481" t="inlineStr">
         <is>
@@ -10741,19 +10749,19 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>GIN GORDONS 750ML</t>
+          <t>CACHACA 51 PIRASSUNUNGA 965ML TRAD</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>GIN GORDONS 750ML</t>
+          <t>CACHACA 51 965ML</t>
         </is>
       </c>
       <c r="E481" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" t="n">
-        <v>206930</v>
+        <v>215568</v>
       </c>
       <c r="B482" t="inlineStr">
         <is>
@@ -10762,19 +10770,19 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>GIN TANQUERAY LONDON 750ML</t>
+          <t>CACHACA BANANAZINHA 900ML</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>GIN TANQUERAY LONDON 750ML</t>
+          <t>CACHACA BANANAZINHA 900ML</t>
         </is>
       </c>
       <c r="E482" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" t="n">
-        <v>110373</v>
+        <v>174010</v>
       </c>
       <c r="B483" t="inlineStr">
         <is>
@@ -10783,19 +10791,19 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>WHISKY BLACK &amp;WHITE 1L 8 ANOS</t>
+          <t>CACHACA SELETA 600ML</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t xml:space="preserve">WHISKY BLACK &amp; WHITE 1L 8 ANOS </t>
+          <t>CACHAÇA SELETA 600ML</t>
         </is>
       </c>
       <c r="E483" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" t="n">
-        <v>248750</v>
+        <v>301843</v>
       </c>
       <c r="B484" t="inlineStr">
         <is>
@@ -10804,21 +10812,19 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>WHISKY NATU NOBILIS APERITIVO 1L</t>
+          <t>APERITIVO BITER CAMPARI 998ML</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>WHISKY NATU NOBILIS 1L APERITIVO</t>
-        </is>
-      </c>
-      <c r="E484" t="n">
-        <v>55.99</v>
-      </c>
+          <t>CAMPARI 998ML</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" t="n">
-        <v>102077</v>
+        <v>219274</v>
       </c>
       <c r="B485" t="inlineStr">
         <is>
@@ -10827,208 +10833,214 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>WHISKY OLD PARR 12 ANOS 1L</t>
+          <t>GIN GORDONS 750ML</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t xml:space="preserve">WHISKY OLD PARR 1L 12 ANOS </t>
+          <t>GIN GORDONS 750ML</t>
         </is>
       </c>
       <c r="E485" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" t="n">
-        <v>295198</v>
+        <v>206930</v>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - FERMENTADOS</t>
+          <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>CHOPP DE VINHO STEMPEL 600ML RED</t>
+          <t>GIN TANQUERAY LONDON 750ML</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHOPP DE VINHO STEMPEL 600ML RED </t>
+          <t>GIN TANQUERAY LONDON 750ML</t>
         </is>
       </c>
       <c r="E486" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" t="n">
-        <v>155994</v>
+        <v>110373</v>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - FERMENTADOS</t>
+          <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>VINHO GALIOTTO 1L TINTO SECO</t>
+          <t>WHISKY BLACK &amp;WHITE 1L 8 ANOS</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t xml:space="preserve">VINHO GALIOTTO 1L TINTO SECO </t>
+          <t xml:space="preserve">WHISKY BLACK &amp; WHITE 1L 8 ANOS </t>
         </is>
       </c>
       <c r="E487" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" t="n">
-        <v>139964</v>
+        <v>248750</v>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - FERMENTADOS</t>
+          <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t xml:space="preserve">VINHO PERGOLA TINTO SUAVE 1L </t>
+          <t>WHISKY NATU NOBILIS APERITIVO 1L</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t xml:space="preserve">VINHO PERGOLA 1L TINTO SUAVE </t>
-        </is>
-      </c>
-      <c r="E488" t="inlineStr"/>
+          <t>WHISKY NATU NOBILIS 1L APERITIVO</t>
+        </is>
+      </c>
+      <c r="E488" t="n">
+        <v>55.99</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
-        <v>105842</v>
+        <v>102077</v>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>ASA FRANGO KG</t>
+          <t>WHISKY OLD PARR 12 ANOS 1L</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>ASA DE FRANGO KG</t>
+          <t xml:space="preserve">WHISKY OLD PARR 1L 12 ANOS </t>
         </is>
       </c>
       <c r="E489" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" t="n">
-        <v>119923</v>
+        <v>158451</v>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#05 BEBIDA - FERMENTADOS</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>CORACAO FRANGO AMERICANO CONG 1KG</t>
+          <t>CACHACA YPIOCA PRATA S/ PALHA 965 ML</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>CORAÇÃO DE FRANGO AMERICANO 1KG</t>
-        </is>
-      </c>
-      <c r="E490" t="inlineStr"/>
+          <t>CACHAÇA YPIOCA  965ML PRATA SEM PALHA</t>
+        </is>
+      </c>
+      <c r="E490" t="n">
+        <v>29.99</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
-        <v>105838</v>
+        <v>295198</v>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#05 BEBIDA - FERMENTADOS</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>COXA/SOBRECOXA FRANGO KG</t>
+          <t>CHOPP DE VINHO STEMPEL 600ML RED</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>COXA COM SOBRECOXA DE FRANGO KG</t>
+          <t xml:space="preserve">CHOPP DE VINHO STEMPEL 600ML RED </t>
         </is>
       </c>
       <c r="E491" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" t="n">
-        <v>105840</v>
+        <v>155994</v>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#05 BEBIDA - FERMENTADOS</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>COXINHA DA ASA FRANGO KG</t>
+          <t>VINHO GALIOTTO 1L TINTO SECO</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>COXINHA DA ASA DE FRANGO KG</t>
+          <t xml:space="preserve">VINHO GALIOTTO 1L TINTO SECO </t>
         </is>
       </c>
       <c r="E492" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" t="n">
-        <v>306504</v>
+        <v>139964</v>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#05 BEBIDA - FERMENTADOS</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>FIGADO FRANGO CONGELADO PERDIGAO 1KG</t>
+          <t xml:space="preserve">VINHO PERGOLA TINTO SUAVE 1L </t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>FIGADO DE FRANGO PERDIGAO KG</t>
+          <t xml:space="preserve">VINHO PERGOLA 1L TINTO SUAVE </t>
         </is>
       </c>
       <c r="E493" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" t="n">
-        <v>109597</v>
+        <v>134156</v>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - AVE</t>
+          <t>#05 BEBIDA - FERMENTADOS</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>FILE PEITO FRANGO KG</t>
+          <t>VODKA SKYY 980ML</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>FILE DE PEITO DE FRANGO KG</t>
-        </is>
-      </c>
-      <c r="E494" t="inlineStr"/>
+          <t>VODKA SKYY 980ML</t>
+        </is>
+      </c>
+      <c r="E494" t="n">
+        <v>59.99</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
-        <v>108786</v>
+        <v>105842</v>
       </c>
       <c r="B495" t="inlineStr">
         <is>
@@ -11037,19 +11049,19 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>FILEZINHO PEITO SADIA PACOTE 1KG</t>
+          <t>ASA FRANGO KG</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>FILEZINHO DE PEITO SADIA PCT 1KG</t>
+          <t>ASA DE FRANGO KG</t>
         </is>
       </c>
       <c r="E495" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" t="n">
-        <v>225767</v>
+        <v>119923</v>
       </c>
       <c r="B496" t="inlineStr">
         <is>
@@ -11058,19 +11070,19 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>FRANGO CONGELADO BONASA KG</t>
+          <t>CORACAO FRANGO AMERICANO CONG 1KG</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>FRANGO BONASA CONGELADO KG</t>
+          <t>CORAÇÃO DE FRANGO AMERICANO 1KG</t>
         </is>
       </c>
       <c r="E496" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" t="n">
-        <v>105853</v>
+        <v>105838</v>
       </c>
       <c r="B497" t="inlineStr">
         <is>
@@ -11079,19 +11091,19 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>FRANGO CONG MARINGA KG</t>
+          <t>COXA/SOBRECOXA FRANGO KG</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>FRANGO MARINGA CONGELADO KG</t>
+          <t>COXA COM SOBRECOXA DE FRANGO KG</t>
         </is>
       </c>
       <c r="E497" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" t="n">
-        <v>108788</v>
+        <v>105840</v>
       </c>
       <c r="B498" t="inlineStr">
         <is>
@@ -11100,19 +11112,19 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>FRANGO A PASSARINHO SADIA TEMPE PC 1KG</t>
+          <t>COXINHA DA ASA FRANGO KG</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRANGO SADIA PCT 1KG A PASSARINHO TEMPERADO </t>
+          <t>COXINHA DA ASA DE FRANGO KG</t>
         </is>
       </c>
       <c r="E498" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" t="n">
-        <v>185934</v>
+        <v>306504</v>
       </c>
       <c r="B499" t="inlineStr">
         <is>
@@ -11121,19 +11133,19 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>GALINHA LEVE NOROESTE CONG KG</t>
+          <t>FIGADO FRANGO CONGELADO PERDIGAO 1KG</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>GALINHA NOROESTE CONGELADA KG</t>
+          <t>FIGADO DE FRANGO PERDIGAO KG</t>
         </is>
       </c>
       <c r="E499" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" t="n">
-        <v>108774</v>
+        <v>109597</v>
       </c>
       <c r="B500" t="inlineStr">
         <is>
@@ -11142,19 +11154,19 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>MEIO DA ASA FRANGO SADIA 1KG TULIPA PAC</t>
+          <t>FILE PEITO FRANGO KG</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEIO DE DA ASA FRANGO SADIA PCT 1KG TULIPA </t>
+          <t>FILE DE PEITO DE FRANGO KG</t>
         </is>
       </c>
       <c r="E500" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" t="n">
-        <v>108773</v>
+        <v>108786</v>
       </c>
       <c r="B501" t="inlineStr">
         <is>
@@ -11163,155 +11175,145 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>MOELA FRANGO SADIA CONG BDJ 1KG</t>
+          <t>FILEZINHO PEITO SADIA PACOTE 1KG</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>MOELA DE FRANGO SADIA BDJ 1KG</t>
+          <t>FILEZINHO DE PEITO SADIA PCT 1KG</t>
         </is>
       </c>
       <c r="E501" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" t="n">
-        <v>157014</v>
+        <v>225767</v>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#06 AÇOUGUE - AVE</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>BOVINO - ACEM C/ OSSO KG</t>
+          <t>FRANGO CONGELADO BONASA KG</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>ACEM BOVINO COM OSSO KG</t>
-        </is>
-      </c>
-      <c r="E502" t="n">
-        <v>13.99</v>
-      </c>
+          <t>FRANGO BONASA CONGELADO KG</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" t="n">
-        <v>105470</v>
+        <v>105853</v>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#06 AÇOUGUE - AVE</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>BOVINO - ACEM KG</t>
+          <t>FRANGO CONG MARINGA KG</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>ACEM BOVINO KG</t>
+          <t>FRANGO MARINGA CONGELADO KG</t>
         </is>
       </c>
       <c r="E503" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" t="n">
-        <v>105450</v>
+        <v>108788</v>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#06 AÇOUGUE - AVE</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>BOVINO - ALCATRA KG</t>
+          <t>FRANGO A PASSARINHO SADIA TEMPE PC 1KG</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>ALCATRA BOVINA KG</t>
-        </is>
-      </c>
-      <c r="E504" t="n">
-        <v>37.99</v>
-      </c>
+          <t xml:space="preserve">FRANGO SADIA PCT 1KG A PASSARINHO TEMPERADO </t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" t="n">
-        <v>105460</v>
+        <v>185934</v>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#06 AÇOUGUE - AVE</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>BOVINA - BISTECA PALETA KG</t>
+          <t>GALINHA LEVE NOROESTE CONG KG</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>BISTECA BOVINA KG PALETA</t>
-        </is>
-      </c>
-      <c r="E505" t="n">
-        <v>19.99</v>
-      </c>
+          <t>GALINHA NOROESTE CONGELADA KG</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" t="n">
-        <v>158997</v>
+        <v>108774</v>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#06 AÇOUGUE - AVE</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>BOVINO - BISTECA DO ACEM KG</t>
+          <t>MEIO DA ASA FRANGO SADIA 1KG TULIPA PAC</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>BISTECA BOVINA KG ACEM</t>
-        </is>
-      </c>
-      <c r="E506" t="n">
-        <v>14.99</v>
-      </c>
+          <t xml:space="preserve">MEIO DE DA ASA FRANGO SADIA PCT 1KG TULIPA </t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" t="n">
-        <v>105459</v>
+        <v>108773</v>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - BOVINO</t>
+          <t>#06 AÇOUGUE - AVE</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>BOVINO - BISTECA MACA PEITO KG</t>
+          <t>MOELA FRANGO SADIA CONG BDJ 1KG</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>BISTECA DA MAÇÃ DO PEITO KG</t>
-        </is>
-      </c>
-      <c r="E507" t="n">
-        <v>20.99</v>
-      </c>
+          <t>MOELA DE FRANGO SADIA BDJ 1KG</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr"/>
     </row>
     <row r="508">
       <c r="A508" t="n">
-        <v>105461</v>
+        <v>157014</v>
       </c>
       <c r="B508" t="inlineStr">
         <is>
@@ -11320,19 +11322,21 @@
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>BOVINO - BISTECA CONTRA FILE KG</t>
+          <t>BOVINO - ACEM C/ OSSO KG</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>BISTECA DO CONTRA FILE KG</t>
-        </is>
-      </c>
-      <c r="E508" t="inlineStr"/>
+          <t>ACEM BOVINO COM OSSO KG</t>
+        </is>
+      </c>
+      <c r="E508" t="n">
+        <v>13.99</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="n">
-        <v>152232</v>
+        <v>105470</v>
       </c>
       <c r="B509" t="inlineStr">
         <is>
@@ -11341,19 +11345,19 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>BOVINO - BUCHO/HUMEM KG</t>
+          <t>BOVINO - ACEM KG</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>BUCHO BOVINO KG</t>
+          <t>ACEM BOVINO KG</t>
         </is>
       </c>
       <c r="E509" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" t="n">
-        <v>105456</v>
+        <v>105450</v>
       </c>
       <c r="B510" t="inlineStr">
         <is>
@@ -11362,21 +11366,21 @@
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>BOVINO - CARNE DE SOL KG SEGUNDA</t>
+          <t>BOVINO - ALCATRA KG</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>CARNE DE SOL KG SEGUNDA</t>
+          <t>ALCATRA BOVINA KG</t>
         </is>
       </c>
       <c r="E510" t="n">
-        <v>26.99</v>
+        <v>37.99</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="n">
-        <v>105468</v>
+        <v>158997</v>
       </c>
       <c r="B511" t="inlineStr">
         <is>
@@ -11385,21 +11389,21 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>BOVINO - CARNE MOIDA KG</t>
+          <t>BOVINO - BISTECA DO ACEM KG</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>CARNE MOIDA KG</t>
+          <t>BISTECA BOVINA KG ACEM</t>
         </is>
       </c>
       <c r="E511" t="n">
-        <v>15.99</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="n">
-        <v>105458</v>
+        <v>105460</v>
       </c>
       <c r="B512" t="inlineStr">
         <is>
@@ -11408,19 +11412,21 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>BOVINO - CHAMBARI KG</t>
+          <t>BOVINA - BISTECA PALETA KG</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>CHAMBARI KG</t>
-        </is>
-      </c>
-      <c r="E512" t="inlineStr"/>
+          <t>BISTECA BOVINA KG PALETA</t>
+        </is>
+      </c>
+      <c r="E512" t="n">
+        <v>19.99</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="n">
-        <v>105451</v>
+        <v>105459</v>
       </c>
       <c r="B513" t="inlineStr">
         <is>
@@ -11429,21 +11435,21 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>BOVINO - CONTRA FILE KG</t>
+          <t>BOVINO - BISTECA MACA PEITO KG</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>CONTRA FILE KG</t>
+          <t>BISTECA DA MAÇÃ DO PEITO KG</t>
         </is>
       </c>
       <c r="E513" t="n">
-        <v>36.99</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="n">
-        <v>105463</v>
+        <v>105461</v>
       </c>
       <c r="B514" t="inlineStr">
         <is>
@@ -11452,21 +11458,19 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>BOVINO - CORACAO KG</t>
+          <t>BOVINO - BISTECA CONTRA FILE KG</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>CORAÇÃO BOVINO KG</t>
-        </is>
-      </c>
-      <c r="E514" t="n">
-        <v>11.99</v>
-      </c>
+          <t>BISTECA DO CONTRA FILE KG</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" t="n">
-        <v>105471</v>
+        <v>152232</v>
       </c>
       <c r="B515" t="inlineStr">
         <is>
@@ -11475,19 +11479,19 @@
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>BOVINO - COSTELA KG</t>
+          <t>BOVINO - BUCHO/HUMEM KG</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>COSTELA BOVINA KG</t>
+          <t>BUCHO BOVINO KG</t>
         </is>
       </c>
       <c r="E515" t="inlineStr"/>
     </row>
     <row r="516">
       <c r="A516" t="n">
-        <v>105449</v>
+        <v>105456</v>
       </c>
       <c r="B516" t="inlineStr">
         <is>
@@ -11496,21 +11500,21 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>BOVINO - COXAO DURO KG</t>
+          <t>BOVINO - CARNE DE SOL KG SEGUNDA</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>COXÃO DURO KG</t>
+          <t>CARNE DE SOL KG SEGUNDA</t>
         </is>
       </c>
       <c r="E516" t="n">
-        <v>31.99</v>
+        <v>26.99</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="n">
-        <v>105435</v>
+        <v>105468</v>
       </c>
       <c r="B517" t="inlineStr">
         <is>
@@ -11519,21 +11523,21 @@
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>BOVINO - COXAO MOLE KG</t>
+          <t>BOVINO - CARNE MOIDA KG</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>COXAO MOLE KG</t>
+          <t>CARNE MOIDA KG</t>
         </is>
       </c>
       <c r="E517" t="n">
-        <v>36.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="n">
-        <v>105487</v>
+        <v>105458</v>
       </c>
       <c r="B518" t="inlineStr">
         <is>
@@ -11542,21 +11546,19 @@
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>BOVINO - CUPIM KG</t>
+          <t>BOVINO - CHAMBARI KG</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUPIM BOVINO KG </t>
-        </is>
-      </c>
-      <c r="E518" t="n">
-        <v>37.99</v>
-      </c>
+          <t>CHAMBARI KG</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" t="n">
-        <v>105453</v>
+        <v>105451</v>
       </c>
       <c r="B519" t="inlineStr">
         <is>
@@ -11565,19 +11567,21 @@
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>BOVINO - FILE MIGNON KG</t>
+          <t>BOVINO - CONTRA FILE KG</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>FILE MIGNON KG</t>
-        </is>
-      </c>
-      <c r="E519" t="inlineStr"/>
+          <t>CONTRA FILE KG</t>
+        </is>
+      </c>
+      <c r="E519" t="n">
+        <v>36.99</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="n">
-        <v>105474</v>
+        <v>105463</v>
       </c>
       <c r="B520" t="inlineStr">
         <is>
@@ -11586,19 +11590,21 @@
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>BOVINO - FRALDINHA KG</t>
+          <t>BOVINO - CORACAO KG</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>FRALDINHA BOVINA KG</t>
-        </is>
-      </c>
-      <c r="E520" t="inlineStr"/>
+          <t>CORAÇÃO BOVINO KG</t>
+        </is>
+      </c>
+      <c r="E520" t="n">
+        <v>11.99</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="n">
-        <v>107260</v>
+        <v>105471</v>
       </c>
       <c r="B521" t="inlineStr">
         <is>
@@ -11607,19 +11613,19 @@
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>BOVINO - MACA DO PEITO KG</t>
+          <t>BOVINO - COSTELA KG</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>MAÇÃ DO PEITO KG</t>
+          <t>COSTELA BOVINA KG</t>
         </is>
       </c>
       <c r="E521" t="inlineStr"/>
     </row>
     <row r="522">
       <c r="A522" t="n">
-        <v>115278</v>
+        <v>105449</v>
       </c>
       <c r="B522" t="inlineStr">
         <is>
@@ -11628,21 +11634,21 @@
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>BOVINO - MIOLO DA PALETA KG</t>
+          <t>BOVINO - COXAO DURO KG</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>MIOLO DA PALETA KG BOVINA</t>
+          <t>COXÃO DURO KG</t>
         </is>
       </c>
       <c r="E522" t="n">
-        <v>26.99</v>
+        <v>31.99</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="n">
-        <v>231292</v>
+        <v>105435</v>
       </c>
       <c r="B523" t="inlineStr">
         <is>
@@ -11651,19 +11657,21 @@
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>BOVINO - MIOLO DO ACEM KG</t>
+          <t>BOVINO - COXAO MOLE KG</t>
         </is>
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>MIOLO DO ACEM KG</t>
-        </is>
-      </c>
-      <c r="E523" t="inlineStr"/>
+          <t>COXAO MOLE KG</t>
+        </is>
+      </c>
+      <c r="E523" t="n">
+        <v>36.99</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="n">
-        <v>173342</v>
+        <v>105487</v>
       </c>
       <c r="B524" t="inlineStr">
         <is>
@@ -11672,19 +11680,21 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>BOVINO - MOCOTO KG</t>
+          <t>BOVINO - CUPIM KG</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>MOCOTO BOVINO KG</t>
-        </is>
-      </c>
-      <c r="E524" t="inlineStr"/>
+          <t xml:space="preserve">CUPIM BOVINO KG </t>
+        </is>
+      </c>
+      <c r="E524" t="n">
+        <v>37.99</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="n">
-        <v>105475</v>
+        <v>105453</v>
       </c>
       <c r="B525" t="inlineStr">
         <is>
@@ -11693,19 +11703,19 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>MUSCULO BOV KG</t>
+          <t>BOVINO - FILE MIGNON KG</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>MUSCULO BOVINO KG</t>
+          <t>FILE MIGNON KG</t>
         </is>
       </c>
       <c r="E525" t="inlineStr"/>
     </row>
     <row r="526">
       <c r="A526" t="n">
-        <v>105469</v>
+        <v>105474</v>
       </c>
       <c r="B526" t="inlineStr">
         <is>
@@ -11714,19 +11724,19 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>BOVINO - PALETA KG</t>
+          <t>BOVINO - FRALDINHA KG</t>
         </is>
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>PALETA BOVINA KG</t>
+          <t>FRALDINHA BOVINA KG</t>
         </is>
       </c>
       <c r="E526" t="inlineStr"/>
     </row>
     <row r="527">
       <c r="A527" t="n">
-        <v>261519</v>
+        <v>107260</v>
       </c>
       <c r="B527" t="inlineStr">
         <is>
@@ -11735,19 +11745,19 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>BOVINO - PICANHA FATIADA KG</t>
+          <t>BOVINO - MACA DO PEITO KG</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>PICANHA BOVINA KG FATIADA</t>
+          <t>MAÇÃ DO PEITO KG</t>
         </is>
       </c>
       <c r="E527" t="inlineStr"/>
     </row>
     <row r="528">
       <c r="A528" t="n">
-        <v>106249</v>
+        <v>115278</v>
       </c>
       <c r="B528" t="inlineStr">
         <is>
@@ -11756,145 +11766,147 @@
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>BOVINO - PICANHA QUALITY BEEF KG</t>
+          <t>BOVINO - MIOLO DA PALETA KG</t>
         </is>
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>PICANHA QUALITY BEEF KG</t>
-        </is>
-      </c>
-      <c r="E528" t="inlineStr"/>
+          <t>MIOLO DA PALETA KG BOVINA</t>
+        </is>
+      </c>
+      <c r="E528" t="n">
+        <v>26.99</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="n">
-        <v>286549</v>
+        <v>231292</v>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - EMBUTIDO</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>LINGUICA CALABRESA BONFRIGO KG</t>
+          <t>BOVINO - MIOLO DO ACEM KG</t>
         </is>
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>LINGUICA BONFRIGO CALABRESA KG</t>
+          <t>MIOLO DO ACEM KG</t>
         </is>
       </c>
       <c r="E529" t="inlineStr"/>
     </row>
     <row r="530">
       <c r="A530" t="n">
-        <v>305039</v>
+        <v>173342</v>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - EMBUTIDO</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>LINGUICA BOVINA KG CASEIRA</t>
+          <t>BOVINO - MOCOTO KG</t>
         </is>
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>LINGUICA BOVINA CASEIRA KG</t>
+          <t>MOCOTO BOVINO KG</t>
         </is>
       </c>
       <c r="E530" t="inlineStr"/>
     </row>
     <row r="531">
       <c r="A531" t="n">
-        <v>189031</v>
+        <v>105475</v>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - EMBUTIDO</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>LINGUICA MISTA FRICO KG</t>
+          <t>MUSCULO BOV KG</t>
         </is>
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>LINGUICA FRICO MISTA KG</t>
+          <t>MUSCULO BOVINO KG</t>
         </is>
       </c>
       <c r="E531" t="inlineStr"/>
     </row>
     <row r="532">
       <c r="A532" t="n">
-        <v>117117</v>
+        <v>105469</v>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - EMBUTIDO</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>LINGUICA TOSC SUINA FRIMESA KG</t>
+          <t>BOVINO - PALETA KG</t>
         </is>
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>LINGUICA FRIMESA TOSCANA SUINA KG</t>
+          <t>PALETA BOVINA KG</t>
         </is>
       </c>
       <c r="E532" t="inlineStr"/>
     </row>
     <row r="533">
       <c r="A533" t="n">
-        <v>289127</v>
+        <v>261519</v>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - EMBUTIDO</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>LINGUICA MISTA SADIA 215GR FININHA DEFUM</t>
+          <t>BOVINO - PICANHA FATIADA KG</t>
         </is>
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t xml:space="preserve">LINGUICA SADIA 215G MISTA FININHA DEFUMADA </t>
+          <t>PICANHA BOVINA KG FATIADA</t>
         </is>
       </c>
       <c r="E533" t="inlineStr"/>
     </row>
     <row r="534">
       <c r="A534" t="n">
-        <v>129515</v>
+        <v>106249</v>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - EMBUTIDO</t>
+          <t>#06 AÇOUGUE - BOVINO</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>LINGUICA CALABRESA SEARA KG CURADA</t>
+          <t>BOVINO - PICANHA QUALITY BEEF KG</t>
         </is>
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>LINGUICA SEARA CALABRESA CURADA KG</t>
+          <t>PICANHA QUALITY BEEF KG</t>
         </is>
       </c>
       <c r="E534" t="inlineStr"/>
     </row>
     <row r="535">
       <c r="A535" t="n">
-        <v>228422</v>
+        <v>286549</v>
       </c>
       <c r="B535" t="inlineStr">
         <is>
@@ -11903,19 +11915,19 @@
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>LINGUICA SUPER FRANGO KG FRANGO GROSSA</t>
+          <t>LINGUICA CALABRESA BONFRIGO KG</t>
         </is>
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t xml:space="preserve">LINGUICA SUPER FRANGO GROSSA KG </t>
+          <t>LINGUICA BONFRIGO CALABRESA KG</t>
         </is>
       </c>
       <c r="E535" t="inlineStr"/>
     </row>
     <row r="536">
       <c r="A536" t="n">
-        <v>105770</v>
+        <v>305039</v>
       </c>
       <c r="B536" t="inlineStr">
         <is>
@@ -11924,19 +11936,19 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>MORTADELA FRANGO PERDIGAO KG</t>
+          <t>LINGUICA BOVINA KG CASEIRA</t>
         </is>
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>MORTADELA PERDIGÃO FRANGO KG</t>
+          <t>LINGUICA BOVINA CASEIRA KG</t>
         </is>
       </c>
       <c r="E536" t="inlineStr"/>
     </row>
     <row r="537">
       <c r="A537" t="n">
-        <v>105765</v>
+        <v>189031</v>
       </c>
       <c r="B537" t="inlineStr">
         <is>
@@ -11945,19 +11957,19 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>MORTADELA MISTA PERDIGAO KG</t>
+          <t>LINGUICA MISTA FRICO KG</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>MORTADELA PERDIGAO MISTA KG</t>
+          <t>LINGUICA FRICO MISTA KG</t>
         </is>
       </c>
       <c r="E537" t="inlineStr"/>
     </row>
     <row r="538">
       <c r="A538" t="n">
-        <v>173405</v>
+        <v>117117</v>
       </c>
       <c r="B538" t="inlineStr">
         <is>
@@ -11966,19 +11978,19 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>MORTADELA DEFUMADA SEARA KG</t>
+          <t>LINGUICA TOSC SUINA FRIMESA KG</t>
         </is>
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t xml:space="preserve">MORTADELA SEARA DEFUMADA KG </t>
+          <t>LINGUICA FRIMESA TOSCANA SUINA KG</t>
         </is>
       </c>
       <c r="E538" t="inlineStr"/>
     </row>
     <row r="539">
       <c r="A539" t="n">
-        <v>111741</v>
+        <v>289127</v>
       </c>
       <c r="B539" t="inlineStr">
         <is>
@@ -11987,19 +11999,19 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>PRESUNTO COZIDO S/CAPA GORDURA SADIA</t>
+          <t>LINGUICA MISTA SADIA 215GR FININHA DEFUM</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRESUNTO SADIA COZIDO SEM CAPA GORDURA KG </t>
+          <t xml:space="preserve">LINGUICA SADIA 215G MISTA FININHA DEFUMADA </t>
         </is>
       </c>
       <c r="E539" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" t="n">
-        <v>286228</v>
+        <v>129515</v>
       </c>
       <c r="B540" t="inlineStr">
         <is>
@@ -12008,268 +12020,256 @@
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>SALSICHA BOUA KG</t>
+          <t>LINGUICA CALABRESA SEARA KG CURADA</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>SALSICHA BOUA KG</t>
+          <t>LINGUICA SEARA CALABRESA CURADA KG</t>
         </is>
       </c>
       <c r="E540" t="inlineStr"/>
     </row>
     <row r="541">
       <c r="A541" t="n">
-        <v>138538</v>
+        <v>228422</v>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - EMPANADO</t>
+          <t>#06 AÇOUGUE - EMBUTIDO</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>TEKITOS SEARA FRANGO 300G</t>
+          <t>LINGUICA SUPER FRANGO KG FRANGO GROSSA</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t xml:space="preserve">TEKITOS SEARA 300G FRANGO </t>
+          <t xml:space="preserve">LINGUICA SUPER FRANGO GROSSA KG </t>
         </is>
       </c>
       <c r="E541" t="inlineStr"/>
     </row>
     <row r="542">
       <c r="A542" t="n">
-        <v>127328</v>
+        <v>105770</v>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - EMPANADO</t>
+          <t>#06 AÇOUGUE - EMBUTIDO</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>TEKITOS SEARA QUEIJO OREGANO 300GR</t>
+          <t>MORTADELA FRANGO PERDIGAO KG</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t xml:space="preserve">TEKITOS SEARA 300G QUEIJO OREGANO </t>
+          <t>MORTADELA PERDIGÃO FRANGO KG</t>
         </is>
       </c>
       <c r="E542" t="inlineStr"/>
     </row>
     <row r="543">
       <c r="A543" t="n">
-        <v>323487</v>
+        <v>105765</v>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - FRUTOS DO MAR</t>
+          <t>#06 AÇOUGUE - EMBUTIDO</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>CAMARAO VAN S/C COZ IQF-M 45/80 40X300G</t>
+          <t>MORTADELA MISTA PERDIGAO KG</t>
         </is>
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>CAMARAO COSTA SUL 300G VAN SEM CABEÇA COZIDO</t>
-        </is>
-      </c>
-      <c r="E543" t="n">
-        <v>29.99</v>
-      </c>
+          <t>MORTADELA PERDIGAO MISTA KG</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr"/>
     </row>
     <row r="544">
       <c r="A544" t="n">
-        <v>303488</v>
+        <v>173405</v>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - FRUTOS DO MAR</t>
+          <t>#06 AÇOUGUE - EMBUTIDO</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>CAMARAO CINZA COSTAMAR 1KG DESC 51/60</t>
+          <t>MORTADELA DEFUMADA SEARA KG</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>CAMARÃO COSTAMAR 1KG CINZA DESCASCADO</t>
-        </is>
-      </c>
-      <c r="E544" t="n">
-        <v>115.99</v>
-      </c>
+          <t xml:space="preserve">MORTADELA SEARA DEFUMADA KG </t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr"/>
     </row>
     <row r="545">
       <c r="A545" t="n">
-        <v>323489</v>
+        <v>111741</v>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - FRUTOS DO MAR</t>
+          <t>#06 AÇOUGUE - EMBUTIDO</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>MEXILHAO COSTA SUL 300GR MARISCO DESCONC</t>
+          <t>PRESUNTO COZIDO S/CAPA GORDURA SADIA</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>MEXILHÃO COSTA SUL 300G MARISCO DESCONCHADO</t>
-        </is>
-      </c>
-      <c r="E545" t="n">
-        <v>25.99</v>
-      </c>
+          <t xml:space="preserve">PRESUNTO SADIA COZIDO SEM CAPA GORDURA KG </t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr"/>
     </row>
     <row r="546">
       <c r="A546" t="n">
-        <v>311307</v>
+        <v>286228</v>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - PEIXES</t>
+          <t>#06 AÇOUGUE - EMBUTIDO</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>BOLINHO DE TILAPIA 270GR CONG</t>
+          <t>SALSICHA BOUA KG</t>
         </is>
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>BOLINHO DE TILAPIA 270G CONGELADO</t>
-        </is>
-      </c>
-      <c r="E546" t="n">
-        <v>15.99</v>
-      </c>
+          <t>SALSICHA BOUA KG</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr"/>
     </row>
     <row r="547">
       <c r="A547" t="n">
-        <v>262170</v>
+        <v>138538</v>
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - PEIXES</t>
+          <t>#06 AÇOUGUE - EMPANADO</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>COSTELA DE TILAPIA KG</t>
+          <t>TEKITOS SEARA FRANGO 300G</t>
         </is>
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>COSTELA DE TILAPIA KG</t>
-        </is>
-      </c>
-      <c r="E547" t="n">
-        <v>29.99</v>
-      </c>
+          <t xml:space="preserve">TEKITOS SEARA 300G FRANGO </t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr"/>
     </row>
     <row r="548">
       <c r="A548" t="n">
-        <v>254014</v>
+        <v>127328</v>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - PEIXES</t>
+          <t>#06 AÇOUGUE - EMPANADO</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>PESCADA AMARELA FILE 1KG</t>
+          <t>TEKITOS SEARA QUEIJO OREGANO 300GR</t>
         </is>
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>FILÉ DE DOURADA VITÓRIA PESCADOS 1KG</t>
-        </is>
-      </c>
-      <c r="E548" t="n">
-        <v>35.99</v>
-      </c>
+          <t xml:space="preserve">TEKITOS SEARA 300G QUEIJO OREGANO </t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr"/>
     </row>
     <row r="549">
       <c r="A549" t="n">
-        <v>141831</v>
+        <v>323487</v>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - PEIXES</t>
+          <t>#06 AÇOUGUE - FRUTOS DO MAR</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>FILE DE PEIXE PANGA KG</t>
+          <t>CAMARAO VAN S/C COZ IQF-M 45/80 40X300G</t>
         </is>
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>FILÉ DE PANGA KG</t>
+          <t>CAMARAO COSTA SUL 300G VAN SEM CABEÇA COZIDO</t>
         </is>
       </c>
       <c r="E549" t="n">
-        <v>44.99</v>
+        <v>29.99</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="n">
-        <v>323501</v>
+        <v>303488</v>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - PEIXES</t>
+          <t>#06 AÇOUGUE - FRUTOS DO MAR</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>PEIXE SALMAO COSTA SUL 400GR C/PELE FILE</t>
+          <t>CAMARAO CINZA COSTAMAR 1KG DESC 51/60</t>
         </is>
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>FILÉ DE SALMAO COSTA SUL 400G COM PELE</t>
+          <t>CAMARÃO COSTAMAR 1KG CINZA DESCASCADO</t>
         </is>
       </c>
       <c r="E550" t="n">
-        <v>48.99</v>
+        <v>115.99</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="n">
-        <v>315711</v>
+        <v>323489</v>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - PEIXES</t>
+          <t>#06 AÇOUGUE - FRUTOS DO MAR</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>FILE DE TILAPIA DO PESCADO 500G</t>
+          <t>MEXILHAO COSTA SUL 300GR MARISCO DESCONC</t>
         </is>
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>FILÉ DE TILAPIA DO PESCADO 500G</t>
+          <t>MEXILHÃO COSTA SUL 300G MARISCO DESCONCHADO</t>
         </is>
       </c>
       <c r="E551" t="n">
-        <v>32.99</v>
+        <v>25.99</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="n">
-        <v>203263</v>
+        <v>311307</v>
       </c>
       <c r="B552" t="inlineStr">
         <is>
@@ -12278,21 +12278,21 @@
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>FILE DE TILAPIA KG</t>
+          <t>BOLINHO DE TILAPIA 270GR CONG</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>FILÉ DE TILAPIA KG</t>
+          <t>BOLINHO DE TILAPIA 270G CONGELADO</t>
         </is>
       </c>
       <c r="E552" t="n">
-        <v>49.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="n">
-        <v>284245</v>
+        <v>262170</v>
       </c>
       <c r="B553" t="inlineStr">
         <is>
@@ -12301,21 +12301,21 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>PESCADO PEIXITOS COSTA SUL 300GR</t>
+          <t>COSTELA DE TILAPIA KG</t>
         </is>
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>PEIXITOS COSTA SUL 300G</t>
+          <t>COSTELA DE TILAPIA KG</t>
         </is>
       </c>
       <c r="E553" t="n">
-        <v>10.99</v>
+        <v>29.99</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="n">
-        <v>284246</v>
+        <v>254014</v>
       </c>
       <c r="B554" t="inlineStr">
         <is>
@@ -12324,151 +12324,157 @@
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>TIRINHAS DE TILAP?A COSTA SUL 300GR EMPA</t>
+          <t>PESCADA AMARELA FILE 1KG</t>
         </is>
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>TIRINHAS DE TILÁPIA COSTA SUL 300G EMPANADO</t>
-        </is>
-      </c>
-      <c r="E554" t="inlineStr"/>
+          <t>FILÉ DE DOURADA VITÓRIA PESCADOS 1KG</t>
+        </is>
+      </c>
+      <c r="E554" t="n">
+        <v>35.99</v>
+      </c>
     </row>
     <row r="555">
       <c r="A555" t="n">
-        <v>298215</v>
+        <v>141831</v>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - SUINO</t>
+          <t>#06 AÇOUGUE - PEIXES</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>BACON BONFRIGO KG PALETA</t>
+          <t>FILE DE PEIXE PANGA KG</t>
         </is>
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t xml:space="preserve">BACON BONFRIGO PALETA KG </t>
-        </is>
-      </c>
-      <c r="E555" t="inlineStr"/>
+          <t>FILÉ DE PANGA KG</t>
+        </is>
+      </c>
+      <c r="E555" t="n">
+        <v>44.99</v>
+      </c>
     </row>
     <row r="556">
       <c r="A556" t="n">
-        <v>106053</v>
+        <v>323501</v>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - SUINO</t>
+          <t>#06 AÇOUGUE - PEIXES</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>SUINO - BISTECA CARRE FRESCA KG</t>
+          <t>PEIXE SALMAO COSTA SUL 400GR C/PELE FILE</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>BISTECA SUINA CARRE KG</t>
-        </is>
-      </c>
-      <c r="E556" t="inlineStr"/>
+          <t>FILÉ DE SALMAO COSTA SUL 400G COM PELE</t>
+        </is>
+      </c>
+      <c r="E556" t="n">
+        <v>48.99</v>
+      </c>
     </row>
     <row r="557">
       <c r="A557" t="n">
-        <v>105062</v>
+        <v>315711</v>
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - SUINO</t>
+          <t>#06 AÇOUGUE - PEIXES</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>SUINO - BISTECA PERNIL FRESCA KG</t>
+          <t>FILE DE TILAPIA DO PESCADO 500G</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>BISTECA SUINA DO PERNIL KG</t>
-        </is>
-      </c>
-      <c r="E557" t="inlineStr"/>
+          <t>FILÉ DE TILAPIA DO PESCADO 500G</t>
+        </is>
+      </c>
+      <c r="E557" t="n">
+        <v>32.99</v>
+      </c>
     </row>
     <row r="558">
       <c r="A558" t="n">
-        <v>320822</v>
+        <v>203263</v>
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - SUINO</t>
+          <t>#06 AÇOUGUE - PEIXES</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>SUINO - BISTECA PALETA FRESCA KG</t>
+          <t>FILE DE TILAPIA KG</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t xml:space="preserve">BISTECA SUINA KG PALETA FRESCA </t>
+          <t>FILÉ DE TILAPIA KG</t>
         </is>
       </c>
       <c r="E558" t="n">
-        <v>21.99</v>
+        <v>49.99</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="n">
-        <v>105433</v>
+        <v>284245</v>
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - SUINO</t>
+          <t>#06 AÇOUGUE - PEIXES</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>SUINO - COSTELA SUINA KG</t>
+          <t>PESCADO PEIXITOS COSTA SUL 300GR</t>
         </is>
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>COSTELA SUINA KG</t>
+          <t>PEIXITOS COSTA SUL 300G</t>
         </is>
       </c>
       <c r="E559" t="n">
-        <v>19.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="n">
-        <v>106054</v>
+        <v>284246</v>
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - SUINO</t>
+          <t>#06 AÇOUGUE - PEIXES</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>SUINO - LOMBO FRESCO KG</t>
+          <t>TIRINHAS DE TILAP?A COSTA SUL 300GR EMPA</t>
         </is>
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>LOMBO SUINO FRESCO KG</t>
-        </is>
-      </c>
-      <c r="E560" t="n">
-        <v>19.99</v>
-      </c>
+          <t>TIRINHAS DE TILÁPIA COSTA SUL 300G EMPANADO</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr"/>
     </row>
     <row r="561">
       <c r="A561" t="n">
-        <v>258810</v>
+        <v>298215</v>
       </c>
       <c r="B561" t="inlineStr">
         <is>
@@ -12477,19 +12483,19 @@
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>SUINO - PANCETA KG</t>
+          <t>BACON BONFRIGO KG PALETA</t>
         </is>
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>PANCETA SUINA KG</t>
+          <t xml:space="preserve">BACON BONFRIGO PALETA KG </t>
         </is>
       </c>
       <c r="E561" t="inlineStr"/>
     </row>
     <row r="562">
       <c r="A562" t="n">
-        <v>106052</v>
+        <v>106053</v>
       </c>
       <c r="B562" t="inlineStr">
         <is>
@@ -12498,21 +12504,19 @@
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>SUINO - PELE SUINA FRESCA KG</t>
+          <t>SUINO - BISTECA CARRE FRESCA KG</t>
         </is>
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>PELE SUINA KG</t>
-        </is>
-      </c>
-      <c r="E562" t="n">
-        <v>12.99</v>
-      </c>
+          <t>BISTECA SUINA CARRE KG</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr"/>
     </row>
     <row r="563">
       <c r="A563" t="n">
-        <v>106034</v>
+        <v>105062</v>
       </c>
       <c r="B563" t="inlineStr">
         <is>
@@ -12521,19 +12525,19 @@
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>SUINO - SUAN FRESCA KG</t>
+          <t>SUINO - BISTECA PERNIL FRESCA KG</t>
         </is>
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>SUAN SUINA KG</t>
+          <t>BISTECA SUINA DO PERNIL KG</t>
         </is>
       </c>
       <c r="E563" t="inlineStr"/>
     </row>
     <row r="564">
       <c r="A564" t="n">
-        <v>106032</v>
+        <v>320822</v>
       </c>
       <c r="B564" t="inlineStr">
         <is>
@@ -12542,147 +12546,155 @@
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>SUINO - TOUCINHO FRESCO KG</t>
+          <t>SUINO - BISTECA PALETA FRESCA KG</t>
         </is>
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>TOUCINHO FRESCO KG</t>
+          <t xml:space="preserve">BISTECA SUINA KG PALETA FRESCA </t>
         </is>
       </c>
       <c r="E564" t="n">
-        <v>18.99</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="n">
-        <v>110086</v>
+        <v>105433</v>
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>#08 BAZAR</t>
+          <t>#06 AÇOUGUE - SUINO</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>SUINO - SUAN FRESCA KG</t>
+          <t>SUINO - COSTELA SUINA KG</t>
         </is>
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t xml:space="preserve">COPO DESCARTAVEL TERMOPOT 180ML CRISTAL </t>
-        </is>
-      </c>
-      <c r="E565" t="inlineStr"/>
+          <t>COSTELA SUINA KG</t>
+        </is>
+      </c>
+      <c r="E565" t="n">
+        <v>19.99</v>
+      </c>
     </row>
     <row r="566">
       <c r="A566" t="n">
-        <v>114556</v>
+        <v>106054</v>
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>#08 BAZAR</t>
+          <t>#06 AÇOUGUE - SUINO</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>GARRAFAO TERMICO TERMOLAR 5LT AZUL</t>
+          <t>SUINO - LOMBO FRESCO KG</t>
         </is>
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARRAFAO TERMICO TERMOLAR 5L AZUL </t>
-        </is>
-      </c>
-      <c r="E566" t="inlineStr"/>
+          <t>LOMBO SUINO FRESCO KG</t>
+        </is>
+      </c>
+      <c r="E566" t="n">
+        <v>19.99</v>
+      </c>
     </row>
     <row r="567">
       <c r="A567" t="n">
-        <v>113301</v>
+        <v>258810</v>
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>#08 BAZAR</t>
+          <t>#06 AÇOUGUE - SUINO</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>GARRAFAO TERMICO TERMOLAR 5LT VERMELHO</t>
+          <t>SUINO - PANCETA KG</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARRAFAO TERMICO TERMOLAR 5L VERMELHO </t>
+          <t>PANCETA SUINA KG</t>
         </is>
       </c>
       <c r="E567" t="inlineStr"/>
     </row>
     <row r="568">
       <c r="A568" t="n">
-        <v>171272</v>
+        <v>106052</v>
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>#08 BAZAR</t>
+          <t>#06 AÇOUGUE - SUINO</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>PANELA DE PRESSAO PANELUX EMB AZ</t>
+          <t>SUINO - PELE SUINA FRESCA KG</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>PANELA DE PRESSAO PANELUX 4,5L</t>
-        </is>
-      </c>
-      <c r="E568" t="inlineStr"/>
+          <t>PELE SUINA KG</t>
+        </is>
+      </c>
+      <c r="E568" t="n">
+        <v>12.99</v>
+      </c>
     </row>
     <row r="569">
       <c r="A569" t="n">
-        <v>302448</v>
+        <v>106034</v>
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>#08 BAZAR</t>
+          <t>#06 AÇOUGUE - SUINO</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>PAPEL ALUMINIO VABENE 45CMX4M</t>
+          <t>SUINO - SUAN FRESCA KG</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>PAPEL ALUMINIO VABENE 45CM X 4M</t>
+          <t>SUAN SUINA KG</t>
         </is>
       </c>
       <c r="E569" t="inlineStr"/>
     </row>
     <row r="570">
       <c r="A570" t="n">
-        <v>121635</v>
+        <v>106032</v>
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>#08 BAZAR</t>
+          <t>#06 AÇOUGUE - SUINO</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>PAPEL TOALHA SCALA 2X1</t>
+          <t>SUINO - TOUCINHO FRESCO KG</t>
         </is>
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>PAPEL TOALHA SCALA 2UN</t>
-        </is>
-      </c>
-      <c r="E570" t="inlineStr"/>
+          <t>TOUCINHO FRESCO KG</t>
+        </is>
+      </c>
+      <c r="E570" t="n">
+        <v>18.99</v>
+      </c>
     </row>
     <row r="571">
       <c r="A571" t="n">
-        <v>229361</v>
+        <v>110086</v>
       </c>
       <c r="B571" t="inlineStr">
         <is>
@@ -12691,19 +12703,19 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>PRATO DESC RASO TOTAL PLAST 15CM</t>
+          <t>SUINO - SUAN FRESCA KG</t>
         </is>
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRATO DESCARTAVEL TOTAL PLASTICO 15CM RASO </t>
+          <t xml:space="preserve">COPO DESCARTAVEL TERMOPOT 180ML CRISTAL </t>
         </is>
       </c>
       <c r="E571" t="inlineStr"/>
     </row>
     <row r="572">
       <c r="A572" t="n">
-        <v>311249</v>
+        <v>114556</v>
       </c>
       <c r="B572" t="inlineStr">
         <is>
@@ -12712,157 +12724,145 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>SACO PLASTICO FREEZER E MICRO VABENE 5 L</t>
+          <t>GARRAFAO TERMICO TERMOLAR 5LT AZUL</t>
         </is>
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t xml:space="preserve">SACO PLASTICO VABENE 5L FREEZER E MICRO </t>
+          <t xml:space="preserve">GARRAFAO TERMICO TERMOLAR 5L AZUL </t>
         </is>
       </c>
       <c r="E572" t="inlineStr"/>
     </row>
     <row r="573">
       <c r="A573" t="n">
-        <v>104937</v>
+        <v>113301</v>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI</t>
+          <t>#08 BAZAR</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>ALHO A GRANEL KG</t>
+          <t>GARRAFAO TERMICO TERMOLAR 5LT VERMELHO</t>
         </is>
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>ALHO A GRANEL KG</t>
-        </is>
-      </c>
-      <c r="E573" t="n">
-        <v>31.99</v>
-      </c>
+          <t xml:space="preserve">GARRAFAO TERMICO TERMOLAR 5L VERMELHO </t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr"/>
     </row>
     <row r="574">
       <c r="A574" t="n">
-        <v>105023</v>
+        <v>171272</v>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI</t>
+          <t>#08 BAZAR</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>BANANA PRATA KG</t>
+          <t>PANELA DE PRESSAO PANELUX EMB AZ</t>
         </is>
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>BANANA PRATA KG</t>
-        </is>
-      </c>
-      <c r="E574" t="n">
-        <v>5.99</v>
-      </c>
+          <t>PANELA DE PRESSAO PANELUX 4,5L</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr"/>
     </row>
     <row r="575">
       <c r="A575" t="n">
-        <v>105010</v>
+        <v>302448</v>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI</t>
+          <t>#08 BAZAR</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>BATATA MONALISA KG</t>
+          <t>PAPEL ALUMINIO VABENE 45CMX4M</t>
         </is>
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>BATATA MONALISA KG</t>
-        </is>
-      </c>
-      <c r="E575" t="n">
-        <v>4.89</v>
-      </c>
+          <t>PAPEL ALUMINIO VABENE 45CM X 4M</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr"/>
     </row>
     <row r="576">
       <c r="A576" t="n">
-        <v>105001</v>
+        <v>121635</v>
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI</t>
+          <t>#08 BAZAR</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>BETERRABA KG</t>
+          <t>PAPEL TOALHA SCALA 2X1</t>
         </is>
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>BETERRABA KG</t>
-        </is>
-      </c>
-      <c r="E576" t="n">
-        <v>4.99</v>
-      </c>
+          <t>PAPEL TOALHA SCALA 2UN</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr"/>
     </row>
     <row r="577">
       <c r="A577" t="n">
-        <v>104919</v>
+        <v>229361</v>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI</t>
+          <t>#08 BAZAR</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>CEBOLA NACIONAL KG</t>
+          <t>PRATO DESC RASO TOTAL PLAST 15CM</t>
         </is>
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>CEBOLA NACIONAL KG</t>
-        </is>
-      </c>
-      <c r="E577" t="n">
-        <v>4.59</v>
-      </c>
+          <t xml:space="preserve">PRATO DESCARTAVEL TOTAL PLASTICO 15CM RASO </t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr"/>
     </row>
     <row r="578">
       <c r="A578" t="n">
-        <v>104862</v>
+        <v>311249</v>
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>#09 HORTIFRUTI</t>
+          <t>#08 BAZAR</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>CENOURA KG</t>
+          <t>SACO PLASTICO FREEZER E MICRO VABENE 5 L</t>
         </is>
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>CENOURA KG</t>
-        </is>
-      </c>
-      <c r="E578" t="n">
-        <v>4.99</v>
-      </c>
+          <t xml:space="preserve">SACO PLASTICO VABENE 5L FREEZER E MICRO </t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr"/>
     </row>
     <row r="579">
       <c r="A579" t="n">
-        <v>104931</v>
+        <v>104937</v>
       </c>
       <c r="B579" t="inlineStr">
         <is>
@@ -12871,21 +12871,21 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>LARANJA KG</t>
+          <t>ALHO A GRANEL KG</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>LARANJA KG</t>
+          <t>ALHO A GRANEL KG</t>
         </is>
       </c>
       <c r="E579" t="n">
-        <v>9.99</v>
+        <v>31.99</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="n">
-        <v>104944</v>
+        <v>105023</v>
       </c>
       <c r="B580" t="inlineStr">
         <is>
@@ -12894,21 +12894,21 @@
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>MACA NACIONAL KG</t>
+          <t>BANANA PRATA KG</t>
         </is>
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>MACA NACIONAL KG</t>
+          <t>BANANA PRATA KG</t>
         </is>
       </c>
       <c r="E580" t="n">
-        <v>11.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="n">
-        <v>104928</v>
+        <v>105010</v>
       </c>
       <c r="B581" t="inlineStr">
         <is>
@@ -12917,21 +12917,21 @@
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>MANGA PALMER KG</t>
+          <t>BATATA MONALISA KG</t>
         </is>
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>MANGA PALMER KG</t>
+          <t>BATATA MONALISA KG</t>
         </is>
       </c>
       <c r="E581" t="n">
-        <v>6.99</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="n">
-        <v>104947</v>
+        <v>105001</v>
       </c>
       <c r="B582" t="inlineStr">
         <is>
@@ -12940,21 +12940,21 @@
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>MELANCIA INTEIRA KG</t>
+          <t>BETERRABA KG</t>
         </is>
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>MELANCIA INTEIRA KG</t>
+          <t>BETERRABA KG</t>
         </is>
       </c>
       <c r="E582" t="n">
-        <v>2.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="n">
-        <v>104996</v>
+        <v>104919</v>
       </c>
       <c r="B583" t="inlineStr">
         <is>
@@ -12963,21 +12963,21 @@
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>MELAO AMARELO KG</t>
+          <t>CEBOLA NACIONAL KG</t>
         </is>
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>MELAO AMARELO KG</t>
+          <t>CEBOLA NACIONAL KG</t>
         </is>
       </c>
       <c r="E583" t="n">
-        <v>7.19</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="n">
-        <v>239921</v>
+        <v>104862</v>
       </c>
       <c r="B584" t="inlineStr">
         <is>
@@ -12986,21 +12986,21 @@
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>OVOS BRANCOS CARTELA 30 UNID</t>
+          <t>CENOURA KG</t>
         </is>
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>OVOS DE GRANJA BDJ 30UN BRANCOS</t>
+          <t>CENOURA KG</t>
         </is>
       </c>
       <c r="E584" t="n">
-        <v>23.7</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="n">
-        <v>104992</v>
+        <v>104931</v>
       </c>
       <c r="B585" t="inlineStr">
         <is>
@@ -13009,21 +13009,21 @@
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>REPOLHO VERDE KG</t>
+          <t>LARANJA KG</t>
         </is>
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>REPOLHO VERDE KG</t>
+          <t>LARANJA KG</t>
         </is>
       </c>
       <c r="E585" t="n">
-        <v>3.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="n">
-        <v>104961</v>
+        <v>104944</v>
       </c>
       <c r="B586" t="inlineStr">
         <is>
@@ -13032,38 +13032,176 @@
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>TOMATE CARMEM KG</t>
+          <t>MACA NACIONAL KG</t>
         </is>
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>TOMATE CARMEM KG</t>
+          <t>MACA NACIONAL KG</t>
         </is>
       </c>
       <c r="E586" t="n">
-        <v>7.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="n">
+        <v>104928</v>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>MANGA PALMER KG</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>MANGA PALMER KG</t>
+        </is>
+      </c>
+      <c r="E587" t="n">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="n">
+        <v>104947</v>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>MELANCIA INTEIRA KG</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>MELANCIA INTEIRA KG</t>
+        </is>
+      </c>
+      <c r="E588" t="n">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="n">
+        <v>104996</v>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>MELAO AMARELO KG</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>MELAO AMARELO KG</t>
+        </is>
+      </c>
+      <c r="E589" t="n">
+        <v>7.19</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="n">
+        <v>239921</v>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>OVOS BRANCOS CARTELA 30 UNID</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>OVOS DE GRANJA BDJ 30UN BRANCOS</t>
+        </is>
+      </c>
+      <c r="E590" t="n">
+        <v>23.7</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="n">
+        <v>104992</v>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>REPOLHO VERDE KG</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>REPOLHO VERDE KG</t>
+        </is>
+      </c>
+      <c r="E591" t="n">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="n">
+        <v>104961</v>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>TOMATE CARMEM KG</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>TOMATE CARMEM KG</t>
+        </is>
+      </c>
+      <c r="E592" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="n">
         <v>104863</v>
       </c>
-      <c r="B587" t="inlineStr">
+      <c r="B593" t="inlineStr">
         <is>
           <t>#09 HORTIFRUTI</t>
         </is>
       </c>
-      <c r="C587" t="inlineStr">
+      <c r="C593" t="inlineStr">
         <is>
           <t>TOMATE SALADETE KG</t>
         </is>
       </c>
-      <c r="D587" t="inlineStr">
+      <c r="D593" t="inlineStr">
         <is>
           <t>TOMATE SALADETE KG</t>
         </is>
       </c>
-      <c r="E587" t="n">
+      <c r="E593" t="n">
         <v>9.49</v>
       </c>
     </row>

--- a/dados_produtos_corrigidos.xlsx
+++ b/dados_produtos_corrigidos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E593"/>
+  <dimension ref="A1:E595"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13205,6 +13205,52 @@
         <v>9.49</v>
       </c>
     </row>
+    <row r="594">
+      <c r="A594" t="n">
+        <v>104855</v>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>LIMAO TAITI KG</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>LIMAO TAITI KG</t>
+        </is>
+      </c>
+      <c r="E594" t="n">
+        <v>4.69</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="n">
+        <v>104962</v>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>MARACUJA AZEDO</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>MARACUJA AZEDO KG</t>
+        </is>
+      </c>
+      <c r="E595" t="n">
+        <v>4.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dados_produtos_corrigidos.xlsx
+++ b/dados_produtos_corrigidos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E593"/>
+  <dimension ref="A1:E595"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13205,6 +13205,52 @@
         <v>9.49</v>
       </c>
     </row>
+    <row r="594">
+      <c r="A594" t="n">
+        <v>249597</v>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - CERVEJA</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>CERV HEINEKEN ZERO ALCOOL 330ML UNID</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CERVEJA HEINEKEN 330ML ZERO ALCOOL </t>
+        </is>
+      </c>
+      <c r="E594" t="n">
+        <v>6.79</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="n">
+        <v>150356</v>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>SABAO LIQUIDO OMO 3L MULTIACAO</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>SABÃO LIQUIDO OMO 3L MULTIACAO</t>
+        </is>
+      </c>
+      <c r="E595" t="n">
+        <v>40.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dados_produtos_corrigidos.xlsx
+++ b/dados_produtos_corrigidos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E620"/>
+  <dimension ref="A1:E627"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13822,6 +13822,167 @@
         <v>9.49</v>
       </c>
     </row>
+    <row r="621">
+      <c r="A621" t="n">
+        <v>107799</v>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - DESTILADOS</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>BEB RAIZES AMARGAS DE RACA 880ML</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>BEBIDA RAIZES AMARGAS DE RACA 880ML</t>
+        </is>
+      </c>
+      <c r="E621" t="n">
+        <v>10.99</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="n">
+        <v>115855</v>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>CAFE 3CORACOES EXTRAFORTE 250G</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>CAFÉ 3 CORAÇÕES 250G EXTRAFORTE</t>
+        </is>
+      </c>
+      <c r="E622" t="n">
+        <v>15.89</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="n">
+        <v>166152</v>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>FLOCAO MILHO SUPER FLOCAO CORINGA 500GR</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>FLOCÃO DE MILHO CORINGA 500G SUPER FLOCÃO</t>
+        </is>
+      </c>
+      <c r="E623" t="n">
+        <v>3.29</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="n">
+        <v>108415</v>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>MAC CRISTAL 500G SEMOLA PARAFUSO</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>MACARRÃO CRISTAL 500G SEMOLA PARAFUSO</t>
+        </is>
+      </c>
+      <c r="E624" t="n">
+        <v>3.89</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="n">
+        <v>313828</v>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>MASSA TAPIOCA AMAFIL MATUTO 500GR SEMI P</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>MASSA PARA TAPIOCA MATUTO 500G SEMI PRONTA</t>
+        </is>
+      </c>
+      <c r="E625" t="n">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="n">
+        <v>122984</v>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>REFRI SPRITE PET 2L</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>REFRIGERANTE SPRITE 2L</t>
+        </is>
+      </c>
+      <c r="E626" t="n">
+        <v>9.69</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="n">
+        <v>259589</v>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - CERVEJA</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>STELLA ARTOIS ONE WAY 600ML</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CERVEJA STELLA ARTOIS 600ML ONE WAY </t>
+        </is>
+      </c>
+      <c r="E627" t="n">
+        <v>10.59</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dados_produtos_corrigidos.xlsx
+++ b/dados_produtos_corrigidos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E627"/>
+  <dimension ref="A1:E644"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>FARINHA DE TRIGO MIRELLA 1KD SEM FERMENTO</t>
+          <t>FARINHA DE TRIGO MIRELLA 1KG SEM FERMENTO</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>SABÃO EM PÓ OMO CAIXA 890G LAVAGEM PERFEITA</t>
+          <t>SABÃO EM PÓ OMO CAIXA 800G LAVAGEM PERFEITA</t>
         </is>
       </c>
       <c r="E292" t="n">
@@ -10747,7 +10747,7 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>CERVEJA BUDWEISER 330ML LARGER LONG NECK</t>
+          <t>CERVEJA BUDWEISER LONG NECK 330ML LARGER</t>
         </is>
       </c>
       <c r="E480" t="inlineStr"/>
@@ -10768,7 +10768,7 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>CERVEJA BUDWEISER 330ML ZERO ALCOOL LONG NECK</t>
+          <t>CERVEJA BUDWEISER LONG NECK 330ML ZERO ALCOOL</t>
         </is>
       </c>
       <c r="E481" t="n">
@@ -10814,7 +10814,7 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 250ML LONG NECK LAGER</t>
+          <t>CERVEJA HEINEKEN LONG NECK 250ML LAGER</t>
         </is>
       </c>
       <c r="E483" t="n">
@@ -10927,7 +10927,7 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>CERVEJA SPATEN 600ML PURO MALTE LONG NECK</t>
+          <t>CERVEJA SPATEN LONG NECK 600ML PURO MALTE</t>
         </is>
       </c>
       <c r="E488" t="n">
@@ -13981,6 +13981,397 @@
       </c>
       <c r="E627" t="n">
         <v>10.59</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="n">
+        <v>318330</v>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>ACHOCOLATADO NESCAU 350GR EM PO</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>ACHOCOLATADO NESCAU 350G EM PO</t>
+        </is>
+      </c>
+      <c r="E628" t="n">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="n">
+        <v>315854</v>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>BISCOITO RENATA 360GR MAIZENA</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>BISCOITO RENATA 360G MAIZENA</t>
+        </is>
+      </c>
+      <c r="E629" t="n">
+        <v>4.39</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="n">
+        <v>168466</v>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - CERVEJA</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>CERV EISENBAHN L.NECK PILSEN 355ML</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CERVEJA EISENBAHN LONG NECK 355ML PILSEN </t>
+        </is>
+      </c>
+      <c r="E630" t="n">
+        <v>6.19</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="n">
+        <v>253879</v>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>ENERG BALY MACA VERDE LATA 250ML</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>ENERGETICO BALY LATA 250ML MAÇÃ VERDE</t>
+        </is>
+      </c>
+      <c r="E631" t="n">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="n">
+        <v>244425</v>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>ENERG.BALY FRUTAS TROPICAIS LATA 250ML</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>ENERGETICO BALY LATA 250ML FRUTAS TROPICAIS</t>
+        </is>
+      </c>
+      <c r="E632" t="n">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="n">
+        <v>244427</v>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>ENERG.BALY MELANCIA LATA 250ML</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ENERGETICO BALY LATA 250ML MELANCIA </t>
+        </is>
+      </c>
+      <c r="E633" t="n">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="n">
+        <v>318892</v>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>ENERGETICO BALY 250ML ABACAXI  C/ HORTEL</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>ENERGETICO BALY LATA 250ML ABACAXI  COM HORTELÃ</t>
+        </is>
+      </c>
+      <c r="E634" t="n">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="n">
+        <v>244422</v>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>ENERGETICO BALY 250ML COCO E ACAI</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>ENERGETICO BALY LATA 250ML COCO E ACAI</t>
+        </is>
+      </c>
+      <c r="E635" t="n">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="n">
+        <v>312640</v>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>ENERGETICO BALY 250ML COLA</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>ENERGETICO BALY LATA 250ML COLA</t>
+        </is>
+      </c>
+      <c r="E636" t="n">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="n">
+        <v>303516</v>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>ENERGETICO BALY 250ML FLYNOW S/ACUCAR</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>ENERGETICO BALY LATA 250ML FLYNOW SEM ACUCAR</t>
+        </is>
+      </c>
+      <c r="E637" t="n">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="n">
+        <v>312067</v>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>ENERGETICO BALY 250ML FRUTAS VERMELHAS</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>ENERGETICO BALY LATA 250ML FRUTAS VERMELHAS</t>
+        </is>
+      </c>
+      <c r="E638" t="n">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="n">
+        <v>302658</v>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>ENERGETICO BALY 250ML MORANGO E PESSEGO</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>ENERGETICO BALY LATA 250ML MORANGO E PESSEGO</t>
+        </is>
+      </c>
+      <c r="E639" t="n">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="n">
+        <v>302659</v>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>ENERGETICO BALY 250ML TANGERINA</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>ENERGETICO BALY LATA 250ML TANGERINA</t>
+        </is>
+      </c>
+      <c r="E640" t="n">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="n">
+        <v>312639</v>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>ENERGETICO BALY 250ML TROPICAL ZERO ACUC</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>ENERGETICO BALY LATA 250ML TROPICAL ZERO AÇUCAR</t>
+        </is>
+      </c>
+      <c r="E641" t="n">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="n">
+        <v>303517</v>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - #00 ENERGETICO</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>ENERGETICO BALY 250ML ZERO ACUCAR</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>ENERGETICO BALY LATA 250ML ZERO AÇUCAR</t>
+        </is>
+      </c>
+      <c r="E642" t="n">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="n">
+        <v>144572</v>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>POLVILHO DOCE LOPES 1KG</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t xml:space="preserve">POLVILHO LOPES 1KG DOCE </t>
+        </is>
+      </c>
+      <c r="E643" t="n">
+        <v>8.390000000000001</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="n">
+        <v>106008</v>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - SUINO</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>INGREDIENTES P/ FEIJOADA KG</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>INGREDIENTES PARA FEIJOADA KG</t>
+        </is>
+      </c>
+      <c r="E644" t="n">
+        <v>19.99</v>
       </c>
     </row>
   </sheetData>

--- a/dados_produtos_corrigidos.xlsx
+++ b/dados_produtos_corrigidos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E660"/>
+  <dimension ref="A1:E679"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14742,6 +14742,443 @@
         <v>17.99</v>
       </c>
     </row>
+    <row r="661">
+      <c r="A661" t="n">
+        <v>100709</v>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>AZEITE GALLO 500ML TIPO UNICO VIDRO</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>AZEITE DE OLIVA GALLO VIDRO 500ML TIPO UNICO</t>
+        </is>
+      </c>
+      <c r="E661" t="n">
+        <v>57.99</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="n">
+        <v>201454</v>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - DESTILADOS</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>WHISKY BALLANTINES FINEST 8 ANOS 750ML</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>WHISKY BALLANTINES FINEST 750ML 8 ANOS</t>
+        </is>
+      </c>
+      <c r="E662" t="n">
+        <v>85.98999999999999</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="n">
+        <v>105467</v>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - BOVINO</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>BOVINA - LINGUA KG</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>LINGUA BOVINA KG</t>
+        </is>
+      </c>
+      <c r="E663" t="n">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="n">
+        <v>157496</v>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - CERVEJA</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>CERVEJA HEINEKEN GARRAFA 600ML</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>CERVEJA HEINEKEN 600ML</t>
+        </is>
+      </c>
+      <c r="E664" t="n">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="n">
+        <v>259583</v>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>DESINFETANTE LAVABEM 2L ERVA DOCE</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>DESINFETANTE LAVABEM 2L ERVA DOCE</t>
+        </is>
+      </c>
+      <c r="E665" t="n">
+        <v>7.29</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="n">
+        <v>207624</v>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>DESINFETANTE LAVABEM 2LTS FLORAL</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>DESINFETANTE LAVABEM 2LTS FLORAL</t>
+        </is>
+      </c>
+      <c r="E666" t="n">
+        <v>7.29</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="n">
+        <v>207626</v>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>DESINFETANTE LAVABEM 2LTS JASMIN</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>DESINFETANTE LAVABEM 2LTS JASMIN</t>
+        </is>
+      </c>
+      <c r="E667" t="n">
+        <v>7.29</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="n">
+        <v>207628</v>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>DESINFETANTE LAVABEM 2LTS LAVANDA</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>DESINFETANTE LAVABEM 2LTS LAVANDA</t>
+        </is>
+      </c>
+      <c r="E668" t="n">
+        <v>7.29</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="n">
+        <v>207630</v>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>DESINFETANTE LAVABEM 2LTS LIMAO</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>DESINFETANTE LAVABEM 2LTS LIMAO</t>
+        </is>
+      </c>
+      <c r="E669" t="n">
+        <v>7.29</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="n">
+        <v>119826</v>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML CLEAR</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML CLEAR</t>
+        </is>
+      </c>
+      <c r="E670" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="n">
+        <v>111567</v>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML COCO</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML COCO</t>
+        </is>
+      </c>
+      <c r="E671" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="n">
+        <v>110352</v>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML LIMAO</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML LIMAO</t>
+        </is>
+      </c>
+      <c r="E672" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="n">
+        <v>110353</v>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML MACA</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML MACA</t>
+        </is>
+      </c>
+      <c r="E673" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="n">
+        <v>252617</v>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML MICELAR</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML MICELAR</t>
+        </is>
+      </c>
+      <c r="E674" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="n">
+        <v>106663</v>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML NEUTRO</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML NEUTRO</t>
+        </is>
+      </c>
+      <c r="E675" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="n">
+        <v>112163</v>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML. MARINE</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML MARINE</t>
+        </is>
+      </c>
+      <c r="E676" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="n">
+        <v>326954</v>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>SABAO BARRA REGENTE 5X200GR NEUTRO</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>SABÃO EM BARRA REGENTE 5X200G NEUTRO</t>
+        </is>
+      </c>
+      <c r="E677" t="n">
+        <v>10.39</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="n">
+        <v>264452</v>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - #00 SUCO</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>SUCO PRONTO DAFRUTA 1L NECTAR UVA</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>SUCO PRONTO DAFRUTA 1L NECTAR UVA</t>
+        </is>
+      </c>
+      <c r="E678" t="n">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="n">
+        <v>102087</v>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - DESTILADOS</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>VODKA SMIRNOFF 998ML TRIPLE DISTILLED</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>VODKA SMIRNOFF 998ML TRIPLE DISTILLED</t>
+        </is>
+      </c>
+      <c r="E679" t="n">
+        <v>54.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dados_produtos_corrigidos.xlsx
+++ b/dados_produtos_corrigidos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E679"/>
+  <dimension ref="A1:E695"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15179,6 +15179,374 @@
         <v>54.99</v>
       </c>
     </row>
+    <row r="680">
+      <c r="A680" t="n">
+        <v>298700</v>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - CERVEJA</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>CERVEJA AMSTEL 350ML LAGER SLEEK UNID</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>CERVEJA AMSTEL 350ML LAGER SLEEK</t>
+        </is>
+      </c>
+      <c r="E680" t="n">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="n">
+        <v>109002</v>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>#04 HIGIENE PESSOAL</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>CR DENTAL SORRISO DENTES BRANCO 180G DEN</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>CREME DENTAL SORRISO 180G DENTES BRANCOS</t>
+        </is>
+      </c>
+      <c r="E681" t="n">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="n">
+        <v>101085</v>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>LEITE CONDENSADO MOCOCA 395GR. TP</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>LEITE CONDENSADO MOCOCA 395G</t>
+        </is>
+      </c>
+      <c r="E682" t="n">
+        <v>8.49</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="n">
+        <v>134749</v>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>MILHO VERDE OLE 170GR LT</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>MILHO VERDE OLE LATA 170G</t>
+        </is>
+      </c>
+      <c r="E683" t="n">
+        <v>3.79</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="n">
+        <v>167128</v>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>#01 MERCEARIA - #01 ALTO GIRO</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>OLEO SOJA REFINADO CONCORDIA 900ML</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>OLEO DE SOJA CONCORDIA 900ML</t>
+        </is>
+      </c>
+      <c r="E684" t="n">
+        <v>8.390000000000001</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="n">
+        <v>304108</v>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>#04 HIGIENE PESSOAL</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>PAPEL HIGIENICO LEBLON SOFT BLANC 12 ROL</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAPEL HIGIENICO LEBLON 12 X 20M SOFT BLANC </t>
+        </is>
+      </c>
+      <c r="E685" t="n">
+        <v>13.99</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="n">
+        <v>318358</v>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>POLVILHO DONA DE 1KG AZEDO</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>POLVILHO DONA DE 1KG AZEDO</t>
+        </is>
+      </c>
+      <c r="E686" t="n">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="n">
+        <v>238146</v>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>#04 HIGIENE PESSOAL</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>SABONETE FL YPE SV AGUA COCO ALEC 85G</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>SABONETE FLOR DE YPE 85G AGUA DE COCO ALECRIM</t>
+        </is>
+      </c>
+      <c r="E687" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="n">
+        <v>236972</v>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>#04 HIGIENE PESSOAL</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>SABONETE FLOR DE YPE FLOR LAR/DAMASC 85G</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SABONETE FLOR DE YPE 85G FLOR LARANJA DAMASCO </t>
+        </is>
+      </c>
+      <c r="E688" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="n">
+        <v>236971</v>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>#04 HIGIENE PESSOAL</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>SABONETE FLOR DE YPE FRESIA E PESSEGO 85</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SABONETE FLOR DE YPE 85G FRESIA E PESSEGO </t>
+        </is>
+      </c>
+      <c r="E689" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="n">
+        <v>236970</v>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>#04 HIGIENE PESSOAL</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>SABONETE FLOR DE YPE ROSAS BRANCAS AVELA</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>SABONETE FLOR DE YPE 85G ROSAS BRANCAS AVELA</t>
+        </is>
+      </c>
+      <c r="E690" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="n">
+        <v>235599</v>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>#04 HIGIENE PESSOAL</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>SABONETE FLOR YPE  GARDENIA ARGAN 85G</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>SABONETE FLOR DE YPE 85G  GARDENIA ARGAN</t>
+        </is>
+      </c>
+      <c r="E691" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="n">
+        <v>238147</v>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>#04 HIGIENE PESSOAL</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>SABONETE FLOR YPE FLOR BAUN AMENDOA 85G</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>SABONETE FLOR DE YPE 85G FLOR BAUNILHA AMENDOA</t>
+        </is>
+      </c>
+      <c r="E692" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="n">
+        <v>286325</v>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>SUCO DE UVA AURORA 1,5LT TINTO TP</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>SUCO DE UVA AURORA TP 1,5L TINTO</t>
+        </is>
+      </c>
+      <c r="E693" t="n">
+        <v>23.99</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="n">
+        <v>119927</v>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - AVE</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>FRANGO CONG AMERICANO KG</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>FRANGO AMERICANO KG</t>
+        </is>
+      </c>
+      <c r="E694" t="n">
+        <v>10.99</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="n">
+        <v>116251</v>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - EMBUTIDO</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>MORTADELA  SADIA FRANGO KG</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>MORTADELA SADIA DE FRANGO KG</t>
+        </is>
+      </c>
+      <c r="E695" t="n">
+        <v>10.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dados_produtos_corrigidos.xlsx
+++ b/dados_produtos_corrigidos.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2048" uniqueCount="1272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2063" uniqueCount="1281">
   <si>
     <t>ID Produto</t>
   </si>
@@ -2101,6 +2101,21 @@
     <t>WHISKY WHITE HORSE 1LT</t>
   </si>
   <si>
+    <t>BOVINO - CUPIM FATIADO TEMPERADO KG</t>
+  </si>
+  <si>
+    <t>BEB FIU FIU ABACAXI CORTELA 750ML</t>
+  </si>
+  <si>
+    <t>CERV BRAHMA DUPLO MALTE 350ML PAC C/12 U</t>
+  </si>
+  <si>
+    <t>CERVEJA STELLA ARTOIS 269ML C/8UN</t>
+  </si>
+  <si>
+    <t>MAMAO FORMOSA KG</t>
+  </si>
+  <si>
     <t>ABSORVENTE COTONBABY LADY 8UN SEM ABAS</t>
   </si>
   <si>
@@ -3830,6 +3845,18 @@
   </si>
   <si>
     <t>WHISKY WHITE HORSE 1L</t>
+  </si>
+  <si>
+    <t>CUPIM BOVINO KG FATIADO TEMPERADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEBIDAS FIU FIU 750ML ABACAXI CORTELA </t>
+  </si>
+  <si>
+    <t>CERVEJA BRAHMA 12 X 350ML DUPLO MALTE</t>
+  </si>
+  <si>
+    <t>CERVEJA STELLA ARTOIS 8 X 269ML</t>
   </si>
 </sst>
 </file>
@@ -4187,7 +4214,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E682"/>
+  <dimension ref="A1:E687"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -4218,7 +4245,7 @@
         <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="E2">
         <v>3.99</v>
@@ -4235,7 +4262,7 @@
         <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>696</v>
+        <v>701</v>
       </c>
       <c r="E3">
         <v>7.99</v>
@@ -4252,7 +4279,7 @@
         <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>697</v>
+        <v>702</v>
       </c>
       <c r="E4">
         <v>7.99</v>
@@ -4269,7 +4296,7 @@
         <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="E5">
         <v>13.99</v>
@@ -4286,7 +4313,7 @@
         <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -4300,7 +4327,7 @@
         <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>700</v>
+        <v>705</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -4345,7 +4372,7 @@
         <v>35</v>
       </c>
       <c r="D10" t="s">
-        <v>701</v>
+        <v>706</v>
       </c>
       <c r="E10">
         <v>11.99</v>
@@ -4362,7 +4389,7 @@
         <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>702</v>
+        <v>707</v>
       </c>
       <c r="E11">
         <v>8.19</v>
@@ -4379,7 +4406,7 @@
         <v>37</v>
       </c>
       <c r="D12" t="s">
-        <v>703</v>
+        <v>708</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -4427,7 +4454,7 @@
         <v>40</v>
       </c>
       <c r="D15" t="s">
-        <v>704</v>
+        <v>709</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -4441,7 +4468,7 @@
         <v>41</v>
       </c>
       <c r="D16" t="s">
-        <v>705</v>
+        <v>710</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -4472,7 +4499,7 @@
         <v>43</v>
       </c>
       <c r="D18" t="s">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="E18">
         <v>14.99</v>
@@ -4489,7 +4516,7 @@
         <v>44</v>
       </c>
       <c r="D19" t="s">
-        <v>707</v>
+        <v>712</v>
       </c>
       <c r="E19">
         <v>37.99</v>
@@ -4506,7 +4533,7 @@
         <v>45</v>
       </c>
       <c r="D20" t="s">
-        <v>708</v>
+        <v>713</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -4537,7 +4564,7 @@
         <v>47</v>
       </c>
       <c r="D22" t="s">
-        <v>709</v>
+        <v>714</v>
       </c>
       <c r="E22">
         <v>7.99</v>
@@ -4554,7 +4581,7 @@
         <v>48</v>
       </c>
       <c r="D23" t="s">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="E23">
         <v>7.99</v>
@@ -4571,7 +4598,7 @@
         <v>49</v>
       </c>
       <c r="D24" t="s">
-        <v>711</v>
+        <v>716</v>
       </c>
       <c r="E24">
         <v>17.99</v>
@@ -4588,7 +4615,7 @@
         <v>50</v>
       </c>
       <c r="D25" t="s">
-        <v>712</v>
+        <v>717</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -4602,7 +4629,7 @@
         <v>51</v>
       </c>
       <c r="D26" t="s">
-        <v>713</v>
+        <v>718</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -4616,7 +4643,7 @@
         <v>52</v>
       </c>
       <c r="D27" t="s">
-        <v>714</v>
+        <v>719</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -4630,7 +4657,7 @@
         <v>53</v>
       </c>
       <c r="D28" t="s">
-        <v>715</v>
+        <v>720</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -4644,7 +4671,7 @@
         <v>54</v>
       </c>
       <c r="D29" t="s">
-        <v>716</v>
+        <v>721</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -4658,7 +4685,7 @@
         <v>55</v>
       </c>
       <c r="D30" t="s">
-        <v>717</v>
+        <v>722</v>
       </c>
       <c r="E30">
         <v>11.99</v>
@@ -4675,7 +4702,7 @@
         <v>56</v>
       </c>
       <c r="D31" t="s">
-        <v>718</v>
+        <v>723</v>
       </c>
       <c r="E31">
         <v>11.99</v>
@@ -4692,7 +4719,7 @@
         <v>57</v>
       </c>
       <c r="D32" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="E32">
         <v>11.99</v>
@@ -4709,7 +4736,7 @@
         <v>58</v>
       </c>
       <c r="D33" t="s">
-        <v>720</v>
+        <v>725</v>
       </c>
       <c r="E33">
         <v>11.99</v>
@@ -4726,7 +4753,7 @@
         <v>59</v>
       </c>
       <c r="D34" t="s">
-        <v>721</v>
+        <v>726</v>
       </c>
       <c r="E34">
         <v>11.99</v>
@@ -4743,7 +4770,7 @@
         <v>60</v>
       </c>
       <c r="D35" t="s">
-        <v>722</v>
+        <v>727</v>
       </c>
       <c r="E35">
         <v>10.99</v>
@@ -4760,7 +4787,7 @@
         <v>61</v>
       </c>
       <c r="D36" t="s">
-        <v>723</v>
+        <v>728</v>
       </c>
       <c r="E36">
         <v>11.99</v>
@@ -4777,7 +4804,7 @@
         <v>62</v>
       </c>
       <c r="D37" t="s">
-        <v>724</v>
+        <v>729</v>
       </c>
       <c r="E37">
         <v>10.99</v>
@@ -4794,7 +4821,7 @@
         <v>63</v>
       </c>
       <c r="D38" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="E38">
         <v>26.99</v>
@@ -4811,7 +4838,7 @@
         <v>64</v>
       </c>
       <c r="D39" t="s">
-        <v>726</v>
+        <v>731</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -4825,7 +4852,7 @@
         <v>65</v>
       </c>
       <c r="D40" t="s">
-        <v>727</v>
+        <v>732</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -4839,7 +4866,7 @@
         <v>66</v>
       </c>
       <c r="D41" t="s">
-        <v>728</v>
+        <v>733</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -4853,7 +4880,7 @@
         <v>67</v>
       </c>
       <c r="D42" t="s">
-        <v>729</v>
+        <v>734</v>
       </c>
       <c r="E42">
         <v>30.99</v>
@@ -4870,7 +4897,7 @@
         <v>68</v>
       </c>
       <c r="D43" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
       <c r="E43">
         <v>22.99</v>
@@ -4887,7 +4914,7 @@
         <v>69</v>
       </c>
       <c r="D44" t="s">
-        <v>731</v>
+        <v>736</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -4901,7 +4928,7 @@
         <v>70</v>
       </c>
       <c r="D45" t="s">
-        <v>732</v>
+        <v>737</v>
       </c>
       <c r="E45">
         <v>31.99</v>
@@ -4918,7 +4945,7 @@
         <v>71</v>
       </c>
       <c r="D46" t="s">
-        <v>733</v>
+        <v>738</v>
       </c>
       <c r="E46">
         <v>27.99</v>
@@ -4935,7 +4962,7 @@
         <v>72</v>
       </c>
       <c r="D47" t="s">
-        <v>734</v>
+        <v>739</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -4949,7 +4976,7 @@
         <v>73</v>
       </c>
       <c r="D48" t="s">
-        <v>735</v>
+        <v>740</v>
       </c>
       <c r="E48">
         <v>23.99</v>
@@ -4966,7 +4993,7 @@
         <v>74</v>
       </c>
       <c r="D49" t="s">
-        <v>736</v>
+        <v>741</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -4980,7 +5007,7 @@
         <v>75</v>
       </c>
       <c r="D50" t="s">
-        <v>737</v>
+        <v>742</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -4994,7 +5021,7 @@
         <v>76</v>
       </c>
       <c r="D51" t="s">
-        <v>738</v>
+        <v>743</v>
       </c>
       <c r="E51">
         <v>32.99</v>
@@ -5011,7 +5038,7 @@
         <v>77</v>
       </c>
       <c r="D52" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="E52">
         <v>33.99</v>
@@ -5028,7 +5055,7 @@
         <v>78</v>
       </c>
       <c r="D53" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -5042,7 +5069,7 @@
         <v>79</v>
       </c>
       <c r="D54" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -5056,7 +5083,7 @@
         <v>80</v>
       </c>
       <c r="D55" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="E55">
         <v>57.99</v>
@@ -5073,7 +5100,7 @@
         <v>81</v>
       </c>
       <c r="D56" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -5087,7 +5114,7 @@
         <v>82</v>
       </c>
       <c r="D57" t="s">
-        <v>744</v>
+        <v>749</v>
       </c>
       <c r="E57">
         <v>12.99</v>
@@ -5104,7 +5131,7 @@
         <v>83</v>
       </c>
       <c r="D58" t="s">
-        <v>745</v>
+        <v>750</v>
       </c>
       <c r="E58">
         <v>7.99</v>
@@ -5121,7 +5148,7 @@
         <v>84</v>
       </c>
       <c r="D59" t="s">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="E59">
         <v>6.49</v>
@@ -5138,7 +5165,7 @@
         <v>85</v>
       </c>
       <c r="D60" t="s">
-        <v>747</v>
+        <v>752</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -5186,7 +5213,7 @@
         <v>88</v>
       </c>
       <c r="D63" t="s">
-        <v>748</v>
+        <v>753</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -5285,7 +5312,7 @@
         <v>94</v>
       </c>
       <c r="D69" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -5299,7 +5326,7 @@
         <v>95</v>
       </c>
       <c r="D70" t="s">
-        <v>750</v>
+        <v>755</v>
       </c>
       <c r="E70">
         <v>10.99</v>
@@ -5333,7 +5360,7 @@
         <v>97</v>
       </c>
       <c r="D72" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="E72">
         <v>7.79</v>
@@ -5350,7 +5377,7 @@
         <v>98</v>
       </c>
       <c r="D73" t="s">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="E73">
         <v>5.19</v>
@@ -5367,7 +5394,7 @@
         <v>99</v>
       </c>
       <c r="D74" t="s">
-        <v>753</v>
+        <v>758</v>
       </c>
       <c r="E74">
         <v>5.99</v>
@@ -5384,7 +5411,7 @@
         <v>100</v>
       </c>
       <c r="D75" t="s">
-        <v>754</v>
+        <v>759</v>
       </c>
       <c r="E75">
         <v>4.19</v>
@@ -5401,7 +5428,7 @@
         <v>101</v>
       </c>
       <c r="D76" t="s">
-        <v>755</v>
+        <v>760</v>
       </c>
       <c r="E76">
         <v>7.59</v>
@@ -5418,7 +5445,7 @@
         <v>102</v>
       </c>
       <c r="D77" t="s">
-        <v>756</v>
+        <v>761</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -5432,7 +5459,7 @@
         <v>103</v>
       </c>
       <c r="D78" t="s">
-        <v>757</v>
+        <v>762</v>
       </c>
       <c r="E78">
         <v>7.99</v>
@@ -5449,7 +5476,7 @@
         <v>104</v>
       </c>
       <c r="D79" t="s">
-        <v>758</v>
+        <v>763</v>
       </c>
       <c r="E79">
         <v>5.99</v>
@@ -5466,7 +5493,7 @@
         <v>105</v>
       </c>
       <c r="D80" t="s">
-        <v>759</v>
+        <v>764</v>
       </c>
       <c r="E80">
         <v>4.39</v>
@@ -5483,7 +5510,7 @@
         <v>106</v>
       </c>
       <c r="D81" t="s">
-        <v>760</v>
+        <v>765</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -5497,7 +5524,7 @@
         <v>107</v>
       </c>
       <c r="D82" t="s">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="E82">
         <v>14.99</v>
@@ -5514,7 +5541,7 @@
         <v>108</v>
       </c>
       <c r="D83" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="E83">
         <v>19.99</v>
@@ -5531,7 +5558,7 @@
         <v>109</v>
       </c>
       <c r="D84" t="s">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="E84">
         <v>20.99</v>
@@ -5548,7 +5575,7 @@
         <v>110</v>
       </c>
       <c r="D85" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -5562,7 +5589,7 @@
         <v>111</v>
       </c>
       <c r="D86" t="s">
-        <v>765</v>
+        <v>770</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -5576,7 +5603,7 @@
         <v>112</v>
       </c>
       <c r="D87" t="s">
-        <v>766</v>
+        <v>771</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -5590,7 +5617,7 @@
         <v>113</v>
       </c>
       <c r="D88" t="s">
-        <v>767</v>
+        <v>772</v>
       </c>
       <c r="E88">
         <v>21.99</v>
@@ -5607,7 +5634,7 @@
         <v>114</v>
       </c>
       <c r="D89" t="s">
-        <v>768</v>
+        <v>773</v>
       </c>
       <c r="E89">
         <v>15.99</v>
@@ -5624,7 +5651,7 @@
         <v>115</v>
       </c>
       <c r="D90" t="s">
-        <v>769</v>
+        <v>774</v>
       </c>
       <c r="E90">
         <v>14.99</v>
@@ -5641,7 +5668,7 @@
         <v>116</v>
       </c>
       <c r="D91" t="s">
-        <v>770</v>
+        <v>775</v>
       </c>
       <c r="E91">
         <v>15.99</v>
@@ -5658,7 +5685,7 @@
         <v>117</v>
       </c>
       <c r="D92" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="E92">
         <v>17.69</v>
@@ -5675,7 +5702,7 @@
         <v>118</v>
       </c>
       <c r="D93" t="s">
-        <v>772</v>
+        <v>777</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -5689,7 +5716,7 @@
         <v>119</v>
       </c>
       <c r="D94" t="s">
-        <v>773</v>
+        <v>778</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -5703,7 +5730,7 @@
         <v>120</v>
       </c>
       <c r="D95" t="s">
-        <v>774</v>
+        <v>779</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -5748,7 +5775,7 @@
         <v>123</v>
       </c>
       <c r="D98" t="s">
-        <v>775</v>
+        <v>780</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -5762,7 +5789,7 @@
         <v>124</v>
       </c>
       <c r="D99" t="s">
-        <v>776</v>
+        <v>781</v>
       </c>
       <c r="E99">
         <v>29.99</v>
@@ -5779,7 +5806,7 @@
         <v>125</v>
       </c>
       <c r="D100" t="s">
-        <v>777</v>
+        <v>782</v>
       </c>
       <c r="E100">
         <v>15.89</v>
@@ -5796,7 +5823,7 @@
         <v>126</v>
       </c>
       <c r="D101" t="s">
-        <v>778</v>
+        <v>783</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -5810,7 +5837,7 @@
         <v>127</v>
       </c>
       <c r="D102" t="s">
-        <v>779</v>
+        <v>784</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -5824,7 +5851,7 @@
         <v>128</v>
       </c>
       <c r="D103" t="s">
-        <v>780</v>
+        <v>785</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -5838,7 +5865,7 @@
         <v>129</v>
       </c>
       <c r="D104" t="s">
-        <v>781</v>
+        <v>786</v>
       </c>
       <c r="E104">
         <v>29.99</v>
@@ -5855,7 +5882,7 @@
         <v>130</v>
       </c>
       <c r="D105" t="s">
-        <v>782</v>
+        <v>787</v>
       </c>
       <c r="E105">
         <v>115.99</v>
@@ -5872,7 +5899,7 @@
         <v>131</v>
       </c>
       <c r="D106" t="s">
-        <v>783</v>
+        <v>788</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -5886,7 +5913,7 @@
         <v>132</v>
       </c>
       <c r="D107" t="s">
-        <v>784</v>
+        <v>789</v>
       </c>
       <c r="E107">
         <v>24.99</v>
@@ -5903,7 +5930,7 @@
         <v>133</v>
       </c>
       <c r="D108" t="s">
-        <v>785</v>
+        <v>790</v>
       </c>
       <c r="E108">
         <v>26.99</v>
@@ -5920,7 +5947,7 @@
         <v>134</v>
       </c>
       <c r="D109" t="s">
-        <v>786</v>
+        <v>791</v>
       </c>
       <c r="E109">
         <v>15.99</v>
@@ -5937,7 +5964,7 @@
         <v>135</v>
       </c>
       <c r="D110" t="s">
-        <v>787</v>
+        <v>792</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -5985,7 +6012,7 @@
         <v>138</v>
       </c>
       <c r="D113" t="s">
-        <v>788</v>
+        <v>793</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -5999,7 +6026,7 @@
         <v>139</v>
       </c>
       <c r="D114" t="s">
-        <v>789</v>
+        <v>794</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -6013,7 +6040,7 @@
         <v>140</v>
       </c>
       <c r="D115" t="s">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="E115">
         <v>4.09</v>
@@ -6030,7 +6057,7 @@
         <v>141</v>
       </c>
       <c r="D116" t="s">
-        <v>791</v>
+        <v>796</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -6044,7 +6071,7 @@
         <v>142</v>
       </c>
       <c r="D117" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="E117">
         <v>2.99</v>
@@ -6061,7 +6088,7 @@
         <v>143</v>
       </c>
       <c r="D118" t="s">
-        <v>793</v>
+        <v>798</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -6075,7 +6102,7 @@
         <v>144</v>
       </c>
       <c r="D119" t="s">
-        <v>794</v>
+        <v>799</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -6089,7 +6116,7 @@
         <v>145</v>
       </c>
       <c r="D120" t="s">
-        <v>795</v>
+        <v>800</v>
       </c>
       <c r="E120">
         <v>5.99</v>
@@ -6106,7 +6133,7 @@
         <v>146</v>
       </c>
       <c r="D121" t="s">
-        <v>796</v>
+        <v>801</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -6120,7 +6147,7 @@
         <v>147</v>
       </c>
       <c r="D122" t="s">
-        <v>797</v>
+        <v>802</v>
       </c>
       <c r="E122">
         <v>2.69</v>
@@ -6137,7 +6164,7 @@
         <v>148</v>
       </c>
       <c r="D123" t="s">
-        <v>798</v>
+        <v>803</v>
       </c>
       <c r="E123">
         <v>6.19</v>
@@ -6154,7 +6181,7 @@
         <v>149</v>
       </c>
       <c r="D124" t="s">
-        <v>799</v>
+        <v>804</v>
       </c>
       <c r="E124">
         <v>5.99</v>
@@ -6171,7 +6198,7 @@
         <v>150</v>
       </c>
       <c r="D125" t="s">
-        <v>800</v>
+        <v>805</v>
       </c>
       <c r="E125">
         <v>6.19</v>
@@ -6188,7 +6215,7 @@
         <v>151</v>
       </c>
       <c r="D126" t="s">
-        <v>801</v>
+        <v>806</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -6202,7 +6229,7 @@
         <v>152</v>
       </c>
       <c r="D127" t="s">
-        <v>802</v>
+        <v>807</v>
       </c>
       <c r="E127">
         <v>6.79</v>
@@ -6219,7 +6246,7 @@
         <v>153</v>
       </c>
       <c r="D128" t="s">
-        <v>803</v>
+        <v>808</v>
       </c>
       <c r="E128">
         <v>6.19</v>
@@ -6236,7 +6263,7 @@
         <v>154</v>
       </c>
       <c r="D129" t="s">
-        <v>804</v>
+        <v>809</v>
       </c>
       <c r="E129">
         <v>6.19</v>
@@ -6253,7 +6280,7 @@
         <v>155</v>
       </c>
       <c r="D130" t="s">
-        <v>805</v>
+        <v>810</v>
       </c>
       <c r="E130">
         <v>6.99</v>
@@ -6270,7 +6297,7 @@
         <v>156</v>
       </c>
       <c r="D131" t="s">
-        <v>806</v>
+        <v>811</v>
       </c>
       <c r="E131">
         <v>11.99</v>
@@ -6287,7 +6314,7 @@
         <v>157</v>
       </c>
       <c r="D132" t="s">
-        <v>807</v>
+        <v>812</v>
       </c>
       <c r="E132">
         <v>4.59</v>
@@ -6304,7 +6331,7 @@
         <v>158</v>
       </c>
       <c r="D133" t="s">
-        <v>808</v>
+        <v>813</v>
       </c>
       <c r="E133">
         <v>5.69</v>
@@ -6321,7 +6348,7 @@
         <v>159</v>
       </c>
       <c r="D134" t="s">
-        <v>809</v>
+        <v>814</v>
       </c>
       <c r="E134">
         <v>44.89</v>
@@ -6338,7 +6365,7 @@
         <v>160</v>
       </c>
       <c r="D135" t="s">
-        <v>810</v>
+        <v>815</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -6352,7 +6379,7 @@
         <v>161</v>
       </c>
       <c r="D136" t="s">
-        <v>811</v>
+        <v>816</v>
       </c>
       <c r="E136">
         <v>4.79</v>
@@ -6369,7 +6396,7 @@
         <v>162</v>
       </c>
       <c r="D137" t="s">
-        <v>812</v>
+        <v>817</v>
       </c>
       <c r="E137">
         <v>9.49</v>
@@ -6386,7 +6413,7 @@
         <v>163</v>
       </c>
       <c r="D138" t="s">
-        <v>813</v>
+        <v>818</v>
       </c>
       <c r="E138">
         <v>10.59</v>
@@ -6403,7 +6430,7 @@
         <v>164</v>
       </c>
       <c r="D139" t="s">
-        <v>814</v>
+        <v>819</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -6417,7 +6444,7 @@
         <v>165</v>
       </c>
       <c r="D140" t="s">
-        <v>815</v>
+        <v>820</v>
       </c>
     </row>
     <row r="141" spans="1:5">
@@ -6431,7 +6458,7 @@
         <v>166</v>
       </c>
       <c r="D141" t="s">
-        <v>816</v>
+        <v>821</v>
       </c>
     </row>
     <row r="142" spans="1:5">
@@ -6445,7 +6472,7 @@
         <v>167</v>
       </c>
       <c r="D142" t="s">
-        <v>817</v>
+        <v>822</v>
       </c>
     </row>
     <row r="143" spans="1:5">
@@ -6459,7 +6486,7 @@
         <v>168</v>
       </c>
       <c r="D143" t="s">
-        <v>818</v>
+        <v>823</v>
       </c>
     </row>
     <row r="144" spans="1:5">
@@ -6473,7 +6500,7 @@
         <v>169</v>
       </c>
       <c r="D144" t="s">
-        <v>819</v>
+        <v>824</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -6487,7 +6514,7 @@
         <v>170</v>
       </c>
       <c r="D145" t="s">
-        <v>820</v>
+        <v>825</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -6501,7 +6528,7 @@
         <v>171</v>
       </c>
       <c r="D146" t="s">
-        <v>821</v>
+        <v>826</v>
       </c>
       <c r="E146">
         <v>36.99</v>
@@ -6518,7 +6545,7 @@
         <v>172</v>
       </c>
       <c r="D147" t="s">
-        <v>822</v>
+        <v>827</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -6532,7 +6559,7 @@
         <v>173</v>
       </c>
       <c r="D148" t="s">
-        <v>823</v>
+        <v>828</v>
       </c>
       <c r="E148">
         <v>11.99</v>
@@ -6549,7 +6576,7 @@
         <v>174</v>
       </c>
       <c r="D149" t="s">
-        <v>824</v>
+        <v>829</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -6563,7 +6590,7 @@
         <v>175</v>
       </c>
       <c r="D150" t="s">
-        <v>825</v>
+        <v>830</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -6594,7 +6621,7 @@
         <v>177</v>
       </c>
       <c r="D152" t="s">
-        <v>826</v>
+        <v>831</v>
       </c>
       <c r="E152">
         <v>19.99</v>
@@ -6611,7 +6638,7 @@
         <v>178</v>
       </c>
       <c r="D153" t="s">
-        <v>827</v>
+        <v>832</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -6625,7 +6652,7 @@
         <v>179</v>
       </c>
       <c r="D154" t="s">
-        <v>828</v>
+        <v>833</v>
       </c>
       <c r="E154">
         <v>15.99</v>
@@ -6642,7 +6669,7 @@
         <v>180</v>
       </c>
       <c r="D155" t="s">
-        <v>829</v>
+        <v>834</v>
       </c>
       <c r="E155">
         <v>15.99</v>
@@ -6659,7 +6686,7 @@
         <v>181</v>
       </c>
       <c r="D156" t="s">
-        <v>830</v>
+        <v>835</v>
       </c>
       <c r="E156">
         <v>31.99</v>
@@ -6676,7 +6703,7 @@
         <v>182</v>
       </c>
       <c r="D157" t="s">
-        <v>831</v>
+        <v>836</v>
       </c>
       <c r="E157">
         <v>36.99</v>
@@ -6693,7 +6720,7 @@
         <v>183</v>
       </c>
       <c r="D158" t="s">
-        <v>832</v>
+        <v>837</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -6707,7 +6734,7 @@
         <v>184</v>
       </c>
       <c r="D159" t="s">
-        <v>833</v>
+        <v>838</v>
       </c>
       <c r="E159">
         <v>18.99</v>
@@ -6724,7 +6751,7 @@
         <v>185</v>
       </c>
       <c r="D160" t="s">
-        <v>834</v>
+        <v>839</v>
       </c>
       <c r="E160">
         <v>3.49</v>
@@ -6741,7 +6768,7 @@
         <v>186</v>
       </c>
       <c r="D161" t="s">
-        <v>835</v>
+        <v>840</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -6755,7 +6782,7 @@
         <v>187</v>
       </c>
       <c r="D162" t="s">
-        <v>836</v>
+        <v>841</v>
       </c>
       <c r="E162">
         <v>4.69</v>
@@ -6772,7 +6799,7 @@
         <v>188</v>
       </c>
       <c r="D163" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -6786,7 +6813,7 @@
         <v>189</v>
       </c>
       <c r="D164" t="s">
-        <v>838</v>
+        <v>843</v>
       </c>
     </row>
     <row r="165" spans="1:5">
@@ -6800,7 +6827,7 @@
         <v>190</v>
       </c>
       <c r="D165" t="s">
-        <v>839</v>
+        <v>844</v>
       </c>
     </row>
     <row r="166" spans="1:5">
@@ -6814,7 +6841,7 @@
         <v>191</v>
       </c>
       <c r="D166" t="s">
-        <v>840</v>
+        <v>845</v>
       </c>
     </row>
     <row r="167" spans="1:5">
@@ -6828,7 +6855,7 @@
         <v>192</v>
       </c>
       <c r="D167" t="s">
-        <v>841</v>
+        <v>846</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -6842,7 +6869,7 @@
         <v>193</v>
       </c>
       <c r="D168" t="s">
-        <v>842</v>
+        <v>847</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -6856,7 +6883,7 @@
         <v>194</v>
       </c>
       <c r="D169" t="s">
-        <v>843</v>
+        <v>848</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -6870,7 +6897,7 @@
         <v>195</v>
       </c>
       <c r="D170" t="s">
-        <v>844</v>
+        <v>849</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -6884,7 +6911,7 @@
         <v>196</v>
       </c>
       <c r="D171" t="s">
-        <v>845</v>
+        <v>850</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -6898,7 +6925,7 @@
         <v>197</v>
       </c>
       <c r="D172" t="s">
-        <v>846</v>
+        <v>851</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -6912,7 +6939,7 @@
         <v>198</v>
       </c>
       <c r="D173" t="s">
-        <v>847</v>
+        <v>852</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -6926,7 +6953,7 @@
         <v>199</v>
       </c>
       <c r="D174" t="s">
-        <v>848</v>
+        <v>853</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -6940,7 +6967,7 @@
         <v>200</v>
       </c>
       <c r="D175" t="s">
-        <v>849</v>
+        <v>854</v>
       </c>
     </row>
     <row r="176" spans="1:5">
@@ -6954,7 +6981,7 @@
         <v>201</v>
       </c>
       <c r="D176" t="s">
-        <v>850</v>
+        <v>855</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -6968,7 +6995,7 @@
         <v>202</v>
       </c>
       <c r="D177" t="s">
-        <v>851</v>
+        <v>856</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -6982,7 +7009,7 @@
         <v>203</v>
       </c>
       <c r="D178" t="s">
-        <v>852</v>
+        <v>857</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -6996,7 +7023,7 @@
         <v>204</v>
       </c>
       <c r="D179" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -7010,7 +7037,7 @@
         <v>205</v>
       </c>
       <c r="D180" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -7024,7 +7051,7 @@
         <v>206</v>
       </c>
       <c r="D181" t="s">
-        <v>855</v>
+        <v>860</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -7038,7 +7065,7 @@
         <v>207</v>
       </c>
       <c r="D182" t="s">
-        <v>856</v>
+        <v>861</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -7052,7 +7079,7 @@
         <v>208</v>
       </c>
       <c r="D183" t="s">
-        <v>857</v>
+        <v>862</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -7066,7 +7093,7 @@
         <v>209</v>
       </c>
       <c r="D184" t="s">
-        <v>858</v>
+        <v>863</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -7080,7 +7107,7 @@
         <v>210</v>
       </c>
       <c r="D185" t="s">
-        <v>859</v>
+        <v>864</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -7094,7 +7121,7 @@
         <v>211</v>
       </c>
       <c r="D186" t="s">
-        <v>860</v>
+        <v>865</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -7108,7 +7135,7 @@
         <v>212</v>
       </c>
       <c r="D187" t="s">
-        <v>861</v>
+        <v>866</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -7122,7 +7149,7 @@
         <v>213</v>
       </c>
       <c r="D188" t="s">
-        <v>862</v>
+        <v>867</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -7136,7 +7163,7 @@
         <v>214</v>
       </c>
       <c r="D189" t="s">
-        <v>863</v>
+        <v>868</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -7150,7 +7177,7 @@
         <v>215</v>
       </c>
       <c r="D190" t="s">
-        <v>864</v>
+        <v>869</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -7164,7 +7191,7 @@
         <v>216</v>
       </c>
       <c r="D191" t="s">
-        <v>865</v>
+        <v>870</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -7178,7 +7205,7 @@
         <v>217</v>
       </c>
       <c r="D192" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -7192,7 +7219,7 @@
         <v>218</v>
       </c>
       <c r="D193" t="s">
-        <v>867</v>
+        <v>872</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -7220,7 +7247,7 @@
         <v>220</v>
       </c>
       <c r="D195" t="s">
-        <v>868</v>
+        <v>873</v>
       </c>
     </row>
     <row r="196" spans="1:5">
@@ -7234,7 +7261,7 @@
         <v>221</v>
       </c>
       <c r="D196" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
     </row>
     <row r="197" spans="1:5">
@@ -7248,7 +7275,7 @@
         <v>222</v>
       </c>
       <c r="D197" t="s">
-        <v>870</v>
+        <v>875</v>
       </c>
     </row>
     <row r="198" spans="1:5">
@@ -7290,7 +7317,7 @@
         <v>225</v>
       </c>
       <c r="D200" t="s">
-        <v>871</v>
+        <v>876</v>
       </c>
     </row>
     <row r="201" spans="1:5">
@@ -7304,7 +7331,7 @@
         <v>226</v>
       </c>
       <c r="D201" t="s">
-        <v>872</v>
+        <v>877</v>
       </c>
       <c r="E201">
         <v>37.99</v>
@@ -7321,7 +7348,7 @@
         <v>227</v>
       </c>
       <c r="D202" t="s">
-        <v>873</v>
+        <v>878</v>
       </c>
     </row>
     <row r="203" spans="1:5">
@@ -7335,7 +7362,7 @@
         <v>228</v>
       </c>
       <c r="D203" t="s">
-        <v>874</v>
+        <v>879</v>
       </c>
       <c r="E203">
         <v>2.49</v>
@@ -7352,7 +7379,7 @@
         <v>229</v>
       </c>
       <c r="D204" t="s">
-        <v>875</v>
+        <v>880</v>
       </c>
     </row>
     <row r="205" spans="1:5">
@@ -7366,7 +7393,7 @@
         <v>230</v>
       </c>
       <c r="D205" t="s">
-        <v>876</v>
+        <v>881</v>
       </c>
     </row>
     <row r="206" spans="1:5">
@@ -7647,7 +7674,7 @@
         <v>249</v>
       </c>
       <c r="D224" t="s">
-        <v>877</v>
+        <v>882</v>
       </c>
       <c r="E224">
         <v>12.99</v>
@@ -7664,7 +7691,7 @@
         <v>250</v>
       </c>
       <c r="D225" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="E225">
         <v>12.99</v>
@@ -7681,7 +7708,7 @@
         <v>251</v>
       </c>
       <c r="D226" t="s">
-        <v>879</v>
+        <v>884</v>
       </c>
       <c r="E226">
         <v>12.99</v>
@@ -7698,7 +7725,7 @@
         <v>252</v>
       </c>
       <c r="D227" t="s">
-        <v>880</v>
+        <v>885</v>
       </c>
       <c r="E227">
         <v>11.99</v>
@@ -7729,7 +7756,7 @@
         <v>254</v>
       </c>
       <c r="D229" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
     </row>
     <row r="230" spans="1:5">
@@ -7743,7 +7770,7 @@
         <v>255</v>
       </c>
       <c r="D230" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
     </row>
     <row r="231" spans="1:5">
@@ -7757,7 +7784,7 @@
         <v>256</v>
       </c>
       <c r="D231" t="s">
-        <v>883</v>
+        <v>888</v>
       </c>
     </row>
     <row r="232" spans="1:5">
@@ -7771,7 +7798,7 @@
         <v>257</v>
       </c>
       <c r="D232" t="s">
-        <v>884</v>
+        <v>889</v>
       </c>
     </row>
     <row r="233" spans="1:5">
@@ -7785,7 +7812,7 @@
         <v>258</v>
       </c>
       <c r="D233" t="s">
-        <v>885</v>
+        <v>890</v>
       </c>
     </row>
     <row r="234" spans="1:5">
@@ -7799,7 +7826,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>886</v>
+        <v>891</v>
       </c>
     </row>
     <row r="235" spans="1:5">
@@ -7813,7 +7840,7 @@
         <v>260</v>
       </c>
       <c r="D235" t="s">
-        <v>887</v>
+        <v>892</v>
       </c>
     </row>
     <row r="236" spans="1:5">
@@ -7827,7 +7854,7 @@
         <v>261</v>
       </c>
       <c r="D236" t="s">
-        <v>888</v>
+        <v>893</v>
       </c>
     </row>
     <row r="237" spans="1:5">
@@ -7841,7 +7868,7 @@
         <v>262</v>
       </c>
       <c r="D237" t="s">
-        <v>889</v>
+        <v>894</v>
       </c>
     </row>
     <row r="238" spans="1:5">
@@ -7855,7 +7882,7 @@
         <v>263</v>
       </c>
       <c r="D238" t="s">
-        <v>890</v>
+        <v>895</v>
       </c>
     </row>
     <row r="239" spans="1:5">
@@ -7869,7 +7896,7 @@
         <v>264</v>
       </c>
       <c r="D239" t="s">
-        <v>891</v>
+        <v>896</v>
       </c>
     </row>
     <row r="240" spans="1:5">
@@ -7883,7 +7910,7 @@
         <v>265</v>
       </c>
       <c r="D240" t="s">
-        <v>892</v>
+        <v>897</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -7897,7 +7924,7 @@
         <v>266</v>
       </c>
       <c r="D241" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -7911,7 +7938,7 @@
         <v>267</v>
       </c>
       <c r="D242" t="s">
-        <v>894</v>
+        <v>899</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -7925,7 +7952,7 @@
         <v>268</v>
       </c>
       <c r="D243" t="s">
-        <v>895</v>
+        <v>900</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -7939,7 +7966,7 @@
         <v>269</v>
       </c>
       <c r="D244" t="s">
-        <v>896</v>
+        <v>901</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -7953,7 +7980,7 @@
         <v>270</v>
       </c>
       <c r="D245" t="s">
-        <v>897</v>
+        <v>902</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -7967,7 +7994,7 @@
         <v>271</v>
       </c>
       <c r="D246" t="s">
-        <v>898</v>
+        <v>903</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -7981,7 +8008,7 @@
         <v>272</v>
       </c>
       <c r="D247" t="s">
-        <v>899</v>
+        <v>904</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -7995,7 +8022,7 @@
         <v>273</v>
       </c>
       <c r="D248" t="s">
-        <v>900</v>
+        <v>905</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -8009,7 +8036,7 @@
         <v>274</v>
       </c>
       <c r="D249" t="s">
-        <v>901</v>
+        <v>906</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -8023,7 +8050,7 @@
         <v>275</v>
       </c>
       <c r="D250" t="s">
-        <v>902</v>
+        <v>907</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -8037,7 +8064,7 @@
         <v>276</v>
       </c>
       <c r="D251" t="s">
-        <v>903</v>
+        <v>908</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -8051,7 +8078,7 @@
         <v>277</v>
       </c>
       <c r="D252" t="s">
-        <v>904</v>
+        <v>909</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -8065,7 +8092,7 @@
         <v>278</v>
       </c>
       <c r="D253" t="s">
-        <v>905</v>
+        <v>910</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -8079,7 +8106,7 @@
         <v>279</v>
       </c>
       <c r="D254" t="s">
-        <v>906</v>
+        <v>911</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -8093,7 +8120,7 @@
         <v>280</v>
       </c>
       <c r="D255" t="s">
-        <v>907</v>
+        <v>912</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -8107,7 +8134,7 @@
         <v>281</v>
       </c>
       <c r="D256" t="s">
-        <v>908</v>
+        <v>913</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -8121,7 +8148,7 @@
         <v>282</v>
       </c>
       <c r="D257" t="s">
-        <v>909</v>
+        <v>914</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -8135,7 +8162,7 @@
         <v>283</v>
       </c>
       <c r="D258" t="s">
-        <v>910</v>
+        <v>915</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -8149,7 +8176,7 @@
         <v>284</v>
       </c>
       <c r="D259" t="s">
-        <v>911</v>
+        <v>916</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -8163,7 +8190,7 @@
         <v>285</v>
       </c>
       <c r="D260" t="s">
-        <v>912</v>
+        <v>917</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -8177,7 +8204,7 @@
         <v>284</v>
       </c>
       <c r="D261" t="s">
-        <v>913</v>
+        <v>918</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -8191,7 +8218,7 @@
         <v>286</v>
       </c>
       <c r="D262" t="s">
-        <v>914</v>
+        <v>919</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -8205,7 +8232,7 @@
         <v>287</v>
       </c>
       <c r="D263" t="s">
-        <v>915</v>
+        <v>920</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -8219,7 +8246,7 @@
         <v>284</v>
       </c>
       <c r="D264" t="s">
-        <v>916</v>
+        <v>921</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -8233,7 +8260,7 @@
         <v>284</v>
       </c>
       <c r="D265" t="s">
-        <v>917</v>
+        <v>922</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -8247,7 +8274,7 @@
         <v>284</v>
       </c>
       <c r="D266" t="s">
-        <v>918</v>
+        <v>923</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -8261,7 +8288,7 @@
         <v>284</v>
       </c>
       <c r="D267" t="s">
-        <v>919</v>
+        <v>924</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -8275,7 +8302,7 @@
         <v>288</v>
       </c>
       <c r="D268" t="s">
-        <v>920</v>
+        <v>925</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -8289,7 +8316,7 @@
         <v>284</v>
       </c>
       <c r="D269" t="s">
-        <v>921</v>
+        <v>926</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -8539,7 +8566,7 @@
         <v>301</v>
       </c>
       <c r="D286" t="s">
-        <v>922</v>
+        <v>927</v>
       </c>
       <c r="E286">
         <v>2.69</v>
@@ -8688,7 +8715,7 @@
         <v>311</v>
       </c>
       <c r="D296" t="s">
-        <v>923</v>
+        <v>928</v>
       </c>
     </row>
     <row r="297" spans="1:5">
@@ -8702,7 +8729,7 @@
         <v>312</v>
       </c>
       <c r="D297" t="s">
-        <v>924</v>
+        <v>929</v>
       </c>
     </row>
     <row r="298" spans="1:5">
@@ -8716,7 +8743,7 @@
         <v>313</v>
       </c>
       <c r="D298" t="s">
-        <v>925</v>
+        <v>930</v>
       </c>
     </row>
     <row r="299" spans="1:5">
@@ -8730,7 +8757,7 @@
         <v>314</v>
       </c>
       <c r="D299" t="s">
-        <v>926</v>
+        <v>931</v>
       </c>
       <c r="E299">
         <v>15.99</v>
@@ -8747,7 +8774,7 @@
         <v>315</v>
       </c>
       <c r="D300" t="s">
-        <v>927</v>
+        <v>932</v>
       </c>
     </row>
     <row r="301" spans="1:5">
@@ -8761,7 +8788,7 @@
         <v>316</v>
       </c>
       <c r="D301" t="s">
-        <v>928</v>
+        <v>933</v>
       </c>
     </row>
     <row r="302" spans="1:5">
@@ -8775,7 +8802,7 @@
         <v>317</v>
       </c>
       <c r="D302" t="s">
-        <v>929</v>
+        <v>934</v>
       </c>
     </row>
     <row r="303" spans="1:5">
@@ -8789,7 +8816,7 @@
         <v>318</v>
       </c>
       <c r="D303" t="s">
-        <v>930</v>
+        <v>935</v>
       </c>
     </row>
     <row r="304" spans="1:5">
@@ -8803,7 +8830,7 @@
         <v>319</v>
       </c>
       <c r="D304" t="s">
-        <v>931</v>
+        <v>936</v>
       </c>
     </row>
     <row r="305" spans="1:5">
@@ -8817,7 +8844,7 @@
         <v>320</v>
       </c>
       <c r="D305" t="s">
-        <v>932</v>
+        <v>937</v>
       </c>
     </row>
     <row r="306" spans="1:5">
@@ -8831,7 +8858,7 @@
         <v>321</v>
       </c>
       <c r="D306" t="s">
-        <v>933</v>
+        <v>938</v>
       </c>
     </row>
     <row r="307" spans="1:5">
@@ -8845,7 +8872,7 @@
         <v>322</v>
       </c>
       <c r="D307" t="s">
-        <v>934</v>
+        <v>939</v>
       </c>
       <c r="E307">
         <v>4.99</v>
@@ -8862,7 +8889,7 @@
         <v>323</v>
       </c>
       <c r="D308" t="s">
-        <v>935</v>
+        <v>940</v>
       </c>
       <c r="E308">
         <v>4.99</v>
@@ -8879,7 +8906,7 @@
         <v>324</v>
       </c>
       <c r="D309" t="s">
-        <v>936</v>
+        <v>941</v>
       </c>
       <c r="E309">
         <v>4.99</v>
@@ -8896,7 +8923,7 @@
         <v>325</v>
       </c>
       <c r="D310" t="s">
-        <v>937</v>
+        <v>942</v>
       </c>
       <c r="E310">
         <v>4.99</v>
@@ -8913,7 +8940,7 @@
         <v>326</v>
       </c>
       <c r="D311" t="s">
-        <v>938</v>
+        <v>943</v>
       </c>
       <c r="E311">
         <v>4.99</v>
@@ -8930,7 +8957,7 @@
         <v>327</v>
       </c>
       <c r="D312" t="s">
-        <v>939</v>
+        <v>944</v>
       </c>
       <c r="E312">
         <v>4.99</v>
@@ -8947,7 +8974,7 @@
         <v>328</v>
       </c>
       <c r="D313" t="s">
-        <v>940</v>
+        <v>945</v>
       </c>
       <c r="E313">
         <v>4.99</v>
@@ -8964,7 +8991,7 @@
         <v>329</v>
       </c>
       <c r="D314" t="s">
-        <v>941</v>
+        <v>946</v>
       </c>
       <c r="E314">
         <v>4.99</v>
@@ -8981,7 +9008,7 @@
         <v>330</v>
       </c>
       <c r="D315" t="s">
-        <v>942</v>
+        <v>947</v>
       </c>
       <c r="E315">
         <v>4.99</v>
@@ -8998,7 +9025,7 @@
         <v>331</v>
       </c>
       <c r="D316" t="s">
-        <v>943</v>
+        <v>948</v>
       </c>
       <c r="E316">
         <v>4.99</v>
@@ -9015,7 +9042,7 @@
         <v>332</v>
       </c>
       <c r="D317" t="s">
-        <v>944</v>
+        <v>949</v>
       </c>
       <c r="E317">
         <v>4.99</v>
@@ -9032,7 +9059,7 @@
         <v>333</v>
       </c>
       <c r="D318" t="s">
-        <v>945</v>
+        <v>950</v>
       </c>
       <c r="E318">
         <v>4.99</v>
@@ -9049,7 +9076,7 @@
         <v>334</v>
       </c>
       <c r="D319" t="s">
-        <v>946</v>
+        <v>951</v>
       </c>
       <c r="E319">
         <v>8.49</v>
@@ -9083,7 +9110,7 @@
         <v>336</v>
       </c>
       <c r="D321" t="s">
-        <v>947</v>
+        <v>952</v>
       </c>
       <c r="E321">
         <v>8.49</v>
@@ -9100,7 +9127,7 @@
         <v>337</v>
       </c>
       <c r="D322" t="s">
-        <v>948</v>
+        <v>953</v>
       </c>
     </row>
     <row r="323" spans="1:5">
@@ -9114,7 +9141,7 @@
         <v>338</v>
       </c>
       <c r="D323" t="s">
-        <v>949</v>
+        <v>954</v>
       </c>
       <c r="E323">
         <v>8.69</v>
@@ -9131,7 +9158,7 @@
         <v>339</v>
       </c>
       <c r="D324" t="s">
-        <v>950</v>
+        <v>955</v>
       </c>
     </row>
     <row r="325" spans="1:5">
@@ -9145,7 +9172,7 @@
         <v>340</v>
       </c>
       <c r="D325" t="s">
-        <v>951</v>
+        <v>956</v>
       </c>
     </row>
     <row r="326" spans="1:5">
@@ -9159,7 +9186,7 @@
         <v>341</v>
       </c>
       <c r="D326" t="s">
-        <v>952</v>
+        <v>957</v>
       </c>
     </row>
     <row r="327" spans="1:5">
@@ -9173,7 +9200,7 @@
         <v>342</v>
       </c>
       <c r="D327" t="s">
-        <v>953</v>
+        <v>958</v>
       </c>
     </row>
     <row r="328" spans="1:5">
@@ -9187,7 +9214,7 @@
         <v>343</v>
       </c>
       <c r="D328" t="s">
-        <v>954</v>
+        <v>959</v>
       </c>
     </row>
     <row r="329" spans="1:5">
@@ -9201,7 +9228,7 @@
         <v>344</v>
       </c>
       <c r="D329" t="s">
-        <v>955</v>
+        <v>960</v>
       </c>
     </row>
     <row r="330" spans="1:5">
@@ -9215,7 +9242,7 @@
         <v>345</v>
       </c>
       <c r="D330" t="s">
-        <v>956</v>
+        <v>961</v>
       </c>
     </row>
     <row r="331" spans="1:5">
@@ -9229,7 +9256,7 @@
         <v>346</v>
       </c>
       <c r="D331" t="s">
-        <v>957</v>
+        <v>962</v>
       </c>
     </row>
     <row r="332" spans="1:5">
@@ -9243,7 +9270,7 @@
         <v>347</v>
       </c>
       <c r="D332" t="s">
-        <v>958</v>
+        <v>963</v>
       </c>
     </row>
     <row r="333" spans="1:5">
@@ -9257,7 +9284,7 @@
         <v>348</v>
       </c>
       <c r="D333" t="s">
-        <v>959</v>
+        <v>964</v>
       </c>
       <c r="E333">
         <v>7.99</v>
@@ -9274,7 +9301,7 @@
         <v>349</v>
       </c>
       <c r="D334" t="s">
-        <v>960</v>
+        <v>965</v>
       </c>
     </row>
     <row r="335" spans="1:5">
@@ -9288,7 +9315,7 @@
         <v>350</v>
       </c>
       <c r="D335" t="s">
-        <v>961</v>
+        <v>966</v>
       </c>
     </row>
     <row r="336" spans="1:5">
@@ -9302,7 +9329,7 @@
         <v>351</v>
       </c>
       <c r="D336" t="s">
-        <v>962</v>
+        <v>967</v>
       </c>
       <c r="E336">
         <v>5.99</v>
@@ -9319,7 +9346,7 @@
         <v>352</v>
       </c>
       <c r="D337" t="s">
-        <v>963</v>
+        <v>968</v>
       </c>
       <c r="E337">
         <v>5.29</v>
@@ -9336,7 +9363,7 @@
         <v>353</v>
       </c>
       <c r="D338" t="s">
-        <v>964</v>
+        <v>969</v>
       </c>
     </row>
     <row r="339" spans="1:5">
@@ -9350,7 +9377,7 @@
         <v>354</v>
       </c>
       <c r="D339" t="s">
-        <v>965</v>
+        <v>970</v>
       </c>
     </row>
     <row r="340" spans="1:5">
@@ -9364,7 +9391,7 @@
         <v>355</v>
       </c>
       <c r="D340" t="s">
-        <v>966</v>
+        <v>971</v>
       </c>
       <c r="E340">
         <v>4.99</v>
@@ -9412,7 +9439,7 @@
         <v>358</v>
       </c>
       <c r="D343" t="s">
-        <v>967</v>
+        <v>972</v>
       </c>
       <c r="E343">
         <v>6.19</v>
@@ -9429,7 +9456,7 @@
         <v>359</v>
       </c>
       <c r="D344" t="s">
-        <v>968</v>
+        <v>973</v>
       </c>
       <c r="E344">
         <v>8.69</v>
@@ -9446,7 +9473,7 @@
         <v>360</v>
       </c>
       <c r="D345" t="s">
-        <v>969</v>
+        <v>974</v>
       </c>
       <c r="E345">
         <v>5.99</v>
@@ -9463,7 +9490,7 @@
         <v>361</v>
       </c>
       <c r="D346" t="s">
-        <v>970</v>
+        <v>975</v>
       </c>
       <c r="E346">
         <v>5.99</v>
@@ -9480,7 +9507,7 @@
         <v>362</v>
       </c>
       <c r="D347" t="s">
-        <v>971</v>
+        <v>976</v>
       </c>
     </row>
     <row r="348" spans="1:5">
@@ -9494,7 +9521,7 @@
         <v>363</v>
       </c>
       <c r="D348" t="s">
-        <v>972</v>
+        <v>977</v>
       </c>
     </row>
     <row r="349" spans="1:5">
@@ -9508,7 +9535,7 @@
         <v>364</v>
       </c>
       <c r="D349" t="s">
-        <v>973</v>
+        <v>978</v>
       </c>
     </row>
     <row r="350" spans="1:5">
@@ -9522,7 +9549,7 @@
         <v>365</v>
       </c>
       <c r="D350" t="s">
-        <v>974</v>
+        <v>979</v>
       </c>
       <c r="E350">
         <v>8.69</v>
@@ -9539,7 +9566,7 @@
         <v>366</v>
       </c>
       <c r="D351" t="s">
-        <v>975</v>
+        <v>980</v>
       </c>
     </row>
     <row r="352" spans="1:5">
@@ -9553,7 +9580,7 @@
         <v>367</v>
       </c>
       <c r="D352" t="s">
-        <v>976</v>
+        <v>981</v>
       </c>
       <c r="E352">
         <v>12.99</v>
@@ -9570,7 +9597,7 @@
         <v>368</v>
       </c>
       <c r="D353" t="s">
-        <v>977</v>
+        <v>982</v>
       </c>
     </row>
     <row r="354" spans="1:5">
@@ -9584,7 +9611,7 @@
         <v>369</v>
       </c>
       <c r="D354" t="s">
-        <v>978</v>
+        <v>983</v>
       </c>
       <c r="E354">
         <v>35.99</v>
@@ -9601,7 +9628,7 @@
         <v>370</v>
       </c>
       <c r="D355" t="s">
-        <v>979</v>
+        <v>984</v>
       </c>
       <c r="E355">
         <v>44.99</v>
@@ -9618,7 +9645,7 @@
         <v>371</v>
       </c>
       <c r="D356" t="s">
-        <v>980</v>
+        <v>985</v>
       </c>
     </row>
     <row r="357" spans="1:5">
@@ -9632,7 +9659,7 @@
         <v>372</v>
       </c>
       <c r="D357" t="s">
-        <v>981</v>
+        <v>986</v>
       </c>
       <c r="E357">
         <v>48.99</v>
@@ -9649,7 +9676,7 @@
         <v>373</v>
       </c>
       <c r="D358" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="E358">
         <v>32.99</v>
@@ -9666,7 +9693,7 @@
         <v>374</v>
       </c>
       <c r="D359" t="s">
-        <v>983</v>
+        <v>988</v>
       </c>
       <c r="E359">
         <v>49.99</v>
@@ -9683,7 +9710,7 @@
         <v>375</v>
       </c>
       <c r="D360" t="s">
-        <v>984</v>
+        <v>989</v>
       </c>
     </row>
     <row r="361" spans="1:5">
@@ -9697,7 +9724,7 @@
         <v>376</v>
       </c>
       <c r="D361" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
     </row>
     <row r="362" spans="1:5">
@@ -9711,7 +9738,7 @@
         <v>377</v>
       </c>
       <c r="D362" t="s">
-        <v>986</v>
+        <v>991</v>
       </c>
     </row>
     <row r="363" spans="1:5">
@@ -9725,7 +9752,7 @@
         <v>378</v>
       </c>
       <c r="D363" t="s">
-        <v>987</v>
+        <v>992</v>
       </c>
       <c r="E363">
         <v>2.69</v>
@@ -9756,7 +9783,7 @@
         <v>380</v>
       </c>
       <c r="D365" t="s">
-        <v>988</v>
+        <v>993</v>
       </c>
       <c r="E365">
         <v>3.29</v>
@@ -9773,7 +9800,7 @@
         <v>381</v>
       </c>
       <c r="D366" t="s">
-        <v>989</v>
+        <v>994</v>
       </c>
       <c r="E366">
         <v>2.69</v>
@@ -9790,7 +9817,7 @@
         <v>382</v>
       </c>
       <c r="D367" t="s">
-        <v>990</v>
+        <v>995</v>
       </c>
       <c r="E367">
         <v>2.89</v>
@@ -9807,7 +9834,7 @@
         <v>383</v>
       </c>
       <c r="D368" t="s">
-        <v>991</v>
+        <v>996</v>
       </c>
     </row>
     <row r="369" spans="1:5">
@@ -9821,7 +9848,7 @@
         <v>384</v>
       </c>
       <c r="D369" t="s">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="E369">
         <v>11.99</v>
@@ -9838,7 +9865,7 @@
         <v>385</v>
       </c>
       <c r="D370" t="s">
-        <v>993</v>
+        <v>998</v>
       </c>
     </row>
     <row r="371" spans="1:5">
@@ -9852,7 +9879,7 @@
         <v>386</v>
       </c>
       <c r="D371" t="s">
-        <v>994</v>
+        <v>999</v>
       </c>
       <c r="E371">
         <v>10.99</v>
@@ -9869,7 +9896,7 @@
         <v>387</v>
       </c>
       <c r="D372" t="s">
-        <v>995</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="373" spans="1:5">
@@ -9883,7 +9910,7 @@
         <v>388</v>
       </c>
       <c r="D373" t="s">
-        <v>996</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="374" spans="1:5">
@@ -9897,7 +9924,7 @@
         <v>389</v>
       </c>
       <c r="D374" t="s">
-        <v>997</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="375" spans="1:5">
@@ -9911,7 +9938,7 @@
         <v>390</v>
       </c>
       <c r="D375" t="s">
-        <v>998</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="376" spans="1:5">
@@ -9925,7 +9952,7 @@
         <v>391</v>
       </c>
       <c r="D376" t="s">
-        <v>999</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="377" spans="1:5">
@@ -9939,7 +9966,7 @@
         <v>392</v>
       </c>
       <c r="D377" t="s">
-        <v>1000</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="378" spans="1:5">
@@ -9953,7 +9980,7 @@
         <v>392</v>
       </c>
       <c r="D378" t="s">
-        <v>1001</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="379" spans="1:5">
@@ -9967,7 +9994,7 @@
         <v>393</v>
       </c>
       <c r="D379" t="s">
-        <v>1002</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="380" spans="1:5">
@@ -9981,7 +10008,7 @@
         <v>394</v>
       </c>
       <c r="D380" t="s">
-        <v>1003</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="381" spans="1:5">
@@ -9995,7 +10022,7 @@
         <v>395</v>
       </c>
       <c r="D381" t="s">
-        <v>1004</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="382" spans="1:5">
@@ -10009,7 +10036,7 @@
         <v>396</v>
       </c>
       <c r="D382" t="s">
-        <v>1005</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="383" spans="1:5">
@@ -10023,7 +10050,7 @@
         <v>397</v>
       </c>
       <c r="D383" t="s">
-        <v>1006</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="384" spans="1:5">
@@ -10037,7 +10064,7 @@
         <v>397</v>
       </c>
       <c r="D384" t="s">
-        <v>1007</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="385" spans="1:5">
@@ -10051,7 +10078,7 @@
         <v>398</v>
       </c>
       <c r="D385" t="s">
-        <v>1008</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="386" spans="1:5">
@@ -10065,7 +10092,7 @@
         <v>399</v>
       </c>
       <c r="D386" t="s">
-        <v>1009</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="387" spans="1:5">
@@ -10079,7 +10106,7 @@
         <v>400</v>
       </c>
       <c r="D387" t="s">
-        <v>1010</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="388" spans="1:5">
@@ -10093,7 +10120,7 @@
         <v>401</v>
       </c>
       <c r="D388" t="s">
-        <v>1011</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="389" spans="1:5">
@@ -10107,7 +10134,7 @@
         <v>402</v>
       </c>
       <c r="D389" t="s">
-        <v>1012</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="390" spans="1:5">
@@ -10121,7 +10148,7 @@
         <v>403</v>
       </c>
       <c r="D390" t="s">
-        <v>1013</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="391" spans="1:5">
@@ -10163,7 +10190,7 @@
         <v>406</v>
       </c>
       <c r="D393" t="s">
-        <v>1014</v>
+        <v>1019</v>
       </c>
       <c r="E393">
         <v>19.99</v>
@@ -10180,7 +10207,7 @@
         <v>407</v>
       </c>
       <c r="D394" t="s">
-        <v>1015</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="395" spans="1:5">
@@ -10194,7 +10221,7 @@
         <v>408</v>
       </c>
       <c r="D395" t="s">
-        <v>1016</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="396" spans="1:5">
@@ -10208,7 +10235,7 @@
         <v>409</v>
       </c>
       <c r="D396" t="s">
-        <v>1017</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="397" spans="1:5">
@@ -10222,7 +10249,7 @@
         <v>410</v>
       </c>
       <c r="D397" t="s">
-        <v>1018</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="398" spans="1:5">
@@ -10236,7 +10263,7 @@
         <v>411</v>
       </c>
       <c r="D398" t="s">
-        <v>1019</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="399" spans="1:5">
@@ -10250,7 +10277,7 @@
         <v>412</v>
       </c>
       <c r="D399" t="s">
-        <v>1020</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="400" spans="1:5">
@@ -10264,7 +10291,7 @@
         <v>413</v>
       </c>
       <c r="D400" t="s">
-        <v>1021</v>
+        <v>1026</v>
       </c>
       <c r="E400">
         <v>65.98999999999999</v>
@@ -10281,7 +10308,7 @@
         <v>414</v>
       </c>
       <c r="D401" t="s">
-        <v>1022</v>
+        <v>1027</v>
       </c>
       <c r="E401">
         <v>65.98999999999999</v>
@@ -10298,7 +10325,7 @@
         <v>415</v>
       </c>
       <c r="D402" t="s">
-        <v>1023</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="403" spans="1:5">
@@ -10312,7 +10339,7 @@
         <v>416</v>
       </c>
       <c r="D403" t="s">
-        <v>1024</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="404" spans="1:5">
@@ -10326,7 +10353,7 @@
         <v>417</v>
       </c>
       <c r="D404" t="s">
-        <v>1025</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="405" spans="1:5">
@@ -10340,7 +10367,7 @@
         <v>418</v>
       </c>
       <c r="D405" t="s">
-        <v>1026</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="406" spans="1:5">
@@ -10354,7 +10381,7 @@
         <v>419</v>
       </c>
       <c r="D406" t="s">
-        <v>1027</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="407" spans="1:5">
@@ -10368,7 +10395,7 @@
         <v>420</v>
       </c>
       <c r="D407" t="s">
-        <v>1028</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="408" spans="1:5">
@@ -10382,7 +10409,7 @@
         <v>421</v>
       </c>
       <c r="D408" t="s">
-        <v>1029</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="409" spans="1:5">
@@ -10396,7 +10423,7 @@
         <v>422</v>
       </c>
       <c r="D409" t="s">
-        <v>1030</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="410" spans="1:5">
@@ -10410,7 +10437,7 @@
         <v>423</v>
       </c>
       <c r="D410" t="s">
-        <v>1031</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="411" spans="1:5">
@@ -10441,7 +10468,7 @@
         <v>425</v>
       </c>
       <c r="D412" t="s">
-        <v>1032</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="413" spans="1:5">
@@ -10455,7 +10482,7 @@
         <v>426</v>
       </c>
       <c r="D413" t="s">
-        <v>1033</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="414" spans="1:5">
@@ -10469,7 +10496,7 @@
         <v>427</v>
       </c>
       <c r="D414" t="s">
-        <v>1034</v>
+        <v>1039</v>
       </c>
       <c r="E414">
         <v>6.79</v>
@@ -10486,7 +10513,7 @@
         <v>428</v>
       </c>
       <c r="D415" t="s">
-        <v>1035</v>
+        <v>1040</v>
       </c>
       <c r="E415">
         <v>7.99</v>
@@ -10503,7 +10530,7 @@
         <v>429</v>
       </c>
       <c r="D416" t="s">
-        <v>1036</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="417" spans="1:5">
@@ -10517,7 +10544,7 @@
         <v>430</v>
       </c>
       <c r="D417" t="s">
-        <v>1037</v>
+        <v>1042</v>
       </c>
       <c r="E417">
         <v>6.99</v>
@@ -10534,7 +10561,7 @@
         <v>431</v>
       </c>
       <c r="D418" t="s">
-        <v>1038</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="419" spans="1:5">
@@ -10548,7 +10575,7 @@
         <v>432</v>
       </c>
       <c r="D419" t="s">
-        <v>1039</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="420" spans="1:5">
@@ -10562,7 +10589,7 @@
         <v>433</v>
       </c>
       <c r="D420" t="s">
-        <v>1040</v>
+        <v>1045</v>
       </c>
       <c r="E420">
         <v>38.99</v>
@@ -10579,7 +10606,7 @@
         <v>434</v>
       </c>
       <c r="D421" t="s">
-        <v>1041</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="422" spans="1:5">
@@ -10593,7 +10620,7 @@
         <v>435</v>
       </c>
       <c r="D422" t="s">
-        <v>1042</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="423" spans="1:5">
@@ -10607,7 +10634,7 @@
         <v>436</v>
       </c>
       <c r="D423" t="s">
-        <v>1043</v>
+        <v>1048</v>
       </c>
       <c r="E423">
         <v>6.69</v>
@@ -10624,7 +10651,7 @@
         <v>437</v>
       </c>
       <c r="D424" t="s">
-        <v>1044</v>
+        <v>1049</v>
       </c>
       <c r="E424">
         <v>6.79</v>
@@ -10641,7 +10668,7 @@
         <v>438</v>
       </c>
       <c r="D425" t="s">
-        <v>1045</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="426" spans="1:5">
@@ -10669,7 +10696,7 @@
         <v>440</v>
       </c>
       <c r="D427" t="s">
-        <v>1046</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="428" spans="1:5">
@@ -10683,7 +10710,7 @@
         <v>441</v>
       </c>
       <c r="D428" t="s">
-        <v>1047</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="429" spans="1:5">
@@ -10697,7 +10724,7 @@
         <v>442</v>
       </c>
       <c r="D429" t="s">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="E429">
         <v>5.99</v>
@@ -10714,7 +10741,7 @@
         <v>443</v>
       </c>
       <c r="D430" t="s">
-        <v>1049</v>
+        <v>1054</v>
       </c>
       <c r="E430">
         <v>11.99</v>
@@ -10731,7 +10758,7 @@
         <v>444</v>
       </c>
       <c r="D431" t="s">
-        <v>1050</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="432" spans="1:5">
@@ -10745,7 +10772,7 @@
         <v>445</v>
       </c>
       <c r="D432" t="s">
-        <v>1051</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="433" spans="1:5">
@@ -10759,7 +10786,7 @@
         <v>446</v>
       </c>
       <c r="D433" t="s">
-        <v>1052</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="434" spans="1:5">
@@ -10773,7 +10800,7 @@
         <v>447</v>
       </c>
       <c r="D434" t="s">
-        <v>1053</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="435" spans="1:5">
@@ -10787,7 +10814,7 @@
         <v>448</v>
       </c>
       <c r="D435" t="s">
-        <v>1054</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="436" spans="1:5">
@@ -10801,7 +10828,7 @@
         <v>449</v>
       </c>
       <c r="D436" t="s">
-        <v>1055</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="437" spans="1:5">
@@ -10815,7 +10842,7 @@
         <v>450</v>
       </c>
       <c r="D437" t="s">
-        <v>1056</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="438" spans="1:5">
@@ -10829,7 +10856,7 @@
         <v>451</v>
       </c>
       <c r="D438" t="s">
-        <v>1057</v>
+        <v>1062</v>
       </c>
       <c r="E438">
         <v>19.99</v>
@@ -10846,7 +10873,7 @@
         <v>452</v>
       </c>
       <c r="D439" t="s">
-        <v>1058</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="440" spans="1:5">
@@ -10877,7 +10904,7 @@
         <v>454</v>
       </c>
       <c r="D441" t="s">
-        <v>1059</v>
+        <v>1064</v>
       </c>
       <c r="E441">
         <v>4.49</v>
@@ -10894,7 +10921,7 @@
         <v>455</v>
       </c>
       <c r="D442" t="s">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="E442">
         <v>3.99</v>
@@ -10911,7 +10938,7 @@
         <v>456</v>
       </c>
       <c r="D443" t="s">
-        <v>1061</v>
+        <v>1066</v>
       </c>
       <c r="E443">
         <v>3.89</v>
@@ -10928,7 +10955,7 @@
         <v>457</v>
       </c>
       <c r="D444" t="s">
-        <v>1062</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="445" spans="1:5">
@@ -10942,7 +10969,7 @@
         <v>458</v>
       </c>
       <c r="D445" t="s">
-        <v>1063</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="446" spans="1:5">
@@ -10956,7 +10983,7 @@
         <v>459</v>
       </c>
       <c r="D446" t="s">
-        <v>1064</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="447" spans="1:5">
@@ -10970,7 +10997,7 @@
         <v>460</v>
       </c>
       <c r="D447" t="s">
-        <v>1065</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="448" spans="1:5">
@@ -10984,7 +11011,7 @@
         <v>461</v>
       </c>
       <c r="D448" t="s">
-        <v>1066</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="449" spans="1:4">
@@ -10998,7 +11025,7 @@
         <v>462</v>
       </c>
       <c r="D449" t="s">
-        <v>1067</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="450" spans="1:4">
@@ -11012,7 +11039,7 @@
         <v>463</v>
       </c>
       <c r="D450" t="s">
-        <v>1068</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="451" spans="1:4">
@@ -11026,7 +11053,7 @@
         <v>464</v>
       </c>
       <c r="D451" t="s">
-        <v>1069</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="452" spans="1:4">
@@ -11040,7 +11067,7 @@
         <v>465</v>
       </c>
       <c r="D452" t="s">
-        <v>1070</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="453" spans="1:4">
@@ -11054,7 +11081,7 @@
         <v>466</v>
       </c>
       <c r="D453" t="s">
-        <v>1070</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="454" spans="1:4">
@@ -11068,7 +11095,7 @@
         <v>467</v>
       </c>
       <c r="D454" t="s">
-        <v>1071</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="455" spans="1:4">
@@ -11082,7 +11109,7 @@
         <v>468</v>
       </c>
       <c r="D455" t="s">
-        <v>1072</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="456" spans="1:4">
@@ -11096,7 +11123,7 @@
         <v>469</v>
       </c>
       <c r="D456" t="s">
-        <v>1073</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="457" spans="1:4">
@@ -11110,7 +11137,7 @@
         <v>470</v>
       </c>
       <c r="D457" t="s">
-        <v>1074</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="458" spans="1:4">
@@ -11124,7 +11151,7 @@
         <v>471</v>
       </c>
       <c r="D458" t="s">
-        <v>1075</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="459" spans="1:4">
@@ -11138,7 +11165,7 @@
         <v>472</v>
       </c>
       <c r="D459" t="s">
-        <v>1076</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="460" spans="1:4">
@@ -11152,7 +11179,7 @@
         <v>473</v>
       </c>
       <c r="D460" t="s">
-        <v>1077</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="461" spans="1:4">
@@ -11166,7 +11193,7 @@
         <v>474</v>
       </c>
       <c r="D461" t="s">
-        <v>1078</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="462" spans="1:4">
@@ -11180,7 +11207,7 @@
         <v>475</v>
       </c>
       <c r="D462" t="s">
-        <v>1079</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="463" spans="1:4">
@@ -11194,7 +11221,7 @@
         <v>476</v>
       </c>
       <c r="D463" t="s">
-        <v>1080</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="464" spans="1:4">
@@ -11208,7 +11235,7 @@
         <v>477</v>
       </c>
       <c r="D464" t="s">
-        <v>1081</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="465" spans="1:4">
@@ -11222,7 +11249,7 @@
         <v>478</v>
       </c>
       <c r="D465" t="s">
-        <v>1082</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="466" spans="1:4">
@@ -11236,7 +11263,7 @@
         <v>479</v>
       </c>
       <c r="D466" t="s">
-        <v>1083</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="467" spans="1:4">
@@ -11250,7 +11277,7 @@
         <v>480</v>
       </c>
       <c r="D467" t="s">
-        <v>1084</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="468" spans="1:4">
@@ -11264,7 +11291,7 @@
         <v>481</v>
       </c>
       <c r="D468" t="s">
-        <v>1085</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="469" spans="1:4">
@@ -11278,7 +11305,7 @@
         <v>482</v>
       </c>
       <c r="D469" t="s">
-        <v>1086</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="470" spans="1:4">
@@ -11292,7 +11319,7 @@
         <v>483</v>
       </c>
       <c r="D470" t="s">
-        <v>1087</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="471" spans="1:4">
@@ -11306,7 +11333,7 @@
         <v>484</v>
       </c>
       <c r="D471" t="s">
-        <v>1088</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="472" spans="1:4">
@@ -11320,7 +11347,7 @@
         <v>485</v>
       </c>
       <c r="D472" t="s">
-        <v>1089</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="473" spans="1:4">
@@ -11334,7 +11361,7 @@
         <v>486</v>
       </c>
       <c r="D473" t="s">
-        <v>1090</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="474" spans="1:4">
@@ -11362,7 +11389,7 @@
         <v>488</v>
       </c>
       <c r="D475" t="s">
-        <v>1091</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="476" spans="1:4">
@@ -11376,7 +11403,7 @@
         <v>489</v>
       </c>
       <c r="D476" t="s">
-        <v>1092</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="477" spans="1:4">
@@ -11390,7 +11417,7 @@
         <v>490</v>
       </c>
       <c r="D477" t="s">
-        <v>1093</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="478" spans="1:4">
@@ -11404,7 +11431,7 @@
         <v>491</v>
       </c>
       <c r="D478" t="s">
-        <v>1094</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="479" spans="1:4">
@@ -11418,7 +11445,7 @@
         <v>492</v>
       </c>
       <c r="D479" t="s">
-        <v>1095</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="480" spans="1:4">
@@ -11432,7 +11459,7 @@
         <v>493</v>
       </c>
       <c r="D480" t="s">
-        <v>1096</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="481" spans="1:5">
@@ -11463,7 +11490,7 @@
         <v>495</v>
       </c>
       <c r="D482" t="s">
-        <v>1097</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="483" spans="1:5">
@@ -11494,7 +11521,7 @@
         <v>497</v>
       </c>
       <c r="D484" t="s">
-        <v>1098</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="485" spans="1:5">
@@ -11508,7 +11535,7 @@
         <v>498</v>
       </c>
       <c r="D485" t="s">
-        <v>1099</v>
+        <v>1104</v>
       </c>
       <c r="E485">
         <v>15.99</v>
@@ -11525,7 +11552,7 @@
         <v>499</v>
       </c>
       <c r="D486" t="s">
-        <v>1100</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="487" spans="1:5">
@@ -11539,7 +11566,7 @@
         <v>500</v>
       </c>
       <c r="D487" t="s">
-        <v>1101</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="488" spans="1:5">
@@ -11553,7 +11580,7 @@
         <v>501</v>
       </c>
       <c r="D488" t="s">
-        <v>1102</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="489" spans="1:5">
@@ -11567,7 +11594,7 @@
         <v>502</v>
       </c>
       <c r="D489" t="s">
-        <v>1103</v>
+        <v>1108</v>
       </c>
       <c r="E489">
         <v>11.99</v>
@@ -11584,7 +11611,7 @@
         <v>503</v>
       </c>
       <c r="D490" t="s">
-        <v>1104</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="491" spans="1:5">
@@ -11598,7 +11625,7 @@
         <v>504</v>
       </c>
       <c r="D491" t="s">
-        <v>1105</v>
+        <v>1110</v>
       </c>
       <c r="E491">
         <v>5.19</v>
@@ -11615,7 +11642,7 @@
         <v>505</v>
       </c>
       <c r="D492" t="s">
-        <v>1106</v>
+        <v>1111</v>
       </c>
       <c r="E492">
         <v>7.99</v>
@@ -11632,7 +11659,7 @@
         <v>506</v>
       </c>
       <c r="D493" t="s">
-        <v>1107</v>
+        <v>1112</v>
       </c>
       <c r="E493">
         <v>3.99</v>
@@ -11649,7 +11676,7 @@
         <v>507</v>
       </c>
       <c r="D494" t="s">
-        <v>1108</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="495" spans="1:5">
@@ -11663,7 +11690,7 @@
         <v>508</v>
       </c>
       <c r="D495" t="s">
-        <v>1109</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="496" spans="1:5">
@@ -11711,7 +11738,7 @@
         <v>511</v>
       </c>
       <c r="D498" t="s">
-        <v>1110</v>
+        <v>1115</v>
       </c>
       <c r="E498">
         <v>25.99</v>
@@ -11728,7 +11755,7 @@
         <v>512</v>
       </c>
       <c r="D499" t="s">
-        <v>1111</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="500" spans="1:5">
@@ -11742,7 +11769,7 @@
         <v>513</v>
       </c>
       <c r="D500" t="s">
-        <v>1112</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="501" spans="1:5">
@@ -11756,7 +11783,7 @@
         <v>514</v>
       </c>
       <c r="D501" t="s">
-        <v>1113</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="502" spans="1:5">
@@ -11770,7 +11797,7 @@
         <v>515</v>
       </c>
       <c r="D502" t="s">
-        <v>1114</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="503" spans="1:5">
@@ -11784,7 +11811,7 @@
         <v>516</v>
       </c>
       <c r="D503" t="s">
-        <v>1115</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="504" spans="1:5">
@@ -11798,7 +11825,7 @@
         <v>517</v>
       </c>
       <c r="D504" t="s">
-        <v>1116</v>
+        <v>1121</v>
       </c>
       <c r="E504">
         <v>26.99</v>
@@ -11815,7 +11842,7 @@
         <v>518</v>
       </c>
       <c r="D505" t="s">
-        <v>1117</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="506" spans="1:5">
@@ -11829,7 +11856,7 @@
         <v>519</v>
       </c>
       <c r="D506" t="s">
-        <v>1118</v>
+        <v>1123</v>
       </c>
       <c r="E506">
         <v>4.49</v>
@@ -11846,7 +11873,7 @@
         <v>520</v>
       </c>
       <c r="D507" t="s">
-        <v>1119</v>
+        <v>1124</v>
       </c>
       <c r="E507">
         <v>5.99</v>
@@ -11863,7 +11890,7 @@
         <v>521</v>
       </c>
       <c r="D508" t="s">
-        <v>1120</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="509" spans="1:5">
@@ -11877,7 +11904,7 @@
         <v>522</v>
       </c>
       <c r="D509" t="s">
-        <v>1121</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="510" spans="1:5">
@@ -11891,7 +11918,7 @@
         <v>523</v>
       </c>
       <c r="D510" t="s">
-        <v>1122</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="511" spans="1:5">
@@ -11905,7 +11932,7 @@
         <v>524</v>
       </c>
       <c r="D511" t="s">
-        <v>1123</v>
+        <v>1128</v>
       </c>
       <c r="E511">
         <v>1.69</v>
@@ -11922,7 +11949,7 @@
         <v>525</v>
       </c>
       <c r="D512" t="s">
-        <v>1124</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="513" spans="1:5">
@@ -11936,7 +11963,7 @@
         <v>526</v>
       </c>
       <c r="D513" t="s">
-        <v>1125</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="514" spans="1:5">
@@ -11950,7 +11977,7 @@
         <v>527</v>
       </c>
       <c r="D514" t="s">
-        <v>1126</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="515" spans="1:5">
@@ -11964,7 +11991,7 @@
         <v>528</v>
       </c>
       <c r="D515" t="s">
-        <v>1127</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="516" spans="1:5">
@@ -11978,7 +12005,7 @@
         <v>529</v>
       </c>
       <c r="D516" t="s">
-        <v>1128</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="517" spans="1:5">
@@ -11992,7 +12019,7 @@
         <v>530</v>
       </c>
       <c r="D517" t="s">
-        <v>1129</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="518" spans="1:5">
@@ -12006,7 +12033,7 @@
         <v>531</v>
       </c>
       <c r="D518" t="s">
-        <v>1130</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="519" spans="1:5">
@@ -12020,7 +12047,7 @@
         <v>532</v>
       </c>
       <c r="D519" t="s">
-        <v>1131</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="520" spans="1:5">
@@ -12034,7 +12061,7 @@
         <v>533</v>
       </c>
       <c r="D520" t="s">
-        <v>1132</v>
+        <v>1137</v>
       </c>
       <c r="E520">
         <v>23.7</v>
@@ -12051,7 +12078,7 @@
         <v>534</v>
       </c>
       <c r="D521" t="s">
-        <v>1133</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="522" spans="1:5">
@@ -12065,7 +12092,7 @@
         <v>535</v>
       </c>
       <c r="D522" t="s">
-        <v>1134</v>
+        <v>1139</v>
       </c>
       <c r="E522">
         <v>24.99</v>
@@ -12082,7 +12109,7 @@
         <v>536</v>
       </c>
       <c r="D523" t="s">
-        <v>1135</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="524" spans="1:5">
@@ -12096,7 +12123,7 @@
         <v>537</v>
       </c>
       <c r="D524" t="s">
-        <v>1136</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="525" spans="1:5">
@@ -12110,7 +12137,7 @@
         <v>538</v>
       </c>
       <c r="D525" t="s">
-        <v>1137</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="526" spans="1:5">
@@ -12124,7 +12151,7 @@
         <v>539</v>
       </c>
       <c r="D526" t="s">
-        <v>1138</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="527" spans="1:5">
@@ -12138,7 +12165,7 @@
         <v>540</v>
       </c>
       <c r="D527" t="s">
-        <v>1139</v>
+        <v>1144</v>
       </c>
       <c r="E527">
         <v>20.99</v>
@@ -12155,7 +12182,7 @@
         <v>541</v>
       </c>
       <c r="D528" t="s">
-        <v>1140</v>
+        <v>1145</v>
       </c>
       <c r="E528">
         <v>17.99</v>
@@ -12172,7 +12199,7 @@
         <v>542</v>
       </c>
       <c r="D529" t="s">
-        <v>1141</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="530" spans="1:5">
@@ -12186,7 +12213,7 @@
         <v>543</v>
       </c>
       <c r="D530" t="s">
-        <v>1142</v>
+        <v>1147</v>
       </c>
       <c r="E530">
         <v>34.99</v>
@@ -12203,7 +12230,7 @@
         <v>544</v>
       </c>
       <c r="D531" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="E531">
         <v>18.99</v>
@@ -12220,7 +12247,7 @@
         <v>545</v>
       </c>
       <c r="D532" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="E532">
         <v>10.99</v>
@@ -12237,7 +12264,7 @@
         <v>546</v>
       </c>
       <c r="D533" t="s">
-        <v>1145</v>
+        <v>1150</v>
       </c>
       <c r="E533">
         <v>12.99</v>
@@ -12254,7 +12281,7 @@
         <v>547</v>
       </c>
       <c r="D534" t="s">
-        <v>1146</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="535" spans="1:5">
@@ -12268,7 +12295,7 @@
         <v>548</v>
       </c>
       <c r="D535" t="s">
-        <v>1147</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="536" spans="1:5">
@@ -12282,7 +12309,7 @@
         <v>549</v>
       </c>
       <c r="D536" t="s">
-        <v>1148</v>
+        <v>1153</v>
       </c>
       <c r="E536">
         <v>21.99</v>
@@ -12299,7 +12326,7 @@
         <v>550</v>
       </c>
       <c r="D537" t="s">
-        <v>1149</v>
+        <v>1154</v>
       </c>
       <c r="E537">
         <v>8.390000000000001</v>
@@ -12316,7 +12343,7 @@
         <v>551</v>
       </c>
       <c r="D538" t="s">
-        <v>1150</v>
+        <v>1155</v>
       </c>
       <c r="E538">
         <v>10.99</v>
@@ -12333,7 +12360,7 @@
         <v>552</v>
       </c>
       <c r="D539" t="s">
-        <v>1151</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="540" spans="1:5">
@@ -12347,7 +12374,7 @@
         <v>553</v>
       </c>
       <c r="D540" t="s">
-        <v>1152</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="541" spans="1:5">
@@ -12361,7 +12388,7 @@
         <v>554</v>
       </c>
       <c r="D541" t="s">
-        <v>1153</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="542" spans="1:5">
@@ -12389,7 +12416,7 @@
         <v>556</v>
       </c>
       <c r="D543" t="s">
-        <v>1154</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="544" spans="1:5">
@@ -12403,7 +12430,7 @@
         <v>557</v>
       </c>
       <c r="D544" t="s">
-        <v>1155</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="545" spans="1:4">
@@ -12417,7 +12444,7 @@
         <v>558</v>
       </c>
       <c r="D545" t="s">
-        <v>1156</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="546" spans="1:4">
@@ -12431,7 +12458,7 @@
         <v>559</v>
       </c>
       <c r="D546" t="s">
-        <v>1157</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="547" spans="1:4">
@@ -12445,7 +12472,7 @@
         <v>560</v>
       </c>
       <c r="D547" t="s">
-        <v>1158</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="548" spans="1:4">
@@ -12459,7 +12486,7 @@
         <v>561</v>
       </c>
       <c r="D548" t="s">
-        <v>1159</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="549" spans="1:4">
@@ -12473,7 +12500,7 @@
         <v>562</v>
       </c>
       <c r="D549" t="s">
-        <v>1160</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="550" spans="1:4">
@@ -12487,7 +12514,7 @@
         <v>563</v>
       </c>
       <c r="D550" t="s">
-        <v>1161</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="551" spans="1:4">
@@ -12501,7 +12528,7 @@
         <v>564</v>
       </c>
       <c r="D551" t="s">
-        <v>1162</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="552" spans="1:4">
@@ -12515,7 +12542,7 @@
         <v>565</v>
       </c>
       <c r="D552" t="s">
-        <v>1163</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="553" spans="1:4">
@@ -12529,7 +12556,7 @@
         <v>566</v>
       </c>
       <c r="D553" t="s">
-        <v>1164</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="554" spans="1:4">
@@ -12543,7 +12570,7 @@
         <v>567</v>
       </c>
       <c r="D554" t="s">
-        <v>1165</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="555" spans="1:4">
@@ -12557,7 +12584,7 @@
         <v>568</v>
       </c>
       <c r="D555" t="s">
-        <v>1166</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="556" spans="1:4">
@@ -12571,7 +12598,7 @@
         <v>569</v>
       </c>
       <c r="D556" t="s">
-        <v>1167</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="557" spans="1:4">
@@ -12585,7 +12612,7 @@
         <v>570</v>
       </c>
       <c r="D557" t="s">
-        <v>1168</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="558" spans="1:4">
@@ -12599,7 +12626,7 @@
         <v>571</v>
       </c>
       <c r="D558" t="s">
-        <v>1169</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="559" spans="1:4">
@@ -12613,7 +12640,7 @@
         <v>572</v>
       </c>
       <c r="D559" t="s">
-        <v>1170</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="560" spans="1:4">
@@ -12627,7 +12654,7 @@
         <v>573</v>
       </c>
       <c r="D560" t="s">
-        <v>1171</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="561" spans="1:5">
@@ -12641,7 +12668,7 @@
         <v>574</v>
       </c>
       <c r="D561" t="s">
-        <v>1172</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="562" spans="1:5">
@@ -12655,7 +12682,7 @@
         <v>575</v>
       </c>
       <c r="D562" t="s">
-        <v>1173</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="563" spans="1:5">
@@ -12669,7 +12696,7 @@
         <v>576</v>
       </c>
       <c r="D563" t="s">
-        <v>1174</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="564" spans="1:5">
@@ -12683,7 +12710,7 @@
         <v>577</v>
       </c>
       <c r="D564" t="s">
-        <v>1175</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="565" spans="1:5">
@@ -12697,7 +12724,7 @@
         <v>578</v>
       </c>
       <c r="D565" t="s">
-        <v>1176</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="566" spans="1:5">
@@ -12711,7 +12738,7 @@
         <v>579</v>
       </c>
       <c r="D566" t="s">
-        <v>1177</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="567" spans="1:5">
@@ -12725,7 +12752,7 @@
         <v>580</v>
       </c>
       <c r="D567" t="s">
-        <v>1178</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="568" spans="1:5">
@@ -12739,7 +12766,7 @@
         <v>581</v>
       </c>
       <c r="D568" t="s">
-        <v>1179</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="569" spans="1:5">
@@ -12753,7 +12780,7 @@
         <v>582</v>
       </c>
       <c r="D569" t="s">
-        <v>1180</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="570" spans="1:5">
@@ -12767,7 +12794,7 @@
         <v>583</v>
       </c>
       <c r="D570" t="s">
-        <v>1181</v>
+        <v>1186</v>
       </c>
       <c r="E570">
         <v>7.99</v>
@@ -12784,7 +12811,7 @@
         <v>584</v>
       </c>
       <c r="D571" t="s">
-        <v>1182</v>
+        <v>1187</v>
       </c>
       <c r="E571">
         <v>7.99</v>
@@ -12815,7 +12842,7 @@
         <v>586</v>
       </c>
       <c r="D573" t="s">
-        <v>1183</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="574" spans="1:5">
@@ -12829,7 +12856,7 @@
         <v>587</v>
       </c>
       <c r="D574" t="s">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="E574">
         <v>9.99</v>
@@ -12846,7 +12873,7 @@
         <v>588</v>
       </c>
       <c r="D575" t="s">
-        <v>1185</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="576" spans="1:5">
@@ -12860,7 +12887,7 @@
         <v>589</v>
       </c>
       <c r="D576" t="s">
-        <v>1186</v>
+        <v>1191</v>
       </c>
       <c r="E576">
         <v>7.99</v>
@@ -12877,7 +12904,7 @@
         <v>590</v>
       </c>
       <c r="D577" t="s">
-        <v>1187</v>
+        <v>1192</v>
       </c>
       <c r="E577">
         <v>9.69</v>
@@ -12894,7 +12921,7 @@
         <v>591</v>
       </c>
       <c r="D578" t="s">
-        <v>1188</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="579" spans="1:5">
@@ -12925,7 +12952,7 @@
         <v>593</v>
       </c>
       <c r="D580" t="s">
-        <v>1189</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="581" spans="1:5">
@@ -12939,7 +12966,7 @@
         <v>594</v>
       </c>
       <c r="D581" t="s">
-        <v>1190</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="582" spans="1:5">
@@ -12953,7 +12980,7 @@
         <v>595</v>
       </c>
       <c r="D582" t="s">
-        <v>1191</v>
+        <v>1196</v>
       </c>
       <c r="E582">
         <v>9.99</v>
@@ -12970,7 +12997,7 @@
         <v>596</v>
       </c>
       <c r="D583" t="s">
-        <v>1192</v>
+        <v>1197</v>
       </c>
       <c r="E583">
         <v>10.39</v>
@@ -12987,7 +13014,7 @@
         <v>597</v>
       </c>
       <c r="D584" t="s">
-        <v>1193</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="585" spans="1:5">
@@ -13001,7 +13028,7 @@
         <v>598</v>
       </c>
       <c r="D585" t="s">
-        <v>1194</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="586" spans="1:5">
@@ -13015,7 +13042,7 @@
         <v>599</v>
       </c>
       <c r="D586" t="s">
-        <v>1195</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="587" spans="1:5">
@@ -13029,7 +13056,7 @@
         <v>600</v>
       </c>
       <c r="D587" t="s">
-        <v>1196</v>
+        <v>1201</v>
       </c>
       <c r="E587">
         <v>16.99</v>
@@ -13046,7 +13073,7 @@
         <v>601</v>
       </c>
       <c r="D588" t="s">
-        <v>1197</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="589" spans="1:5">
@@ -13060,7 +13087,7 @@
         <v>602</v>
       </c>
       <c r="D589" t="s">
-        <v>1198</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="590" spans="1:5">
@@ -13074,7 +13101,7 @@
         <v>603</v>
       </c>
       <c r="D590" t="s">
-        <v>1199</v>
+        <v>1204</v>
       </c>
       <c r="E590">
         <v>13.99</v>
@@ -13091,7 +13118,7 @@
         <v>604</v>
       </c>
       <c r="D591" t="s">
-        <v>1200</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="592" spans="1:5">
@@ -13105,7 +13132,7 @@
         <v>605</v>
       </c>
       <c r="D592" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="593" spans="1:5">
@@ -13119,7 +13146,7 @@
         <v>606</v>
       </c>
       <c r="D593" t="s">
-        <v>1202</v>
+        <v>1207</v>
       </c>
       <c r="E593">
         <v>40.99</v>
@@ -13136,7 +13163,7 @@
         <v>607</v>
       </c>
       <c r="D594" t="s">
-        <v>1203</v>
+        <v>1208</v>
       </c>
       <c r="E594">
         <v>1.99</v>
@@ -13221,7 +13248,7 @@
         <v>612</v>
       </c>
       <c r="D599" t="s">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="E599">
         <v>1.99</v>
@@ -13238,7 +13265,7 @@
         <v>613</v>
       </c>
       <c r="D600" t="s">
-        <v>1205</v>
+        <v>1210</v>
       </c>
       <c r="E600">
         <v>1.99</v>
@@ -13255,7 +13282,7 @@
         <v>614</v>
       </c>
       <c r="D601" t="s">
-        <v>1206</v>
+        <v>1211</v>
       </c>
       <c r="E601">
         <v>1.99</v>
@@ -13289,7 +13316,7 @@
         <v>616</v>
       </c>
       <c r="D603" t="s">
-        <v>1207</v>
+        <v>1212</v>
       </c>
       <c r="E603">
         <v>1.99</v>
@@ -13306,7 +13333,7 @@
         <v>617</v>
       </c>
       <c r="D604" t="s">
-        <v>1208</v>
+        <v>1213</v>
       </c>
       <c r="E604">
         <v>1.99</v>
@@ -13323,7 +13350,7 @@
         <v>618</v>
       </c>
       <c r="D605" t="s">
-        <v>1209</v>
+        <v>1214</v>
       </c>
       <c r="E605">
         <v>1.99</v>
@@ -13340,7 +13367,7 @@
         <v>619</v>
       </c>
       <c r="D606" t="s">
-        <v>1210</v>
+        <v>1215</v>
       </c>
       <c r="E606">
         <v>1.99</v>
@@ -13357,7 +13384,7 @@
         <v>620</v>
       </c>
       <c r="D607" t="s">
-        <v>1211</v>
+        <v>1216</v>
       </c>
       <c r="E607">
         <v>2.69</v>
@@ -13374,7 +13401,7 @@
         <v>621</v>
       </c>
       <c r="D608" t="s">
-        <v>1212</v>
+        <v>1217</v>
       </c>
       <c r="E608">
         <v>2.69</v>
@@ -13391,7 +13418,7 @@
         <v>622</v>
       </c>
       <c r="D609" t="s">
-        <v>1213</v>
+        <v>1218</v>
       </c>
       <c r="E609">
         <v>2.69</v>
@@ -13408,7 +13435,7 @@
         <v>623</v>
       </c>
       <c r="D610" t="s">
-        <v>1214</v>
+        <v>1219</v>
       </c>
       <c r="E610">
         <v>2.69</v>
@@ -13425,7 +13452,7 @@
         <v>624</v>
       </c>
       <c r="D611" t="s">
-        <v>1215</v>
+        <v>1220</v>
       </c>
       <c r="E611">
         <v>2.69</v>
@@ -13442,7 +13469,7 @@
         <v>625</v>
       </c>
       <c r="D612" t="s">
-        <v>1216</v>
+        <v>1221</v>
       </c>
       <c r="E612">
         <v>2.69</v>
@@ -13459,7 +13486,7 @@
         <v>626</v>
       </c>
       <c r="D613" t="s">
-        <v>1217</v>
+        <v>1222</v>
       </c>
       <c r="E613">
         <v>2.69</v>
@@ -13476,7 +13503,7 @@
         <v>627</v>
       </c>
       <c r="D614" t="s">
-        <v>1218</v>
+        <v>1223</v>
       </c>
       <c r="E614">
         <v>2.69</v>
@@ -13493,7 +13520,7 @@
         <v>628</v>
       </c>
       <c r="D615" t="s">
-        <v>1219</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="616" spans="1:5">
@@ -13507,7 +13534,7 @@
         <v>629</v>
       </c>
       <c r="D616" t="s">
-        <v>1220</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="617" spans="1:5">
@@ -13521,7 +13548,7 @@
         <v>630</v>
       </c>
       <c r="D617" t="s">
-        <v>1221</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="618" spans="1:5">
@@ -13535,7 +13562,7 @@
         <v>631</v>
       </c>
       <c r="D618" t="s">
-        <v>1222</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="619" spans="1:5">
@@ -13549,7 +13576,7 @@
         <v>632</v>
       </c>
       <c r="D619" t="s">
-        <v>1223</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="620" spans="1:5">
@@ -13563,7 +13590,7 @@
         <v>633</v>
       </c>
       <c r="D620" t="s">
-        <v>1224</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="621" spans="1:5">
@@ -13577,7 +13604,7 @@
         <v>634</v>
       </c>
       <c r="D621" t="s">
-        <v>1225</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="622" spans="1:5">
@@ -13591,7 +13618,7 @@
         <v>635</v>
       </c>
       <c r="D622" t="s">
-        <v>1226</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="623" spans="1:5">
@@ -13605,7 +13632,7 @@
         <v>636</v>
       </c>
       <c r="D623" t="s">
-        <v>1227</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="624" spans="1:5">
@@ -13619,7 +13646,7 @@
         <v>637</v>
       </c>
       <c r="D624" t="s">
-        <v>1228</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="625" spans="1:5">
@@ -13633,7 +13660,7 @@
         <v>638</v>
       </c>
       <c r="D625" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="626" spans="1:5">
@@ -13647,7 +13674,7 @@
         <v>639</v>
       </c>
       <c r="D626" t="s">
-        <v>1230</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="627" spans="1:5">
@@ -13661,7 +13688,7 @@
         <v>640</v>
       </c>
       <c r="D627" t="s">
-        <v>1231</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="628" spans="1:5">
@@ -13675,7 +13702,7 @@
         <v>641</v>
       </c>
       <c r="D628" t="s">
-        <v>1232</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="629" spans="1:5">
@@ -13689,7 +13716,7 @@
         <v>642</v>
       </c>
       <c r="D629" t="s">
-        <v>1233</v>
+        <v>1238</v>
       </c>
       <c r="E629">
         <v>1.99</v>
@@ -13706,7 +13733,7 @@
         <v>643</v>
       </c>
       <c r="D630" t="s">
-        <v>1234</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="631" spans="1:5">
@@ -13734,7 +13761,7 @@
         <v>645</v>
       </c>
       <c r="D632" t="s">
-        <v>1235</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="633" spans="1:5">
@@ -13748,7 +13775,7 @@
         <v>646</v>
       </c>
       <c r="D633" t="s">
-        <v>1236</v>
+        <v>1241</v>
       </c>
       <c r="E633">
         <v>5.49</v>
@@ -13765,7 +13792,7 @@
         <v>647</v>
       </c>
       <c r="D634" t="s">
-        <v>1237</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="635" spans="1:5">
@@ -13779,7 +13806,7 @@
         <v>648</v>
       </c>
       <c r="D635" t="s">
-        <v>1238</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="636" spans="1:5">
@@ -13793,7 +13820,7 @@
         <v>649</v>
       </c>
       <c r="D636" t="s">
-        <v>1239</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="637" spans="1:5">
@@ -13807,7 +13834,7 @@
         <v>650</v>
       </c>
       <c r="D637" t="s">
-        <v>1240</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="638" spans="1:5">
@@ -13821,7 +13848,7 @@
         <v>651</v>
       </c>
       <c r="D638" t="s">
-        <v>1241</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="639" spans="1:5">
@@ -13835,7 +13862,7 @@
         <v>652</v>
       </c>
       <c r="D639" t="s">
-        <v>1242</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="640" spans="1:5">
@@ -13849,7 +13876,7 @@
         <v>653</v>
       </c>
       <c r="D640" t="s">
-        <v>1243</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="641" spans="1:5">
@@ -13863,7 +13890,7 @@
         <v>654</v>
       </c>
       <c r="D641" t="s">
-        <v>1244</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="642" spans="1:5">
@@ -13891,7 +13918,7 @@
         <v>656</v>
       </c>
       <c r="D643" t="s">
-        <v>1245</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="644" spans="1:5">
@@ -13905,7 +13932,7 @@
         <v>657</v>
       </c>
       <c r="D644" t="s">
-        <v>1246</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="645" spans="1:5">
@@ -13919,7 +13946,7 @@
         <v>658</v>
       </c>
       <c r="D645" t="s">
-        <v>1247</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="646" spans="1:5">
@@ -13933,7 +13960,7 @@
         <v>659</v>
       </c>
       <c r="D646" t="s">
-        <v>1248</v>
+        <v>1253</v>
       </c>
       <c r="E646">
         <v>17.99</v>
@@ -13964,7 +13991,7 @@
         <v>172</v>
       </c>
       <c r="D648" t="s">
-        <v>1249</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="649" spans="1:5">
@@ -13978,7 +14005,7 @@
         <v>661</v>
       </c>
       <c r="D649" t="s">
-        <v>1250</v>
+        <v>1255</v>
       </c>
       <c r="E649">
         <v>27.99</v>
@@ -14012,7 +14039,7 @@
         <v>663</v>
       </c>
       <c r="D651" t="s">
-        <v>1251</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="652" spans="1:5">
@@ -14026,7 +14053,7 @@
         <v>664</v>
       </c>
       <c r="D652" t="s">
-        <v>1252</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="653" spans="1:5">
@@ -14040,7 +14067,7 @@
         <v>665</v>
       </c>
       <c r="D653" t="s">
-        <v>1253</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="654" spans="1:5">
@@ -14054,7 +14081,7 @@
         <v>666</v>
       </c>
       <c r="D654" t="s">
-        <v>1254</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="655" spans="1:5">
@@ -14096,7 +14123,7 @@
         <v>669</v>
       </c>
       <c r="D657" t="s">
-        <v>1255</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="658" spans="1:5">
@@ -14110,7 +14137,7 @@
         <v>670</v>
       </c>
       <c r="D658" t="s">
-        <v>1256</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="659" spans="1:5">
@@ -14166,7 +14193,7 @@
         <v>674</v>
       </c>
       <c r="D662" t="s">
-        <v>1257</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="663" spans="1:5">
@@ -14194,7 +14221,7 @@
         <v>676</v>
       </c>
       <c r="D664" t="s">
-        <v>1258</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="665" spans="1:5">
@@ -14208,7 +14235,7 @@
         <v>677</v>
       </c>
       <c r="D665" t="s">
-        <v>1259</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="666" spans="1:5">
@@ -14222,7 +14249,7 @@
         <v>678</v>
       </c>
       <c r="D666" t="s">
-        <v>1260</v>
+        <v>1265</v>
       </c>
       <c r="E666">
         <v>11.99</v>
@@ -14239,7 +14266,7 @@
         <v>679</v>
       </c>
       <c r="D667" t="s">
-        <v>1261</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="668" spans="1:5">
@@ -14253,7 +14280,7 @@
         <v>680</v>
       </c>
       <c r="D668" t="s">
-        <v>1262</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="669" spans="1:5">
@@ -14301,7 +14328,7 @@
         <v>683</v>
       </c>
       <c r="D671" t="s">
-        <v>1263</v>
+        <v>1268</v>
       </c>
       <c r="E671">
         <v>18.99</v>
@@ -14318,7 +14345,7 @@
         <v>684</v>
       </c>
       <c r="D672" t="s">
-        <v>1264</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="673" spans="1:5">
@@ -14349,7 +14376,7 @@
         <v>686</v>
       </c>
       <c r="D674" t="s">
-        <v>1265</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="675" spans="1:5">
@@ -14363,7 +14390,7 @@
         <v>687</v>
       </c>
       <c r="D675" t="s">
-        <v>1266</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="676" spans="1:5">
@@ -14411,7 +14438,7 @@
         <v>690</v>
       </c>
       <c r="D678" t="s">
-        <v>1267</v>
+        <v>1272</v>
       </c>
       <c r="E678">
         <v>85.98999999999999</v>
@@ -14428,7 +14455,7 @@
         <v>691</v>
       </c>
       <c r="D679" t="s">
-        <v>1268</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="680" spans="1:5">
@@ -14442,7 +14469,7 @@
         <v>692</v>
       </c>
       <c r="D680" t="s">
-        <v>1269</v>
+        <v>1274</v>
       </c>
       <c r="E680">
         <v>55.99</v>
@@ -14459,7 +14486,7 @@
         <v>693</v>
       </c>
       <c r="D681" t="s">
-        <v>1270</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="682" spans="1:5">
@@ -14473,10 +14500,95 @@
         <v>694</v>
       </c>
       <c r="D682" t="s">
-        <v>1271</v>
+        <v>1276</v>
       </c>
       <c r="E682">
         <v>99.98999999999999</v>
+      </c>
+    </row>
+    <row r="683" spans="1:5">
+      <c r="A683">
+        <v>132915</v>
+      </c>
+      <c r="B683" t="s">
+        <v>6</v>
+      </c>
+      <c r="C683" t="s">
+        <v>695</v>
+      </c>
+      <c r="D683" t="s">
+        <v>1277</v>
+      </c>
+      <c r="E683">
+        <v>44.99</v>
+      </c>
+    </row>
+    <row r="684" spans="1:5">
+      <c r="A684">
+        <v>236674</v>
+      </c>
+      <c r="B684" t="s">
+        <v>11</v>
+      </c>
+      <c r="C684" t="s">
+        <v>696</v>
+      </c>
+      <c r="D684" t="s">
+        <v>1278</v>
+      </c>
+      <c r="E684">
+        <v>39.99</v>
+      </c>
+    </row>
+    <row r="685" spans="1:5">
+      <c r="A685">
+        <v>157068</v>
+      </c>
+      <c r="B685" t="s">
+        <v>19</v>
+      </c>
+      <c r="C685" t="s">
+        <v>697</v>
+      </c>
+      <c r="D685" t="s">
+        <v>1279</v>
+      </c>
+      <c r="E685">
+        <v>3.59</v>
+      </c>
+    </row>
+    <row r="686" spans="1:5">
+      <c r="A686">
+        <v>198938</v>
+      </c>
+      <c r="B686" t="s">
+        <v>19</v>
+      </c>
+      <c r="C686" t="s">
+        <v>698</v>
+      </c>
+      <c r="D686" t="s">
+        <v>1280</v>
+      </c>
+      <c r="E686">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="687" spans="1:5">
+      <c r="A687">
+        <v>104881</v>
+      </c>
+      <c r="B687" t="s">
+        <v>12</v>
+      </c>
+      <c r="C687" t="s">
+        <v>699</v>
+      </c>
+      <c r="D687" t="s">
+        <v>699</v>
+      </c>
+      <c r="E687">
+        <v>8.99</v>
       </c>
     </row>
   </sheetData>

--- a/dados_produtos_corrigidos.xlsx
+++ b/dados_produtos_corrigidos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E711"/>
+  <dimension ref="A1:E715"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15898,7 +15898,11 @@
       <c r="A711" t="n">
         <v>173405</v>
       </c>
-      <c r="B711" t="inlineStr"/>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - EMBUTIDO</t>
+        </is>
+      </c>
       <c r="C711" t="inlineStr">
         <is>
           <t>MORTADELA DEFUMADA SEARA KG</t>
@@ -15906,10 +15910,102 @@
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t xml:space="preserve">MORTADELA SEARA DEFUMADA KG </t>
+          <t>MORTADELA SEARA KG DEFUMADA</t>
         </is>
       </c>
       <c r="E711" t="inlineStr"/>
+    </row>
+    <row r="712">
+      <c r="A712" t="n">
+        <v>230698</v>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - DESTILADOS</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>BE GIN TANQUERAI TEN 750 ML 750 ML</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>GIN TANQUERAI TEN 750ML</t>
+        </is>
+      </c>
+      <c r="E712" t="n">
+        <v>259.99</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="n">
+        <v>157068</v>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - CERVEJA CX</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>CERV BRAHMA DUPLO MALTE 350ML PAC C/12 U</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>CERVEJA BRAHMA DUPLO MALTE 12 X 350ML</t>
+        </is>
+      </c>
+      <c r="E713" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="n">
+        <v>286271</v>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - #00 REFRIGERANTES</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>REFRIGERANTE PEPSI 2L BLACK ZERO ACUCAR</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>REFRIGERANTE PEPSI 2L BLACK ZERO ACUCAR</t>
+        </is>
+      </c>
+      <c r="E714" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="n">
+        <v>137381</v>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - DESTILADOS</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>WHISKY JOHNNIE WALKER RED LABEL. 1LT</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>WHISKY JOHNNIE WALKER RED LABEL 1L</t>
+        </is>
+      </c>
+      <c r="E715" t="n">
+        <v>128.99</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dados_produtos_corrigidos.xlsx
+++ b/dados_produtos_corrigidos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E761"/>
+  <dimension ref="A1:E767"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17065,6 +17065,144 @@
         <v>25.99</v>
       </c>
     </row>
+    <row r="762">
+      <c r="A762" t="n">
+        <v>193650</v>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>BATATAS PRE-FRITAS CONG BOUA  400GR</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>BATATAS BOUA 400G CONGELADAS PRE-FRITAS</t>
+        </is>
+      </c>
+      <c r="E762" t="n">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="n">
+        <v>194792</v>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>BATATAS PRE-FRITAS CONG BOUA 2KG</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>BATATAS BOUA 2KG CONGELADAS PRE-FRITAS</t>
+        </is>
+      </c>
+      <c r="E763" t="n">
+        <v>40.99</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="n">
+        <v>170464</v>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - EMPANADO</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>STEAK FRANGO EMPANADO SADIA 100G STCE</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>STEAK EMPANADO SADIA 100G FRANGO</t>
+        </is>
+      </c>
+      <c r="E764" t="n">
+        <v>2.19</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="n">
+        <v>113911</v>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML. MACA</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML MAÇÃ</t>
+        </is>
+      </c>
+      <c r="E765" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="n">
+        <v>113914</v>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML. NEUTRO</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML NEUTRO</t>
+        </is>
+      </c>
+      <c r="E766" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="n">
+        <v>274807</v>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>MACARRAO RICOSA ESPAGUETE 400GR COMUM</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>MACARRÃO RICOSA 400G ESPAGUETE COMUM</t>
+        </is>
+      </c>
+      <c r="E767" t="n">
+        <v>3.29</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dados_produtos_corrigidos.xlsx
+++ b/dados_produtos_corrigidos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E767"/>
+  <dimension ref="A1:E770"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17203,6 +17203,75 @@
         <v>3.29</v>
       </c>
     </row>
+    <row r="768">
+      <c r="A768" t="n">
+        <v>106866</v>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>CREME DE MILHO SINHA 500GR</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>CREME DE MILHO SINHA 500G</t>
+        </is>
+      </c>
+      <c r="E768" t="n">
+        <v>2.49</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="n">
+        <v>100110</v>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>FARINHA MILHO SINHA 500G BIJU</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>FARINHA DE MILHO SINHA 500G BIJU</t>
+        </is>
+      </c>
+      <c r="E769" t="n">
+        <v>3.19</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="n">
+        <v>251877</v>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>LEITE PO NINHO INTEGRAL LT 380G</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>LEITE PO NINHO LATA 380G INTEGRAL</t>
+        </is>
+      </c>
+      <c r="E770" t="n">
+        <v>20.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dados_produtos_corrigidos.xlsx
+++ b/dados_produtos_corrigidos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E770"/>
+  <dimension ref="A1:E775"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17272,6 +17272,121 @@
         <v>20.99</v>
       </c>
     </row>
+    <row r="771">
+      <c r="A771" t="n">
+        <v>105007</v>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>ABOBORA CABOTIA KG</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>ABOBORA KG CABOTIA</t>
+        </is>
+      </c>
+      <c r="E771" t="n">
+        <v>4.49</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="n">
+        <v>104903</v>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>BATATA DOCE ROSA KG</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>BATATA DOCE KG ROSA</t>
+        </is>
+      </c>
+      <c r="E772" t="n">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="n">
+        <v>104883</v>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>MANGA TOMY KG</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MANGA KG TOMY </t>
+        </is>
+      </c>
+      <c r="E773" t="n">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="n">
+        <v>113290</v>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>MELAO AMARELO REI / REDINHA KG</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MELAO AMARELO KG REI | REDINHA </t>
+        </is>
+      </c>
+      <c r="E774" t="n">
+        <v>14.99</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="n">
+        <v>104890</v>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>#09 HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>UVA RED GLOBE NACIONAL KG</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>UVA KG RED GLOBE NACIONAL</t>
+        </is>
+      </c>
+      <c r="E775" t="n">
+        <v>21.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dados_produtos_corrigidos.xlsx
+++ b/dados_produtos_corrigidos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B8CD76D-A127-4555-A347-84214480EB6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAD74E94-3BBC-4EC5-9FC5-F56705A0A716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2327" uniqueCount="1446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2399" uniqueCount="1489">
   <si>
     <t>ID Produto</t>
   </si>
@@ -2515,9 +2515,6 @@
     <t>ENXAGUE BUCAL CEPACOL LEV 500ML PAG 350M</t>
   </si>
   <si>
-    <t xml:space="preserve">ENXAGUE BUCAL CEPACOL 500ML MENTA SEM ALCOOL PROMOCIONAL </t>
-  </si>
-  <si>
     <t>GELACREME SALON LINE 500GR TO DE CACHOS</t>
   </si>
   <si>
@@ -3931,9 +3928,6 @@
     <t>TEKITOS SEARA FRANGO 300G</t>
   </si>
   <si>
-    <t xml:space="preserve">TEKITOS SEARA 300G FRANGO </t>
-  </si>
-  <si>
     <t>TEKITOS SEARA QUEIJO OREGANO 300GR</t>
   </si>
   <si>
@@ -4358,6 +4352,141 @@
   </si>
   <si>
     <t>UVA KG RED GLOBE NACIONAL</t>
+  </si>
+  <si>
+    <t>AZEITE COCINERO EXTRA VIRGEM 500ML</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZEITE DE OLIVA COCINERO 500ML EXTRA VIRGEM </t>
+  </si>
+  <si>
+    <t>CAFE UNIAO 250GR TRADICIONAL</t>
+  </si>
+  <si>
+    <t>CAFÉ UNIÃO 250G TRADICIONAL</t>
+  </si>
+  <si>
+    <t>CR D SORRISO TR LIMP COMP PCO ESP 120G</t>
+  </si>
+  <si>
+    <t>CREME DENTAL SORRISO 120G TRIPA LIMPEZA COMPLETA</t>
+  </si>
+  <si>
+    <t>DESINFETANTE POLITRIZ 1,75 LT LIMAO</t>
+  </si>
+  <si>
+    <t>DESINFETANTE POLITRIZ 1,75L LIMÃO</t>
+  </si>
+  <si>
+    <t>DESINFETANTE POLITRIZ 1,75L EUCALIPTO</t>
+  </si>
+  <si>
+    <t>DESINFETANTE POLITRIZ 1,75LT ALFAZEMA</t>
+  </si>
+  <si>
+    <t>DESINFETANTE POLITRIZ 1,75L ALFAZEMA</t>
+  </si>
+  <si>
+    <t>DESINFETANTE POLITRIZ 1,75LT FLORAL</t>
+  </si>
+  <si>
+    <t>DESINFETANTE POLITRIZ 1,75L FLORAL</t>
+  </si>
+  <si>
+    <t>DESINFETANTE POLITRIZ 1,75LT GARDENIA</t>
+  </si>
+  <si>
+    <t>DESINFETANTE POLITRIZ 1,75L GARDENIA</t>
+  </si>
+  <si>
+    <t>DESINFETANTE POLITRIZ 1,75LT LAVANDA</t>
+  </si>
+  <si>
+    <t>DESINFETANTE POLITRIZ 1,75L LAVANDA</t>
+  </si>
+  <si>
+    <t>DESINFETANTE POLITRIZ 1,75LT MARINE</t>
+  </si>
+  <si>
+    <t>DESINFETANTE POLITRIZ 1,75L MARINE</t>
+  </si>
+  <si>
+    <t>DESINFETANTE POLITRIZ 1,75LT ORQUIDEA</t>
+  </si>
+  <si>
+    <t>DESINFETANTE POLITRIZ 1,75L ORQUIDEA</t>
+  </si>
+  <si>
+    <t>DESINFETANTE POLITRIZ 1,75LT PINHO</t>
+  </si>
+  <si>
+    <t>DESINFETANTE POLITRIZ 1,75L PINHO</t>
+  </si>
+  <si>
+    <t>ENERGETICO BALY 250ML CITRUS</t>
+  </si>
+  <si>
+    <t>ENERGETICO BALY 250ML PITAYA DRAGON</t>
+  </si>
+  <si>
+    <t>FARINHA DE MANDIOCA OVINHA DONA DE 1 KG</t>
+  </si>
+  <si>
+    <t>FARINHA DE MANDIOCA OVINHA DONA DE 1KG</t>
+  </si>
+  <si>
+    <t>LEITE UHT INTEGRAL ZERO LACTOSE C/TAMPA</t>
+  </si>
+  <si>
+    <t>LEITE ITALAC 1L INTEGRAL ZERO LACTOSE</t>
+  </si>
+  <si>
+    <t>LIMPADOR QBOA 500ML LIMPEZA PESADA</t>
+  </si>
+  <si>
+    <t>PAPEL HIGIENICO ONDUNORTE ROSE NT 6X12 (</t>
+  </si>
+  <si>
+    <t>PAPEL HIGIENICO ONDUNORTE 12 X 20M ROSE NT</t>
+  </si>
+  <si>
+    <t>PAPEL TOALHA  ABSOLUTO 240FLHAS C/2 ROLO</t>
+  </si>
+  <si>
+    <t>PAPEL TOALHA  ABSOLUTO 2 X 240 FOLHAS</t>
+  </si>
+  <si>
+    <t>REFRIG SUKITA 2L UVA</t>
+  </si>
+  <si>
+    <t>REFRIGERANTE SUKITA 2L UVA</t>
+  </si>
+  <si>
+    <t>ROSQUINHA LEITE MICOS 600G</t>
+  </si>
+  <si>
+    <t>ROSQUINHA MICOS 600G ROSQUINHA LEITE</t>
+  </si>
+  <si>
+    <t>SABAO BARRA ESTRELA 900GR NEUTRO</t>
+  </si>
+  <si>
+    <t>SABÃO BARRA ESTRELA 900G NEUTRO</t>
+  </si>
+  <si>
+    <t>SABAO EM PO ASSIM 800GR TRIPLACAO FLORAL</t>
+  </si>
+  <si>
+    <t>SABÃO EM PO ASSIM 800G TRIPLACAO FLORAL</t>
+  </si>
+  <si>
+    <t>TALCO DESOD TABU PERFUMADO 100GR</t>
+  </si>
+  <si>
+    <t>TALCO TABU 100G DESODORANTE PERFUMADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENXAGUANTE BUCAL CEPACOL 500ML MENTA SEM ALCOOL PROMOCIONAL </t>
   </si>
 </sst>
 </file>
@@ -4376,6 +4505,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -4720,8 +4850,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E775"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E799"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.5703125" bestFit="1" customWidth="1"/>
@@ -11539,7 +11669,7 @@
         <v>830</v>
       </c>
       <c r="D454" t="s">
-        <v>831</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="455" spans="1:4" x14ac:dyDescent="0.25">
@@ -11550,10 +11680,10 @@
         <v>662</v>
       </c>
       <c r="C455" t="s">
+        <v>831</v>
+      </c>
+      <c r="D455" t="s">
         <v>832</v>
-      </c>
-      <c r="D455" t="s">
-        <v>833</v>
       </c>
     </row>
     <row r="456" spans="1:4" x14ac:dyDescent="0.25">
@@ -11564,10 +11694,10 @@
         <v>662</v>
       </c>
       <c r="C456" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="D456" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="457" spans="1:4" x14ac:dyDescent="0.25">
@@ -11578,10 +11708,10 @@
         <v>662</v>
       </c>
       <c r="C457" t="s">
+        <v>834</v>
+      </c>
+      <c r="D457" t="s">
         <v>835</v>
-      </c>
-      <c r="D457" t="s">
-        <v>836</v>
       </c>
     </row>
     <row r="458" spans="1:4" x14ac:dyDescent="0.25">
@@ -11592,10 +11722,10 @@
         <v>662</v>
       </c>
       <c r="C458" t="s">
+        <v>836</v>
+      </c>
+      <c r="D458" t="s">
         <v>837</v>
-      </c>
-      <c r="D458" t="s">
-        <v>838</v>
       </c>
     </row>
     <row r="459" spans="1:4" x14ac:dyDescent="0.25">
@@ -11606,10 +11736,10 @@
         <v>662</v>
       </c>
       <c r="C459" t="s">
+        <v>838</v>
+      </c>
+      <c r="D459" t="s">
         <v>839</v>
-      </c>
-      <c r="D459" t="s">
-        <v>840</v>
       </c>
     </row>
     <row r="460" spans="1:4" x14ac:dyDescent="0.25">
@@ -11620,10 +11750,10 @@
         <v>662</v>
       </c>
       <c r="C460" t="s">
+        <v>840</v>
+      </c>
+      <c r="D460" t="s">
         <v>841</v>
-      </c>
-      <c r="D460" t="s">
-        <v>842</v>
       </c>
     </row>
     <row r="461" spans="1:4" x14ac:dyDescent="0.25">
@@ -11634,10 +11764,10 @@
         <v>662</v>
       </c>
       <c r="C461" t="s">
+        <v>842</v>
+      </c>
+      <c r="D461" t="s">
         <v>843</v>
-      </c>
-      <c r="D461" t="s">
-        <v>844</v>
       </c>
     </row>
     <row r="462" spans="1:4" x14ac:dyDescent="0.25">
@@ -11648,10 +11778,10 @@
         <v>662</v>
       </c>
       <c r="C462" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="D462" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="463" spans="1:4" x14ac:dyDescent="0.25">
@@ -11662,10 +11792,10 @@
         <v>662</v>
       </c>
       <c r="C463" t="s">
+        <v>845</v>
+      </c>
+      <c r="D463" t="s">
         <v>846</v>
-      </c>
-      <c r="D463" t="s">
-        <v>847</v>
       </c>
     </row>
     <row r="464" spans="1:4" x14ac:dyDescent="0.25">
@@ -11676,10 +11806,10 @@
         <v>662</v>
       </c>
       <c r="C464" t="s">
+        <v>847</v>
+      </c>
+      <c r="D464" t="s">
         <v>848</v>
-      </c>
-      <c r="D464" t="s">
-        <v>849</v>
       </c>
     </row>
     <row r="465" spans="1:5" x14ac:dyDescent="0.25">
@@ -11690,10 +11820,10 @@
         <v>662</v>
       </c>
       <c r="C465" t="s">
+        <v>849</v>
+      </c>
+      <c r="D465" t="s">
         <v>850</v>
-      </c>
-      <c r="D465" t="s">
-        <v>851</v>
       </c>
     </row>
     <row r="466" spans="1:5" x14ac:dyDescent="0.25">
@@ -11704,10 +11834,10 @@
         <v>662</v>
       </c>
       <c r="C466" t="s">
+        <v>851</v>
+      </c>
+      <c r="D466" t="s">
         <v>852</v>
-      </c>
-      <c r="D466" t="s">
-        <v>853</v>
       </c>
     </row>
     <row r="467" spans="1:5" x14ac:dyDescent="0.25">
@@ -11718,10 +11848,10 @@
         <v>662</v>
       </c>
       <c r="C467" t="s">
+        <v>853</v>
+      </c>
+      <c r="D467" t="s">
         <v>854</v>
-      </c>
-      <c r="D467" t="s">
-        <v>855</v>
       </c>
     </row>
     <row r="468" spans="1:5" x14ac:dyDescent="0.25">
@@ -11732,10 +11862,10 @@
         <v>662</v>
       </c>
       <c r="C468" t="s">
+        <v>855</v>
+      </c>
+      <c r="D468" t="s">
         <v>856</v>
-      </c>
-      <c r="D468" t="s">
-        <v>857</v>
       </c>
     </row>
     <row r="469" spans="1:5" x14ac:dyDescent="0.25">
@@ -11746,10 +11876,10 @@
         <v>662</v>
       </c>
       <c r="C469" t="s">
+        <v>857</v>
+      </c>
+      <c r="D469" t="s">
         <v>858</v>
-      </c>
-      <c r="D469" t="s">
-        <v>859</v>
       </c>
       <c r="E469">
         <v>65.989999999999995</v>
@@ -11763,10 +11893,10 @@
         <v>662</v>
       </c>
       <c r="C470" t="s">
+        <v>859</v>
+      </c>
+      <c r="D470" t="s">
         <v>860</v>
-      </c>
-      <c r="D470" t="s">
-        <v>861</v>
       </c>
       <c r="E470">
         <v>65.989999999999995</v>
@@ -11780,10 +11910,10 @@
         <v>662</v>
       </c>
       <c r="C471" t="s">
+        <v>861</v>
+      </c>
+      <c r="D471" t="s">
         <v>862</v>
-      </c>
-      <c r="D471" t="s">
-        <v>863</v>
       </c>
     </row>
     <row r="472" spans="1:5" x14ac:dyDescent="0.25">
@@ -11794,10 +11924,10 @@
         <v>662</v>
       </c>
       <c r="C472" t="s">
+        <v>863</v>
+      </c>
+      <c r="D472" t="s">
         <v>864</v>
-      </c>
-      <c r="D472" t="s">
-        <v>865</v>
       </c>
     </row>
     <row r="473" spans="1:5" x14ac:dyDescent="0.25">
@@ -11808,10 +11938,10 @@
         <v>662</v>
       </c>
       <c r="C473" t="s">
+        <v>865</v>
+      </c>
+      <c r="D473" t="s">
         <v>866</v>
-      </c>
-      <c r="D473" t="s">
-        <v>867</v>
       </c>
     </row>
     <row r="474" spans="1:5" x14ac:dyDescent="0.25">
@@ -11822,10 +11952,10 @@
         <v>662</v>
       </c>
       <c r="C474" t="s">
+        <v>867</v>
+      </c>
+      <c r="D474" t="s">
         <v>868</v>
-      </c>
-      <c r="D474" t="s">
-        <v>869</v>
       </c>
     </row>
     <row r="475" spans="1:5" x14ac:dyDescent="0.25">
@@ -11836,10 +11966,10 @@
         <v>662</v>
       </c>
       <c r="C475" t="s">
+        <v>869</v>
+      </c>
+      <c r="D475" t="s">
         <v>870</v>
-      </c>
-      <c r="D475" t="s">
-        <v>871</v>
       </c>
     </row>
     <row r="476" spans="1:5" x14ac:dyDescent="0.25">
@@ -11850,10 +11980,10 @@
         <v>662</v>
       </c>
       <c r="C476" t="s">
+        <v>871</v>
+      </c>
+      <c r="D476" t="s">
         <v>872</v>
-      </c>
-      <c r="D476" t="s">
-        <v>873</v>
       </c>
     </row>
     <row r="477" spans="1:5" x14ac:dyDescent="0.25">
@@ -11864,10 +11994,10 @@
         <v>662</v>
       </c>
       <c r="C477" t="s">
+        <v>873</v>
+      </c>
+      <c r="D477" t="s">
         <v>874</v>
-      </c>
-      <c r="D477" t="s">
-        <v>875</v>
       </c>
     </row>
     <row r="478" spans="1:5" x14ac:dyDescent="0.25">
@@ -11878,10 +12008,10 @@
         <v>662</v>
       </c>
       <c r="C478" t="s">
+        <v>875</v>
+      </c>
+      <c r="D478" t="s">
         <v>876</v>
-      </c>
-      <c r="D478" t="s">
-        <v>877</v>
       </c>
     </row>
     <row r="479" spans="1:5" x14ac:dyDescent="0.25">
@@ -11892,10 +12022,10 @@
         <v>662</v>
       </c>
       <c r="C479" t="s">
+        <v>877</v>
+      </c>
+      <c r="D479" t="s">
         <v>878</v>
-      </c>
-      <c r="D479" t="s">
-        <v>879</v>
       </c>
     </row>
     <row r="480" spans="1:5" x14ac:dyDescent="0.25">
@@ -11906,10 +12036,10 @@
         <v>662</v>
       </c>
       <c r="C480" t="s">
+        <v>879</v>
+      </c>
+      <c r="D480" t="s">
         <v>880</v>
-      </c>
-      <c r="D480" t="s">
-        <v>881</v>
       </c>
       <c r="E480">
         <v>13.99</v>
@@ -11923,10 +12053,10 @@
         <v>662</v>
       </c>
       <c r="C481" t="s">
+        <v>881</v>
+      </c>
+      <c r="D481" t="s">
         <v>882</v>
-      </c>
-      <c r="D481" t="s">
-        <v>883</v>
       </c>
       <c r="E481">
         <v>20.99</v>
@@ -11940,10 +12070,10 @@
         <v>662</v>
       </c>
       <c r="C482" t="s">
+        <v>883</v>
+      </c>
+      <c r="D482" t="s">
         <v>884</v>
-      </c>
-      <c r="D482" t="s">
-        <v>885</v>
       </c>
       <c r="E482">
         <v>17.989999999999998</v>
@@ -11957,10 +12087,10 @@
         <v>662</v>
       </c>
       <c r="C483" t="s">
+        <v>885</v>
+      </c>
+      <c r="D483" t="s">
         <v>886</v>
-      </c>
-      <c r="D483" t="s">
-        <v>887</v>
       </c>
       <c r="E483">
         <v>1.99</v>
@@ -11974,10 +12104,10 @@
         <v>662</v>
       </c>
       <c r="C484" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="D484" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="E484">
         <v>1.99</v>
@@ -11991,10 +12121,10 @@
         <v>662</v>
       </c>
       <c r="C485" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="D485" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="E485">
         <v>1.99</v>
@@ -12008,10 +12138,10 @@
         <v>662</v>
       </c>
       <c r="C486" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="D486" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="E486">
         <v>1.99</v>
@@ -12025,10 +12155,10 @@
         <v>662</v>
       </c>
       <c r="C487" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="D487" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="E487">
         <v>1.99</v>
@@ -12042,10 +12172,10 @@
         <v>662</v>
       </c>
       <c r="C488" t="s">
+        <v>891</v>
+      </c>
+      <c r="D488" t="s">
         <v>892</v>
-      </c>
-      <c r="D488" t="s">
-        <v>893</v>
       </c>
       <c r="E488">
         <v>1.99</v>
@@ -12059,10 +12189,10 @@
         <v>662</v>
       </c>
       <c r="C489" t="s">
+        <v>893</v>
+      </c>
+      <c r="D489" t="s">
         <v>894</v>
-      </c>
-      <c r="D489" t="s">
-        <v>895</v>
       </c>
       <c r="E489">
         <v>1.99</v>
@@ -12076,10 +12206,10 @@
         <v>662</v>
       </c>
       <c r="C490" t="s">
+        <v>895</v>
+      </c>
+      <c r="D490" t="s">
         <v>896</v>
-      </c>
-      <c r="D490" t="s">
-        <v>897</v>
       </c>
       <c r="E490">
         <v>1.99</v>
@@ -12093,10 +12223,10 @@
         <v>662</v>
       </c>
       <c r="C491" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="D491" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="E491">
         <v>1.99</v>
@@ -12110,10 +12240,10 @@
         <v>662</v>
       </c>
       <c r="C492" t="s">
+        <v>898</v>
+      </c>
+      <c r="D492" t="s">
         <v>899</v>
-      </c>
-      <c r="D492" t="s">
-        <v>900</v>
       </c>
       <c r="E492">
         <v>1.99</v>
@@ -12127,10 +12257,10 @@
         <v>662</v>
       </c>
       <c r="C493" t="s">
+        <v>900</v>
+      </c>
+      <c r="D493" t="s">
         <v>901</v>
-      </c>
-      <c r="D493" t="s">
-        <v>902</v>
       </c>
       <c r="E493">
         <v>1.99</v>
@@ -12144,10 +12274,10 @@
         <v>662</v>
       </c>
       <c r="C494" t="s">
+        <v>902</v>
+      </c>
+      <c r="D494" t="s">
         <v>903</v>
-      </c>
-      <c r="D494" t="s">
-        <v>904</v>
       </c>
       <c r="E494">
         <v>1.99</v>
@@ -12161,10 +12291,10 @@
         <v>662</v>
       </c>
       <c r="C495" t="s">
+        <v>904</v>
+      </c>
+      <c r="D495" t="s">
         <v>905</v>
-      </c>
-      <c r="D495" t="s">
-        <v>906</v>
       </c>
       <c r="E495">
         <v>1.99</v>
@@ -12178,10 +12308,10 @@
         <v>662</v>
       </c>
       <c r="C496" t="s">
+        <v>906</v>
+      </c>
+      <c r="D496" t="s">
         <v>907</v>
-      </c>
-      <c r="D496" t="s">
-        <v>908</v>
       </c>
       <c r="E496">
         <v>1.49</v>
@@ -12195,10 +12325,10 @@
         <v>662</v>
       </c>
       <c r="C497" t="s">
+        <v>908</v>
+      </c>
+      <c r="D497" t="s">
         <v>909</v>
-      </c>
-      <c r="D497" t="s">
-        <v>910</v>
       </c>
       <c r="E497">
         <v>1.49</v>
@@ -12212,10 +12342,10 @@
         <v>662</v>
       </c>
       <c r="C498" t="s">
+        <v>910</v>
+      </c>
+      <c r="D498" t="s">
         <v>911</v>
-      </c>
-      <c r="D498" t="s">
-        <v>912</v>
       </c>
       <c r="E498">
         <v>1.49</v>
@@ -12229,10 +12359,10 @@
         <v>662</v>
       </c>
       <c r="C499" t="s">
+        <v>912</v>
+      </c>
+      <c r="D499" t="s">
         <v>913</v>
-      </c>
-      <c r="D499" t="s">
-        <v>914</v>
       </c>
       <c r="E499">
         <v>1.49</v>
@@ -12246,10 +12376,10 @@
         <v>662</v>
       </c>
       <c r="C500" t="s">
+        <v>914</v>
+      </c>
+      <c r="D500" t="s">
         <v>915</v>
-      </c>
-      <c r="D500" t="s">
-        <v>916</v>
       </c>
       <c r="E500">
         <v>1.49</v>
@@ -12263,10 +12393,10 @@
         <v>662</v>
       </c>
       <c r="C501" t="s">
+        <v>916</v>
+      </c>
+      <c r="D501" t="s">
         <v>917</v>
-      </c>
-      <c r="D501" t="s">
-        <v>918</v>
       </c>
       <c r="E501">
         <v>1.49</v>
@@ -12280,10 +12410,10 @@
         <v>662</v>
       </c>
       <c r="C502" t="s">
+        <v>918</v>
+      </c>
+      <c r="D502" t="s">
         <v>919</v>
-      </c>
-      <c r="D502" t="s">
-        <v>920</v>
       </c>
       <c r="E502">
         <v>2.69</v>
@@ -12297,10 +12427,10 @@
         <v>662</v>
       </c>
       <c r="C503" t="s">
+        <v>920</v>
+      </c>
+      <c r="D503" t="s">
         <v>921</v>
-      </c>
-      <c r="D503" t="s">
-        <v>922</v>
       </c>
       <c r="E503">
         <v>2.69</v>
@@ -12314,10 +12444,10 @@
         <v>662</v>
       </c>
       <c r="C504" t="s">
+        <v>922</v>
+      </c>
+      <c r="D504" t="s">
         <v>923</v>
-      </c>
-      <c r="D504" t="s">
-        <v>924</v>
       </c>
       <c r="E504">
         <v>2.69</v>
@@ -12331,10 +12461,10 @@
         <v>662</v>
       </c>
       <c r="C505" t="s">
+        <v>924</v>
+      </c>
+      <c r="D505" t="s">
         <v>925</v>
-      </c>
-      <c r="D505" t="s">
-        <v>926</v>
       </c>
       <c r="E505">
         <v>2.69</v>
@@ -12348,10 +12478,10 @@
         <v>662</v>
       </c>
       <c r="C506" t="s">
+        <v>926</v>
+      </c>
+      <c r="D506" t="s">
         <v>927</v>
-      </c>
-      <c r="D506" t="s">
-        <v>928</v>
       </c>
       <c r="E506">
         <v>2.69</v>
@@ -12365,10 +12495,10 @@
         <v>662</v>
       </c>
       <c r="C507" t="s">
+        <v>928</v>
+      </c>
+      <c r="D507" t="s">
         <v>929</v>
-      </c>
-      <c r="D507" t="s">
-        <v>930</v>
       </c>
       <c r="E507">
         <v>2.69</v>
@@ -12382,10 +12512,10 @@
         <v>662</v>
       </c>
       <c r="C508" t="s">
+        <v>930</v>
+      </c>
+      <c r="D508" t="s">
         <v>931</v>
-      </c>
-      <c r="D508" t="s">
-        <v>932</v>
       </c>
       <c r="E508">
         <v>2.69</v>
@@ -12399,10 +12529,10 @@
         <v>662</v>
       </c>
       <c r="C509" t="s">
+        <v>932</v>
+      </c>
+      <c r="D509" t="s">
         <v>933</v>
-      </c>
-      <c r="D509" t="s">
-        <v>934</v>
       </c>
       <c r="E509">
         <v>2.69</v>
@@ -12416,10 +12546,10 @@
         <v>662</v>
       </c>
       <c r="C510" t="s">
+        <v>934</v>
+      </c>
+      <c r="D510" t="s">
         <v>935</v>
-      </c>
-      <c r="D510" t="s">
-        <v>936</v>
       </c>
     </row>
     <row r="511" spans="1:5" x14ac:dyDescent="0.25">
@@ -12430,10 +12560,10 @@
         <v>662</v>
       </c>
       <c r="C511" t="s">
+        <v>936</v>
+      </c>
+      <c r="D511" t="s">
         <v>937</v>
-      </c>
-      <c r="D511" t="s">
-        <v>938</v>
       </c>
     </row>
     <row r="512" spans="1:5" x14ac:dyDescent="0.25">
@@ -12444,10 +12574,10 @@
         <v>662</v>
       </c>
       <c r="C512" t="s">
+        <v>938</v>
+      </c>
+      <c r="D512" t="s">
         <v>939</v>
-      </c>
-      <c r="D512" t="s">
-        <v>940</v>
       </c>
     </row>
     <row r="513" spans="1:5" x14ac:dyDescent="0.25">
@@ -12458,10 +12588,10 @@
         <v>662</v>
       </c>
       <c r="C513" t="s">
+        <v>940</v>
+      </c>
+      <c r="D513" t="s">
         <v>941</v>
-      </c>
-      <c r="D513" t="s">
-        <v>942</v>
       </c>
     </row>
     <row r="514" spans="1:5" x14ac:dyDescent="0.25">
@@ -12472,10 +12602,10 @@
         <v>662</v>
       </c>
       <c r="C514" t="s">
+        <v>942</v>
+      </c>
+      <c r="D514" t="s">
         <v>943</v>
-      </c>
-      <c r="D514" t="s">
-        <v>944</v>
       </c>
     </row>
     <row r="515" spans="1:5" x14ac:dyDescent="0.25">
@@ -12486,10 +12616,10 @@
         <v>662</v>
       </c>
       <c r="C515" t="s">
+        <v>944</v>
+      </c>
+      <c r="D515" t="s">
         <v>945</v>
-      </c>
-      <c r="D515" t="s">
-        <v>946</v>
       </c>
     </row>
     <row r="516" spans="1:5" x14ac:dyDescent="0.25">
@@ -12500,10 +12630,10 @@
         <v>662</v>
       </c>
       <c r="C516" t="s">
+        <v>946</v>
+      </c>
+      <c r="D516" t="s">
         <v>947</v>
-      </c>
-      <c r="D516" t="s">
-        <v>948</v>
       </c>
     </row>
     <row r="517" spans="1:5" x14ac:dyDescent="0.25">
@@ -12514,10 +12644,10 @@
         <v>662</v>
       </c>
       <c r="C517" t="s">
+        <v>948</v>
+      </c>
+      <c r="D517" t="s">
         <v>949</v>
-      </c>
-      <c r="D517" t="s">
-        <v>950</v>
       </c>
     </row>
     <row r="518" spans="1:5" x14ac:dyDescent="0.25">
@@ -12528,10 +12658,10 @@
         <v>662</v>
       </c>
       <c r="C518" t="s">
+        <v>950</v>
+      </c>
+      <c r="D518" t="s">
         <v>951</v>
-      </c>
-      <c r="D518" t="s">
-        <v>952</v>
       </c>
     </row>
     <row r="519" spans="1:5" x14ac:dyDescent="0.25">
@@ -12542,10 +12672,10 @@
         <v>662</v>
       </c>
       <c r="C519" t="s">
+        <v>952</v>
+      </c>
+      <c r="D519" t="s">
         <v>953</v>
-      </c>
-      <c r="D519" t="s">
-        <v>954</v>
       </c>
     </row>
     <row r="520" spans="1:5" x14ac:dyDescent="0.25">
@@ -12556,10 +12686,10 @@
         <v>662</v>
       </c>
       <c r="C520" t="s">
+        <v>954</v>
+      </c>
+      <c r="D520" t="s">
         <v>955</v>
-      </c>
-      <c r="D520" t="s">
-        <v>956</v>
       </c>
     </row>
     <row r="521" spans="1:5" x14ac:dyDescent="0.25">
@@ -12570,10 +12700,10 @@
         <v>662</v>
       </c>
       <c r="C521" t="s">
+        <v>956</v>
+      </c>
+      <c r="D521" t="s">
         <v>957</v>
-      </c>
-      <c r="D521" t="s">
-        <v>958</v>
       </c>
     </row>
     <row r="522" spans="1:5" x14ac:dyDescent="0.25">
@@ -12584,10 +12714,10 @@
         <v>662</v>
       </c>
       <c r="C522" t="s">
+        <v>958</v>
+      </c>
+      <c r="D522" t="s">
         <v>959</v>
-      </c>
-      <c r="D522" t="s">
-        <v>960</v>
       </c>
     </row>
     <row r="523" spans="1:5" x14ac:dyDescent="0.25">
@@ -12598,10 +12728,10 @@
         <v>662</v>
       </c>
       <c r="C523" t="s">
+        <v>960</v>
+      </c>
+      <c r="D523" t="s">
         <v>961</v>
-      </c>
-      <c r="D523" t="s">
-        <v>962</v>
       </c>
     </row>
     <row r="524" spans="1:5" x14ac:dyDescent="0.25">
@@ -12612,10 +12742,10 @@
         <v>662</v>
       </c>
       <c r="C524" t="s">
+        <v>962</v>
+      </c>
+      <c r="D524" t="s">
         <v>963</v>
-      </c>
-      <c r="D524" t="s">
-        <v>964</v>
       </c>
       <c r="E524">
         <v>1.99</v>
@@ -12629,10 +12759,10 @@
         <v>662</v>
       </c>
       <c r="C525" t="s">
+        <v>964</v>
+      </c>
+      <c r="D525" t="s">
         <v>965</v>
-      </c>
-      <c r="D525" t="s">
-        <v>966</v>
       </c>
     </row>
     <row r="526" spans="1:5" x14ac:dyDescent="0.25">
@@ -12643,10 +12773,10 @@
         <v>662</v>
       </c>
       <c r="C526" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="D526" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="527" spans="1:5" x14ac:dyDescent="0.25">
@@ -12657,10 +12787,10 @@
         <v>662</v>
       </c>
       <c r="C527" t="s">
+        <v>967</v>
+      </c>
+      <c r="D527" t="s">
         <v>968</v>
-      </c>
-      <c r="D527" t="s">
-        <v>969</v>
       </c>
     </row>
     <row r="528" spans="1:5" x14ac:dyDescent="0.25">
@@ -12671,10 +12801,10 @@
         <v>662</v>
       </c>
       <c r="C528" t="s">
+        <v>969</v>
+      </c>
+      <c r="D528" t="s">
         <v>970</v>
-      </c>
-      <c r="D528" t="s">
-        <v>971</v>
       </c>
     </row>
     <row r="529" spans="1:5" x14ac:dyDescent="0.25">
@@ -12685,10 +12815,10 @@
         <v>662</v>
       </c>
       <c r="C529" t="s">
+        <v>971</v>
+      </c>
+      <c r="D529" t="s">
         <v>972</v>
-      </c>
-      <c r="D529" t="s">
-        <v>973</v>
       </c>
     </row>
     <row r="530" spans="1:5" x14ac:dyDescent="0.25">
@@ -12699,10 +12829,10 @@
         <v>662</v>
       </c>
       <c r="C530" t="s">
+        <v>973</v>
+      </c>
+      <c r="D530" t="s">
         <v>974</v>
-      </c>
-      <c r="D530" t="s">
-        <v>975</v>
       </c>
     </row>
     <row r="531" spans="1:5" x14ac:dyDescent="0.25">
@@ -12710,13 +12840,13 @@
         <v>244423</v>
       </c>
       <c r="B531" t="s">
+        <v>975</v>
+      </c>
+      <c r="C531" t="s">
         <v>976</v>
       </c>
-      <c r="C531" t="s">
+      <c r="D531" t="s">
         <v>977</v>
-      </c>
-      <c r="D531" t="s">
-        <v>978</v>
       </c>
       <c r="E531">
         <v>5.69</v>
@@ -12727,13 +12857,13 @@
         <v>305261</v>
       </c>
       <c r="B532" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="C532" t="s">
+        <v>978</v>
+      </c>
+      <c r="D532" t="s">
         <v>979</v>
-      </c>
-      <c r="D532" t="s">
-        <v>980</v>
       </c>
     </row>
     <row r="533" spans="1:5" x14ac:dyDescent="0.25">
@@ -12741,13 +12871,13 @@
         <v>320467</v>
       </c>
       <c r="B533" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="C533" t="s">
+        <v>980</v>
+      </c>
+      <c r="D533" t="s">
         <v>981</v>
-      </c>
-      <c r="D533" t="s">
-        <v>982</v>
       </c>
     </row>
     <row r="534" spans="1:5" x14ac:dyDescent="0.25">
@@ -12755,13 +12885,13 @@
         <v>303008</v>
       </c>
       <c r="B534" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="C534" t="s">
+        <v>982</v>
+      </c>
+      <c r="D534" t="s">
         <v>983</v>
-      </c>
-      <c r="D534" t="s">
-        <v>984</v>
       </c>
       <c r="E534">
         <v>15.99</v>
@@ -12772,13 +12902,13 @@
         <v>253878</v>
       </c>
       <c r="B535" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="C535" t="s">
+        <v>984</v>
+      </c>
+      <c r="D535" t="s">
         <v>985</v>
-      </c>
-      <c r="D535" t="s">
-        <v>986</v>
       </c>
     </row>
     <row r="536" spans="1:5" x14ac:dyDescent="0.25">
@@ -12786,13 +12916,13 @@
         <v>253877</v>
       </c>
       <c r="B536" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="C536" t="s">
+        <v>986</v>
+      </c>
+      <c r="D536" t="s">
         <v>987</v>
-      </c>
-      <c r="D536" t="s">
-        <v>988</v>
       </c>
     </row>
     <row r="537" spans="1:5" x14ac:dyDescent="0.25">
@@ -12800,13 +12930,13 @@
         <v>244424</v>
       </c>
       <c r="B537" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="C537" t="s">
+        <v>988</v>
+      </c>
+      <c r="D537" t="s">
         <v>989</v>
-      </c>
-      <c r="D537" t="s">
-        <v>990</v>
       </c>
     </row>
     <row r="538" spans="1:5" x14ac:dyDescent="0.25">
@@ -12814,13 +12944,13 @@
         <v>244426</v>
       </c>
       <c r="B538" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="C538" t="s">
+        <v>990</v>
+      </c>
+      <c r="D538" t="s">
         <v>991</v>
-      </c>
-      <c r="D538" t="s">
-        <v>992</v>
       </c>
     </row>
     <row r="539" spans="1:5" x14ac:dyDescent="0.25">
@@ -12828,13 +12958,13 @@
         <v>253880</v>
       </c>
       <c r="B539" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="C539" t="s">
+        <v>992</v>
+      </c>
+      <c r="D539" t="s">
         <v>993</v>
-      </c>
-      <c r="D539" t="s">
-        <v>994</v>
       </c>
     </row>
     <row r="540" spans="1:5" x14ac:dyDescent="0.25">
@@ -12842,13 +12972,13 @@
         <v>302661</v>
       </c>
       <c r="B540" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="C540" t="s">
+        <v>994</v>
+      </c>
+      <c r="D540" t="s">
         <v>995</v>
-      </c>
-      <c r="D540" t="s">
-        <v>996</v>
       </c>
     </row>
     <row r="541" spans="1:5" x14ac:dyDescent="0.25">
@@ -12856,13 +12986,13 @@
         <v>302660</v>
       </c>
       <c r="B541" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="C541" t="s">
+        <v>996</v>
+      </c>
+      <c r="D541" t="s">
         <v>997</v>
-      </c>
-      <c r="D541" t="s">
-        <v>998</v>
       </c>
     </row>
     <row r="542" spans="1:5" x14ac:dyDescent="0.25">
@@ -12870,13 +13000,13 @@
         <v>318892</v>
       </c>
       <c r="B542" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="C542" t="s">
+        <v>998</v>
+      </c>
+      <c r="D542" t="s">
         <v>999</v>
-      </c>
-      <c r="D542" t="s">
-        <v>1000</v>
       </c>
       <c r="E542">
         <v>4.99</v>
@@ -12887,13 +13017,13 @@
         <v>244422</v>
       </c>
       <c r="B543" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="C543" t="s">
+        <v>1000</v>
+      </c>
+      <c r="D543" t="s">
         <v>1001</v>
-      </c>
-      <c r="D543" t="s">
-        <v>1002</v>
       </c>
       <c r="E543">
         <v>4.99</v>
@@ -12904,13 +13034,13 @@
         <v>312640</v>
       </c>
       <c r="B544" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="C544" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D544" t="s">
         <v>1003</v>
-      </c>
-      <c r="D544" t="s">
-        <v>1004</v>
       </c>
       <c r="E544">
         <v>4.99</v>
@@ -12921,13 +13051,13 @@
         <v>303516</v>
       </c>
       <c r="B545" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="C545" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D545" t="s">
         <v>1005</v>
-      </c>
-      <c r="D545" t="s">
-        <v>1006</v>
       </c>
       <c r="E545">
         <v>4.99</v>
@@ -12938,13 +13068,13 @@
         <v>244425</v>
       </c>
       <c r="B546" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="C546" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D546" t="s">
         <v>1007</v>
-      </c>
-      <c r="D546" t="s">
-        <v>1008</v>
       </c>
       <c r="E546">
         <v>4.99</v>
@@ -12955,13 +13085,13 @@
         <v>312067</v>
       </c>
       <c r="B547" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="C547" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D547" t="s">
         <v>1009</v>
-      </c>
-      <c r="D547" t="s">
-        <v>1010</v>
       </c>
       <c r="E547">
         <v>4.99</v>
@@ -12972,13 +13102,13 @@
         <v>253879</v>
       </c>
       <c r="B548" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="C548" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D548" t="s">
         <v>1011</v>
-      </c>
-      <c r="D548" t="s">
-        <v>1012</v>
       </c>
       <c r="E548">
         <v>4.99</v>
@@ -12989,13 +13119,13 @@
         <v>244427</v>
       </c>
       <c r="B549" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="C549" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D549" t="s">
         <v>1013</v>
-      </c>
-      <c r="D549" t="s">
-        <v>1014</v>
       </c>
       <c r="E549">
         <v>4.99</v>
@@ -13006,13 +13136,13 @@
         <v>302658</v>
       </c>
       <c r="B550" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="C550" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D550" t="s">
         <v>1015</v>
-      </c>
-      <c r="D550" t="s">
-        <v>1016</v>
       </c>
       <c r="E550">
         <v>4.99</v>
@@ -13023,13 +13153,13 @@
         <v>302659</v>
       </c>
       <c r="B551" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="C551" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D551" t="s">
         <v>1017</v>
-      </c>
-      <c r="D551" t="s">
-        <v>1018</v>
       </c>
       <c r="E551">
         <v>4.99</v>
@@ -13040,13 +13170,13 @@
         <v>312639</v>
       </c>
       <c r="B552" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="C552" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D552" t="s">
         <v>1019</v>
-      </c>
-      <c r="D552" t="s">
-        <v>1020</v>
       </c>
       <c r="E552">
         <v>4.99</v>
@@ -13057,13 +13187,13 @@
         <v>303517</v>
       </c>
       <c r="B553" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="C553" t="s">
+        <v>1020</v>
+      </c>
+      <c r="D553" t="s">
         <v>1021</v>
-      </c>
-      <c r="D553" t="s">
-        <v>1022</v>
       </c>
       <c r="E553">
         <v>4.99</v>
@@ -13074,13 +13204,13 @@
         <v>273004</v>
       </c>
       <c r="B554" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="C554" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D554" t="s">
         <v>1023</v>
-      </c>
-      <c r="D554" t="s">
-        <v>1024</v>
       </c>
       <c r="E554">
         <v>8.49</v>
@@ -13091,13 +13221,13 @@
         <v>273000</v>
       </c>
       <c r="B555" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="C555" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="D555" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="E555">
         <v>8.49</v>
@@ -13108,13 +13238,13 @@
         <v>273005</v>
       </c>
       <c r="B556" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="C556" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D556" t="s">
         <v>1026</v>
-      </c>
-      <c r="D556" t="s">
-        <v>1027</v>
       </c>
       <c r="E556">
         <v>8.49</v>
@@ -13125,13 +13255,13 @@
         <v>102287</v>
       </c>
       <c r="B557" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="C557" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D557" t="s">
         <v>1028</v>
-      </c>
-      <c r="D557" t="s">
-        <v>1029</v>
       </c>
     </row>
     <row r="558" spans="1:5" x14ac:dyDescent="0.25">
@@ -13139,13 +13269,13 @@
         <v>102282</v>
       </c>
       <c r="B558" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="C558" t="s">
+        <v>1029</v>
+      </c>
+      <c r="D558" t="s">
         <v>1030</v>
-      </c>
-      <c r="D558" t="s">
-        <v>1031</v>
       </c>
       <c r="E558">
         <v>8.69</v>
@@ -13156,13 +13286,13 @@
         <v>229014</v>
       </c>
       <c r="B559" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C559" t="s">
         <v>1032</v>
       </c>
-      <c r="C559" t="s">
-        <v>1033</v>
-      </c>
       <c r="D559" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="E559">
         <v>12.99</v>
@@ -13173,13 +13303,13 @@
         <v>286589</v>
       </c>
       <c r="B560" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="C560" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="D560" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="E560">
         <v>9.99</v>
@@ -13190,13 +13320,13 @@
         <v>287184</v>
       </c>
       <c r="B561" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="C561" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="D561" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="E561">
         <v>9.99</v>
@@ -13207,13 +13337,13 @@
         <v>324170</v>
       </c>
       <c r="B562" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="C562" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="D562" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="E562">
         <v>9.99</v>
@@ -13224,13 +13354,13 @@
         <v>286326</v>
       </c>
       <c r="B563" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="C563" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="D563" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="E563">
         <v>9.99</v>
@@ -13241,13 +13371,13 @@
         <v>287177</v>
       </c>
       <c r="B564" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="C564" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="D564" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="E564">
         <v>9.99</v>
@@ -13258,13 +13388,13 @@
         <v>161871</v>
       </c>
       <c r="B565" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="C565" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D565" t="s">
         <v>1039</v>
-      </c>
-      <c r="D565" t="s">
-        <v>1040</v>
       </c>
       <c r="E565">
         <v>7.99</v>
@@ -13275,13 +13405,13 @@
         <v>108686</v>
       </c>
       <c r="B566" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="C566" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D566" t="s">
         <v>1041</v>
-      </c>
-      <c r="D566" t="s">
-        <v>1042</v>
       </c>
       <c r="E566">
         <v>7.99</v>
@@ -13292,13 +13422,13 @@
         <v>104406</v>
       </c>
       <c r="B567" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="C567" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="D567" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="568" spans="1:5" x14ac:dyDescent="0.25">
@@ -13306,13 +13436,13 @@
         <v>104404</v>
       </c>
       <c r="B568" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="C568" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D568" t="s">
         <v>1044</v>
-      </c>
-      <c r="D568" t="s">
-        <v>1045</v>
       </c>
     </row>
     <row r="569" spans="1:5" x14ac:dyDescent="0.25">
@@ -13320,13 +13450,13 @@
         <v>104403</v>
       </c>
       <c r="B569" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="C569" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D569" t="s">
         <v>1046</v>
-      </c>
-      <c r="D569" t="s">
-        <v>1047</v>
       </c>
       <c r="E569">
         <v>9.99</v>
@@ -13337,13 +13467,13 @@
         <v>104410</v>
       </c>
       <c r="B570" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="C570" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D570" t="s">
         <v>1048</v>
-      </c>
-      <c r="D570" t="s">
-        <v>1049</v>
       </c>
     </row>
     <row r="571" spans="1:5" x14ac:dyDescent="0.25">
@@ -13351,13 +13481,13 @@
         <v>286271</v>
       </c>
       <c r="B571" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="C571" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="D571" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="E571">
         <v>7.99</v>
@@ -13368,13 +13498,13 @@
         <v>104424</v>
       </c>
       <c r="B572" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="C572" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D572" t="s">
         <v>1051</v>
-      </c>
-      <c r="D572" t="s">
-        <v>1052</v>
       </c>
       <c r="E572">
         <v>7.99</v>
@@ -13385,13 +13515,13 @@
         <v>122984</v>
       </c>
       <c r="B573" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="C573" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D573" t="s">
         <v>1053</v>
-      </c>
-      <c r="D573" t="s">
-        <v>1054</v>
       </c>
       <c r="E573">
         <v>9.69</v>
@@ -13402,13 +13532,13 @@
         <v>104405</v>
       </c>
       <c r="B574" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="C574" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D574" t="s">
         <v>1055</v>
-      </c>
-      <c r="D574" t="s">
-        <v>1056</v>
       </c>
     </row>
     <row r="575" spans="1:5" x14ac:dyDescent="0.25">
@@ -13416,13 +13546,13 @@
         <v>102237</v>
       </c>
       <c r="B575" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C575" t="s">
         <v>1057</v>
       </c>
-      <c r="C575" t="s">
+      <c r="D575" t="s">
         <v>1058</v>
-      </c>
-      <c r="D575" t="s">
-        <v>1059</v>
       </c>
       <c r="E575">
         <v>27.99</v>
@@ -13433,13 +13563,13 @@
         <v>264452</v>
       </c>
       <c r="B576" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="C576" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="D576" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="E576">
         <v>5.99</v>
@@ -13450,13 +13580,13 @@
         <v>298700</v>
       </c>
       <c r="B577" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C577" t="s">
         <v>1061</v>
       </c>
-      <c r="C577" t="s">
+      <c r="D577" t="s">
         <v>1062</v>
-      </c>
-      <c r="D577" t="s">
-        <v>1063</v>
       </c>
       <c r="E577">
         <v>3.99</v>
@@ -13467,13 +13597,13 @@
         <v>239441</v>
       </c>
       <c r="B578" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="C578" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D578" t="s">
         <v>1064</v>
-      </c>
-      <c r="D578" t="s">
-        <v>1065</v>
       </c>
       <c r="E578">
         <v>2.99</v>
@@ -13484,13 +13614,13 @@
         <v>247800</v>
       </c>
       <c r="B579" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="C579" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D579" t="s">
         <v>1066</v>
-      </c>
-      <c r="D579" t="s">
-        <v>1067</v>
       </c>
     </row>
     <row r="580" spans="1:5" x14ac:dyDescent="0.25">
@@ -13498,13 +13628,13 @@
         <v>267604</v>
       </c>
       <c r="B580" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="C580" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D580" t="s">
         <v>1068</v>
-      </c>
-      <c r="D580" t="s">
-        <v>1069</v>
       </c>
       <c r="E580">
         <v>5.99</v>
@@ -13515,13 +13645,13 @@
         <v>239382</v>
       </c>
       <c r="B581" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="C581" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D581" t="s">
         <v>1070</v>
-      </c>
-      <c r="D581" t="s">
-        <v>1071</v>
       </c>
       <c r="E581">
         <v>2.69</v>
@@ -13532,13 +13662,13 @@
         <v>168466</v>
       </c>
       <c r="B582" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="C582" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D582" t="s">
         <v>1072</v>
-      </c>
-      <c r="D582" t="s">
-        <v>1073</v>
       </c>
       <c r="E582">
         <v>6.19</v>
@@ -13549,13 +13679,13 @@
         <v>242930</v>
       </c>
       <c r="B583" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="C583" t="s">
+        <v>1073</v>
+      </c>
+      <c r="D583" t="s">
         <v>1074</v>
-      </c>
-      <c r="D583" t="s">
-        <v>1075</v>
       </c>
     </row>
     <row r="584" spans="1:5" x14ac:dyDescent="0.25">
@@ -13563,13 +13693,13 @@
         <v>249597</v>
       </c>
       <c r="B584" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="C584" t="s">
+        <v>1075</v>
+      </c>
+      <c r="D584" t="s">
         <v>1076</v>
-      </c>
-      <c r="D584" t="s">
-        <v>1077</v>
       </c>
       <c r="E584">
         <v>6.79</v>
@@ -13580,13 +13710,13 @@
         <v>303282</v>
       </c>
       <c r="B585" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="C585" t="s">
+        <v>1077</v>
+      </c>
+      <c r="D585" t="s">
         <v>1078</v>
-      </c>
-      <c r="D585" t="s">
-        <v>1079</v>
       </c>
       <c r="E585">
         <v>6.19</v>
@@ -13597,13 +13727,13 @@
         <v>298123</v>
       </c>
       <c r="B586" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="C586" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D586" t="s">
         <v>1080</v>
-      </c>
-      <c r="D586" t="s">
-        <v>1081</v>
       </c>
       <c r="E586">
         <v>6.19</v>
@@ -13614,13 +13744,13 @@
         <v>157496</v>
       </c>
       <c r="B587" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="C587" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D587" t="s">
         <v>1082</v>
-      </c>
-      <c r="D587" t="s">
-        <v>1083</v>
       </c>
       <c r="E587">
         <v>11.99</v>
@@ -13631,13 +13761,13 @@
         <v>184034</v>
       </c>
       <c r="B588" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="C588" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D588" t="s">
         <v>1084</v>
-      </c>
-      <c r="D588" t="s">
-        <v>1085</v>
       </c>
       <c r="E588">
         <v>5.69</v>
@@ -13648,13 +13778,13 @@
         <v>286362</v>
       </c>
       <c r="B589" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="C589" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D589" t="s">
         <v>1086</v>
-      </c>
-      <c r="D589" t="s">
-        <v>1087</v>
       </c>
       <c r="E589">
         <v>9.49</v>
@@ -13665,13 +13795,13 @@
         <v>259589</v>
       </c>
       <c r="B590" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="C590" t="s">
+        <v>1087</v>
+      </c>
+      <c r="D590" t="s">
         <v>1088</v>
-      </c>
-      <c r="D590" t="s">
-        <v>1089</v>
       </c>
       <c r="E590">
         <v>10.59</v>
@@ -13682,13 +13812,13 @@
         <v>220499</v>
       </c>
       <c r="B591" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="C591" t="s">
+        <v>1089</v>
+      </c>
+      <c r="D591" t="s">
         <v>1090</v>
-      </c>
-      <c r="D591" t="s">
-        <v>1091</v>
       </c>
       <c r="E591">
         <v>7.99</v>
@@ -13699,13 +13829,13 @@
         <v>239446</v>
       </c>
       <c r="B592" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C592" t="s">
         <v>1092</v>
       </c>
-      <c r="C592" t="s">
+      <c r="D592" t="s">
         <v>1093</v>
-      </c>
-      <c r="D592" t="s">
-        <v>1094</v>
       </c>
     </row>
     <row r="593" spans="1:5" x14ac:dyDescent="0.25">
@@ -13713,13 +13843,13 @@
         <v>298701</v>
       </c>
       <c r="B593" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="C593" t="s">
+        <v>1094</v>
+      </c>
+      <c r="D593" t="s">
         <v>1095</v>
-      </c>
-      <c r="D593" t="s">
-        <v>1096</v>
       </c>
       <c r="E593">
         <v>4.09</v>
@@ -13730,13 +13860,13 @@
         <v>287369</v>
       </c>
       <c r="B594" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="C594" t="s">
+        <v>1096</v>
+      </c>
+      <c r="D594" t="s">
         <v>1097</v>
-      </c>
-      <c r="D594" t="s">
-        <v>1098</v>
       </c>
     </row>
     <row r="595" spans="1:5" x14ac:dyDescent="0.25">
@@ -13744,13 +13874,13 @@
         <v>168712</v>
       </c>
       <c r="B595" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="C595" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D595" t="s">
         <v>1099</v>
-      </c>
-      <c r="D595" t="s">
-        <v>1100</v>
       </c>
       <c r="E595">
         <v>2.99</v>
@@ -13761,13 +13891,13 @@
         <v>170451</v>
       </c>
       <c r="B596" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="C596" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D596" t="s">
         <v>1101</v>
-      </c>
-      <c r="D596" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="597" spans="1:5" x14ac:dyDescent="0.25">
@@ -13775,13 +13905,13 @@
         <v>157068</v>
       </c>
       <c r="B597" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="C597" t="s">
+        <v>1102</v>
+      </c>
+      <c r="D597" t="s">
         <v>1103</v>
-      </c>
-      <c r="D597" t="s">
-        <v>1104</v>
       </c>
       <c r="E597">
         <v>3.49</v>
@@ -13792,13 +13922,13 @@
         <v>313599</v>
       </c>
       <c r="B598" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="C598" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D598" t="s">
         <v>1105</v>
-      </c>
-      <c r="D598" t="s">
-        <v>1106</v>
       </c>
       <c r="E598">
         <v>3.99</v>
@@ -13809,13 +13939,13 @@
         <v>177250</v>
       </c>
       <c r="B599" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="C599" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D599" t="s">
         <v>1107</v>
-      </c>
-      <c r="D599" t="s">
-        <v>1108</v>
       </c>
     </row>
     <row r="600" spans="1:5" x14ac:dyDescent="0.25">
@@ -13823,13 +13953,13 @@
         <v>303283</v>
       </c>
       <c r="B600" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="C600" t="s">
+        <v>1108</v>
+      </c>
+      <c r="D600" t="s">
         <v>1109</v>
-      </c>
-      <c r="D600" t="s">
-        <v>1110</v>
       </c>
       <c r="E600">
         <v>5.99</v>
@@ -13840,13 +13970,13 @@
         <v>309102</v>
       </c>
       <c r="B601" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="C601" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D601" t="s">
         <v>1111</v>
-      </c>
-      <c r="D601" t="s">
-        <v>1112</v>
       </c>
       <c r="E601">
         <v>6.19</v>
@@ -13857,13 +13987,13 @@
         <v>108423</v>
       </c>
       <c r="B602" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="C602" t="s">
+        <v>1112</v>
+      </c>
+      <c r="D602" t="s">
         <v>1113</v>
-      </c>
-      <c r="D602" t="s">
-        <v>1114</v>
       </c>
       <c r="E602">
         <v>6.99</v>
@@ -13874,13 +14004,13 @@
         <v>265727</v>
       </c>
       <c r="B603" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="C603" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D603" t="s">
         <v>1115</v>
-      </c>
-      <c r="D603" t="s">
-        <v>1116</v>
       </c>
       <c r="E603">
         <v>4.59</v>
@@ -13891,13 +14021,13 @@
         <v>324556</v>
       </c>
       <c r="B604" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="C604" t="s">
+        <v>1116</v>
+      </c>
+      <c r="D604" t="s">
         <v>1117</v>
-      </c>
-      <c r="D604" t="s">
-        <v>1118</v>
       </c>
       <c r="E604">
         <v>44.89</v>
@@ -13908,13 +14038,13 @@
         <v>107376</v>
       </c>
       <c r="B605" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="C605" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D605" t="s">
         <v>1119</v>
-      </c>
-      <c r="D605" t="s">
-        <v>1120</v>
       </c>
     </row>
     <row r="606" spans="1:5" x14ac:dyDescent="0.25">
@@ -13922,13 +14052,13 @@
         <v>259153</v>
       </c>
       <c r="B606" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="C606" t="s">
+        <v>1120</v>
+      </c>
+      <c r="D606" t="s">
         <v>1121</v>
-      </c>
-      <c r="D606" t="s">
-        <v>1122</v>
       </c>
       <c r="E606">
         <v>4.79</v>
@@ -13939,13 +14069,13 @@
         <v>102242</v>
       </c>
       <c r="B607" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C607" t="s">
         <v>1123</v>
       </c>
-      <c r="C607" t="s">
+      <c r="D607" t="s">
         <v>1124</v>
-      </c>
-      <c r="D607" t="s">
-        <v>1125</v>
       </c>
       <c r="E607">
         <v>14.99</v>
@@ -13956,13 +14086,13 @@
         <v>107799</v>
       </c>
       <c r="B608" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="C608" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D608" t="s">
         <v>1126</v>
-      </c>
-      <c r="D608" t="s">
-        <v>1127</v>
       </c>
       <c r="E608">
         <v>10.99</v>
@@ -13973,13 +14103,13 @@
         <v>293188</v>
       </c>
       <c r="B609" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="C609" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D609" t="s">
         <v>1128</v>
-      </c>
-      <c r="D609" t="s">
-        <v>1129</v>
       </c>
     </row>
     <row r="610" spans="1:5" x14ac:dyDescent="0.25">
@@ -13987,13 +14117,13 @@
         <v>102085</v>
       </c>
       <c r="B610" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="C610" t="s">
+        <v>1129</v>
+      </c>
+      <c r="D610" t="s">
         <v>1130</v>
-      </c>
-      <c r="D610" t="s">
-        <v>1131</v>
       </c>
     </row>
     <row r="611" spans="1:5" x14ac:dyDescent="0.25">
@@ -14001,13 +14131,13 @@
         <v>215568</v>
       </c>
       <c r="B611" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="C611" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="D611" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="612" spans="1:5" x14ac:dyDescent="0.25">
@@ -14015,13 +14145,13 @@
         <v>157976</v>
       </c>
       <c r="B612" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="C612" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="D612" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="E612">
         <v>59.99</v>
@@ -14032,13 +14162,13 @@
         <v>174010</v>
       </c>
       <c r="B613" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="C613" t="s">
+        <v>1133</v>
+      </c>
+      <c r="D613" t="s">
         <v>1134</v>
-      </c>
-      <c r="D613" t="s">
-        <v>1135</v>
       </c>
     </row>
     <row r="614" spans="1:5" x14ac:dyDescent="0.25">
@@ -14046,13 +14176,13 @@
         <v>158451</v>
       </c>
       <c r="B614" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="C614" t="s">
+        <v>1135</v>
+      </c>
+      <c r="D614" t="s">
         <v>1136</v>
-      </c>
-      <c r="D614" t="s">
-        <v>1137</v>
       </c>
       <c r="E614">
         <v>29.99</v>
@@ -14063,13 +14193,13 @@
         <v>301843</v>
       </c>
       <c r="B615" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="C615" t="s">
+        <v>1137</v>
+      </c>
+      <c r="D615" t="s">
         <v>1138</v>
-      </c>
-      <c r="D615" t="s">
-        <v>1139</v>
       </c>
     </row>
     <row r="616" spans="1:5" x14ac:dyDescent="0.25">
@@ -14077,13 +14207,13 @@
         <v>219274</v>
       </c>
       <c r="B616" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="C616" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="D616" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="617" spans="1:5" x14ac:dyDescent="0.25">
@@ -14091,13 +14221,13 @@
         <v>230698</v>
       </c>
       <c r="B617" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="C617" t="s">
+        <v>1140</v>
+      </c>
+      <c r="D617" t="s">
         <v>1141</v>
-      </c>
-      <c r="D617" t="s">
-        <v>1142</v>
       </c>
       <c r="E617">
         <v>259.99</v>
@@ -14108,13 +14238,13 @@
         <v>206930</v>
       </c>
       <c r="B618" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="C618" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="D618" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="619" spans="1:5" x14ac:dyDescent="0.25">
@@ -14122,13 +14252,13 @@
         <v>134156</v>
       </c>
       <c r="B619" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="C619" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="D619" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E619">
         <v>59.99</v>
@@ -14139,13 +14269,13 @@
         <v>102087</v>
       </c>
       <c r="B620" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="C620" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="D620" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="E620">
         <v>54.99</v>
@@ -14156,13 +14286,13 @@
         <v>201454</v>
       </c>
       <c r="B621" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="C621" t="s">
+        <v>1145</v>
+      </c>
+      <c r="D621" t="s">
         <v>1146</v>
-      </c>
-      <c r="D621" t="s">
-        <v>1147</v>
       </c>
       <c r="E621">
         <v>85.99</v>
@@ -14173,13 +14303,13 @@
         <v>110373</v>
       </c>
       <c r="B622" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="C622" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D622" t="s">
         <v>1148</v>
-      </c>
-      <c r="D622" t="s">
-        <v>1149</v>
       </c>
     </row>
     <row r="623" spans="1:5" x14ac:dyDescent="0.25">
@@ -14187,13 +14317,13 @@
         <v>102071</v>
       </c>
       <c r="B623" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="C623" t="s">
+        <v>1149</v>
+      </c>
+      <c r="D623" t="s">
         <v>1150</v>
-      </c>
-      <c r="D623" t="s">
-        <v>1151</v>
       </c>
       <c r="E623">
         <v>99.99</v>
@@ -14204,13 +14334,13 @@
         <v>137381</v>
       </c>
       <c r="B624" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="C624" t="s">
+        <v>1151</v>
+      </c>
+      <c r="D624" t="s">
         <v>1152</v>
-      </c>
-      <c r="D624" t="s">
-        <v>1153</v>
       </c>
       <c r="E624">
         <v>128.99</v>
@@ -14221,13 +14351,13 @@
         <v>248750</v>
       </c>
       <c r="B625" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="C625" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D625" t="s">
         <v>1154</v>
-      </c>
-      <c r="D625" t="s">
-        <v>1155</v>
       </c>
       <c r="E625">
         <v>55.99</v>
@@ -14238,13 +14368,13 @@
         <v>102077</v>
       </c>
       <c r="B626" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="C626" t="s">
+        <v>1155</v>
+      </c>
+      <c r="D626" t="s">
         <v>1156</v>
-      </c>
-      <c r="D626" t="s">
-        <v>1157</v>
       </c>
     </row>
     <row r="627" spans="1:5" x14ac:dyDescent="0.25">
@@ -14252,13 +14382,13 @@
         <v>109729</v>
       </c>
       <c r="B627" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="C627" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D627" t="s">
         <v>1158</v>
-      </c>
-      <c r="D627" t="s">
-        <v>1159</v>
       </c>
       <c r="E627">
         <v>99.99</v>
@@ -14269,13 +14399,13 @@
         <v>295198</v>
       </c>
       <c r="B628" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C628" t="s">
         <v>1160</v>
       </c>
-      <c r="C628" t="s">
+      <c r="D628" t="s">
         <v>1161</v>
-      </c>
-      <c r="D628" t="s">
-        <v>1162</v>
       </c>
     </row>
     <row r="629" spans="1:5" x14ac:dyDescent="0.25">
@@ -14283,13 +14413,13 @@
         <v>155994</v>
       </c>
       <c r="B629" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="C629" t="s">
+        <v>1162</v>
+      </c>
+      <c r="D629" t="s">
         <v>1163</v>
-      </c>
-      <c r="D629" t="s">
-        <v>1164</v>
       </c>
     </row>
     <row r="630" spans="1:5" x14ac:dyDescent="0.25">
@@ -14297,13 +14427,13 @@
         <v>139964</v>
       </c>
       <c r="B630" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="C630" t="s">
+        <v>1164</v>
+      </c>
+      <c r="D630" t="s">
         <v>1165</v>
-      </c>
-      <c r="D630" t="s">
-        <v>1166</v>
       </c>
     </row>
     <row r="631" spans="1:5" x14ac:dyDescent="0.25">
@@ -14311,13 +14441,13 @@
         <v>105842</v>
       </c>
       <c r="B631" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C631" t="s">
         <v>1167</v>
       </c>
-      <c r="C631" t="s">
+      <c r="D631" t="s">
         <v>1168</v>
-      </c>
-      <c r="D631" t="s">
-        <v>1169</v>
       </c>
     </row>
     <row r="632" spans="1:5" x14ac:dyDescent="0.25">
@@ -14325,13 +14455,13 @@
         <v>119923</v>
       </c>
       <c r="B632" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="C632" t="s">
+        <v>1169</v>
+      </c>
+      <c r="D632" t="s">
         <v>1170</v>
-      </c>
-      <c r="D632" t="s">
-        <v>1171</v>
       </c>
     </row>
     <row r="633" spans="1:5" x14ac:dyDescent="0.25">
@@ -14339,13 +14469,13 @@
         <v>105838</v>
       </c>
       <c r="B633" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="C633" t="s">
+        <v>1171</v>
+      </c>
+      <c r="D633" t="s">
         <v>1172</v>
-      </c>
-      <c r="D633" t="s">
-        <v>1173</v>
       </c>
     </row>
     <row r="634" spans="1:5" x14ac:dyDescent="0.25">
@@ -14353,13 +14483,13 @@
         <v>104602</v>
       </c>
       <c r="B634" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="C634" t="s">
+        <v>1173</v>
+      </c>
+      <c r="D634" t="s">
         <v>1174</v>
-      </c>
-      <c r="D634" t="s">
-        <v>1175</v>
       </c>
       <c r="E634">
         <v>15.99</v>
@@ -14370,13 +14500,13 @@
         <v>105840</v>
       </c>
       <c r="B635" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="C635" t="s">
+        <v>1175</v>
+      </c>
+      <c r="D635" t="s">
         <v>1176</v>
-      </c>
-      <c r="D635" t="s">
-        <v>1177</v>
       </c>
     </row>
     <row r="636" spans="1:5" x14ac:dyDescent="0.25">
@@ -14384,13 +14514,13 @@
         <v>108785</v>
       </c>
       <c r="B636" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="C636" t="s">
+        <v>1177</v>
+      </c>
+      <c r="D636" t="s">
         <v>1178</v>
-      </c>
-      <c r="D636" t="s">
-        <v>1179</v>
       </c>
       <c r="E636">
         <v>18.989999999999998</v>
@@ -14401,13 +14531,13 @@
         <v>306504</v>
       </c>
       <c r="B637" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="C637" t="s">
+        <v>1179</v>
+      </c>
+      <c r="D637" t="s">
         <v>1180</v>
-      </c>
-      <c r="D637" t="s">
-        <v>1181</v>
       </c>
     </row>
     <row r="638" spans="1:5" x14ac:dyDescent="0.25">
@@ -14415,13 +14545,13 @@
         <v>299338</v>
       </c>
       <c r="B638" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="C638" t="s">
+        <v>1181</v>
+      </c>
+      <c r="D638" t="s">
         <v>1182</v>
-      </c>
-      <c r="D638" t="s">
-        <v>1183</v>
       </c>
       <c r="E638">
         <v>18.989999999999998</v>
@@ -14432,13 +14562,13 @@
         <v>109597</v>
       </c>
       <c r="B639" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="C639" t="s">
+        <v>1183</v>
+      </c>
+      <c r="D639" t="s">
         <v>1184</v>
-      </c>
-      <c r="D639" t="s">
-        <v>1185</v>
       </c>
     </row>
     <row r="640" spans="1:5" x14ac:dyDescent="0.25">
@@ -14446,13 +14576,13 @@
         <v>108786</v>
       </c>
       <c r="B640" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="C640" t="s">
+        <v>1185</v>
+      </c>
+      <c r="D640" t="s">
         <v>1186</v>
-      </c>
-      <c r="D640" t="s">
-        <v>1187</v>
       </c>
     </row>
     <row r="641" spans="1:5" x14ac:dyDescent="0.25">
@@ -14460,13 +14590,13 @@
         <v>291440</v>
       </c>
       <c r="B641" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="C641" t="s">
+        <v>1187</v>
+      </c>
+      <c r="D641" t="s">
         <v>1188</v>
-      </c>
-      <c r="D641" t="s">
-        <v>1189</v>
       </c>
       <c r="E641">
         <v>24.99</v>
@@ -14477,13 +14607,13 @@
         <v>119927</v>
       </c>
       <c r="B642" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="C642" t="s">
+        <v>1189</v>
+      </c>
+      <c r="D642" t="s">
         <v>1190</v>
-      </c>
-      <c r="D642" t="s">
-        <v>1191</v>
       </c>
       <c r="E642">
         <v>10.99</v>
@@ -14494,13 +14624,13 @@
         <v>225767</v>
       </c>
       <c r="B643" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="C643" t="s">
+        <v>1191</v>
+      </c>
+      <c r="D643" t="s">
         <v>1192</v>
-      </c>
-      <c r="D643" t="s">
-        <v>1193</v>
       </c>
     </row>
     <row r="644" spans="1:5" x14ac:dyDescent="0.25">
@@ -14508,13 +14638,13 @@
         <v>228289</v>
       </c>
       <c r="B644" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="C644" t="s">
+        <v>1193</v>
+      </c>
+      <c r="D644" t="s">
         <v>1194</v>
-      </c>
-      <c r="D644" t="s">
-        <v>1195</v>
       </c>
       <c r="E644">
         <v>10.99</v>
@@ -14525,13 +14655,13 @@
         <v>105853</v>
       </c>
       <c r="B645" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="C645" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D645" t="s">
         <v>1196</v>
-      </c>
-      <c r="D645" t="s">
-        <v>1197</v>
       </c>
     </row>
     <row r="646" spans="1:5" x14ac:dyDescent="0.25">
@@ -14539,13 +14669,13 @@
         <v>108788</v>
       </c>
       <c r="B646" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="C646" t="s">
+        <v>1197</v>
+      </c>
+      <c r="D646" t="s">
         <v>1198</v>
-      </c>
-      <c r="D646" t="s">
-        <v>1199</v>
       </c>
     </row>
     <row r="647" spans="1:5" x14ac:dyDescent="0.25">
@@ -14553,13 +14683,13 @@
         <v>185934</v>
       </c>
       <c r="B647" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="C647" t="s">
+        <v>1199</v>
+      </c>
+      <c r="D647" t="s">
         <v>1200</v>
-      </c>
-      <c r="D647" t="s">
-        <v>1201</v>
       </c>
     </row>
     <row r="648" spans="1:5" x14ac:dyDescent="0.25">
@@ -14567,13 +14697,13 @@
         <v>108774</v>
       </c>
       <c r="B648" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="C648" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D648" t="s">
         <v>1202</v>
-      </c>
-      <c r="D648" t="s">
-        <v>1203</v>
       </c>
     </row>
     <row r="649" spans="1:5" x14ac:dyDescent="0.25">
@@ -14581,13 +14711,13 @@
         <v>108773</v>
       </c>
       <c r="B649" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="C649" t="s">
+        <v>1203</v>
+      </c>
+      <c r="D649" t="s">
         <v>1204</v>
-      </c>
-      <c r="D649" t="s">
-        <v>1205</v>
       </c>
     </row>
     <row r="650" spans="1:5" x14ac:dyDescent="0.25">
@@ -14595,13 +14725,13 @@
         <v>261357</v>
       </c>
       <c r="B650" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="C650" t="s">
+        <v>1205</v>
+      </c>
+      <c r="D650" t="s">
         <v>1206</v>
-      </c>
-      <c r="D650" t="s">
-        <v>1207</v>
       </c>
       <c r="E650">
         <v>18.989999999999998</v>
@@ -14612,13 +14742,13 @@
         <v>108771</v>
       </c>
       <c r="B651" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="C651" t="s">
+        <v>1207</v>
+      </c>
+      <c r="D651" t="s">
         <v>1208</v>
-      </c>
-      <c r="D651" t="s">
-        <v>1209</v>
       </c>
       <c r="E651">
         <v>17.989999999999998</v>
@@ -14629,13 +14759,13 @@
         <v>157014</v>
       </c>
       <c r="B652" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C652" t="s">
         <v>1210</v>
       </c>
-      <c r="C652" t="s">
+      <c r="D652" t="s">
         <v>1211</v>
-      </c>
-      <c r="D652" t="s">
-        <v>1212</v>
       </c>
       <c r="E652">
         <v>13.99</v>
@@ -14646,13 +14776,13 @@
         <v>105470</v>
       </c>
       <c r="B653" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="C653" t="s">
+        <v>1212</v>
+      </c>
+      <c r="D653" t="s">
         <v>1213</v>
-      </c>
-      <c r="D653" t="s">
-        <v>1214</v>
       </c>
     </row>
     <row r="654" spans="1:5" x14ac:dyDescent="0.25">
@@ -14660,13 +14790,13 @@
         <v>105450</v>
       </c>
       <c r="B654" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="C654" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D654" t="s">
         <v>1215</v>
-      </c>
-      <c r="D654" t="s">
-        <v>1216</v>
       </c>
       <c r="E654">
         <v>37.99</v>
@@ -14677,13 +14807,13 @@
         <v>158997</v>
       </c>
       <c r="B655" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="C655" t="s">
+        <v>1216</v>
+      </c>
+      <c r="D655" t="s">
         <v>1217</v>
-      </c>
-      <c r="D655" t="s">
-        <v>1218</v>
       </c>
       <c r="E655">
         <v>14.99</v>
@@ -14694,13 +14824,13 @@
         <v>105460</v>
       </c>
       <c r="B656" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="C656" t="s">
+        <v>1218</v>
+      </c>
+      <c r="D656" t="s">
         <v>1219</v>
-      </c>
-      <c r="D656" t="s">
-        <v>1220</v>
       </c>
       <c r="E656">
         <v>19.989999999999998</v>
@@ -14711,13 +14841,13 @@
         <v>105459</v>
       </c>
       <c r="B657" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="C657" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D657" t="s">
         <v>1221</v>
-      </c>
-      <c r="D657" t="s">
-        <v>1222</v>
       </c>
       <c r="E657">
         <v>20.99</v>
@@ -14728,13 +14858,13 @@
         <v>105461</v>
       </c>
       <c r="B658" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="C658" t="s">
+        <v>1222</v>
+      </c>
+      <c r="D658" t="s">
         <v>1223</v>
-      </c>
-      <c r="D658" t="s">
-        <v>1224</v>
       </c>
     </row>
     <row r="659" spans="1:5" x14ac:dyDescent="0.25">
@@ -14742,13 +14872,13 @@
         <v>152232</v>
       </c>
       <c r="B659" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="C659" t="s">
+        <v>1224</v>
+      </c>
+      <c r="D659" t="s">
         <v>1225</v>
-      </c>
-      <c r="D659" t="s">
-        <v>1226</v>
       </c>
     </row>
     <row r="660" spans="1:5" x14ac:dyDescent="0.25">
@@ -14756,13 +14886,13 @@
         <v>239334</v>
       </c>
       <c r="B660" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="C660" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D660" t="s">
         <v>1227</v>
-      </c>
-      <c r="D660" t="s">
-        <v>1228</v>
       </c>
       <c r="E660">
         <v>24.99</v>
@@ -14773,13 +14903,13 @@
         <v>105456</v>
       </c>
       <c r="B661" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="C661" t="s">
+        <v>1228</v>
+      </c>
+      <c r="D661" t="s">
         <v>1229</v>
-      </c>
-      <c r="D661" t="s">
-        <v>1230</v>
       </c>
       <c r="E661">
         <v>26.99</v>
@@ -14790,13 +14920,13 @@
         <v>105468</v>
       </c>
       <c r="B662" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="C662" t="s">
+        <v>1230</v>
+      </c>
+      <c r="D662" t="s">
         <v>1231</v>
-      </c>
-      <c r="D662" t="s">
-        <v>1232</v>
       </c>
       <c r="E662">
         <v>15.99</v>
@@ -14807,13 +14937,13 @@
         <v>105458</v>
       </c>
       <c r="B663" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="C663" t="s">
+        <v>1232</v>
+      </c>
+      <c r="D663" t="s">
         <v>1233</v>
-      </c>
-      <c r="D663" t="s">
-        <v>1234</v>
       </c>
     </row>
     <row r="664" spans="1:5" x14ac:dyDescent="0.25">
@@ -14821,13 +14951,13 @@
         <v>105451</v>
       </c>
       <c r="B664" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="C664" t="s">
+        <v>1234</v>
+      </c>
+      <c r="D664" t="s">
         <v>1235</v>
-      </c>
-      <c r="D664" t="s">
-        <v>1236</v>
       </c>
       <c r="E664">
         <v>36.99</v>
@@ -14838,13 +14968,13 @@
         <v>105463</v>
       </c>
       <c r="B665" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="C665" t="s">
+        <v>1236</v>
+      </c>
+      <c r="D665" t="s">
         <v>1237</v>
-      </c>
-      <c r="D665" t="s">
-        <v>1238</v>
       </c>
       <c r="E665">
         <v>11.99</v>
@@ -14855,13 +14985,13 @@
         <v>105471</v>
       </c>
       <c r="B666" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="C666" t="s">
+        <v>1238</v>
+      </c>
+      <c r="D666" t="s">
         <v>1239</v>
-      </c>
-      <c r="D666" t="s">
-        <v>1240</v>
       </c>
     </row>
     <row r="667" spans="1:5" x14ac:dyDescent="0.25">
@@ -14869,13 +14999,13 @@
         <v>105449</v>
       </c>
       <c r="B667" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="C667" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D667" t="s">
         <v>1241</v>
-      </c>
-      <c r="D667" t="s">
-        <v>1242</v>
       </c>
       <c r="E667">
         <v>31.99</v>
@@ -14886,13 +15016,13 @@
         <v>105435</v>
       </c>
       <c r="B668" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="C668" t="s">
+        <v>1242</v>
+      </c>
+      <c r="D668" t="s">
         <v>1243</v>
-      </c>
-      <c r="D668" t="s">
-        <v>1244</v>
       </c>
       <c r="E668">
         <v>36.99</v>
@@ -14903,13 +15033,13 @@
         <v>105487</v>
       </c>
       <c r="B669" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="C669" t="s">
+        <v>1244</v>
+      </c>
+      <c r="D669" t="s">
         <v>1245</v>
-      </c>
-      <c r="D669" t="s">
-        <v>1246</v>
       </c>
       <c r="E669">
         <v>37.99</v>
@@ -14920,13 +15050,13 @@
         <v>106065</v>
       </c>
       <c r="B670" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="C670" t="s">
+        <v>1246</v>
+      </c>
+      <c r="D670" t="s">
         <v>1247</v>
-      </c>
-      <c r="D670" t="s">
-        <v>1248</v>
       </c>
       <c r="E670">
         <v>12.99</v>
@@ -14937,13 +15067,13 @@
         <v>105453</v>
       </c>
       <c r="B671" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="C671" t="s">
+        <v>1248</v>
+      </c>
+      <c r="D671" t="s">
         <v>1249</v>
-      </c>
-      <c r="D671" t="s">
-        <v>1250</v>
       </c>
     </row>
     <row r="672" spans="1:5" x14ac:dyDescent="0.25">
@@ -14951,13 +15081,13 @@
         <v>105474</v>
       </c>
       <c r="B672" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="C672" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D672" t="s">
         <v>1251</v>
-      </c>
-      <c r="D672" t="s">
-        <v>1252</v>
       </c>
     </row>
     <row r="673" spans="1:5" x14ac:dyDescent="0.25">
@@ -14965,13 +15095,13 @@
         <v>105467</v>
       </c>
       <c r="B673" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="C673" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D673" t="s">
         <v>1253</v>
-      </c>
-      <c r="D673" t="s">
-        <v>1254</v>
       </c>
       <c r="E673">
         <v>11.99</v>
@@ -14982,13 +15112,13 @@
         <v>107260</v>
       </c>
       <c r="B674" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="C674" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D674" t="s">
         <v>1255</v>
-      </c>
-      <c r="D674" t="s">
-        <v>1256</v>
       </c>
     </row>
     <row r="675" spans="1:5" x14ac:dyDescent="0.25">
@@ -14996,13 +15126,13 @@
         <v>115278</v>
       </c>
       <c r="B675" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="C675" t="s">
+        <v>1256</v>
+      </c>
+      <c r="D675" t="s">
         <v>1257</v>
-      </c>
-      <c r="D675" t="s">
-        <v>1258</v>
       </c>
       <c r="E675">
         <v>26.99</v>
@@ -15013,13 +15143,13 @@
         <v>231292</v>
       </c>
       <c r="B676" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="C676" t="s">
+        <v>1258</v>
+      </c>
+      <c r="D676" t="s">
         <v>1259</v>
-      </c>
-      <c r="D676" t="s">
-        <v>1260</v>
       </c>
     </row>
     <row r="677" spans="1:5" x14ac:dyDescent="0.25">
@@ -15027,13 +15157,13 @@
         <v>173342</v>
       </c>
       <c r="B677" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="C677" t="s">
+        <v>1260</v>
+      </c>
+      <c r="D677" t="s">
         <v>1261</v>
-      </c>
-      <c r="D677" t="s">
-        <v>1262</v>
       </c>
     </row>
     <row r="678" spans="1:5" x14ac:dyDescent="0.25">
@@ -15041,13 +15171,13 @@
         <v>105475</v>
       </c>
       <c r="B678" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="C678" t="s">
+        <v>1262</v>
+      </c>
+      <c r="D678" t="s">
         <v>1263</v>
-      </c>
-      <c r="D678" t="s">
-        <v>1264</v>
       </c>
     </row>
     <row r="679" spans="1:5" x14ac:dyDescent="0.25">
@@ -15055,13 +15185,13 @@
         <v>105469</v>
       </c>
       <c r="B679" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="C679" t="s">
+        <v>1264</v>
+      </c>
+      <c r="D679" t="s">
         <v>1265</v>
-      </c>
-      <c r="D679" t="s">
-        <v>1266</v>
       </c>
     </row>
     <row r="680" spans="1:5" x14ac:dyDescent="0.25">
@@ -15069,13 +15199,13 @@
         <v>105452</v>
       </c>
       <c r="B680" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="C680" t="s">
+        <v>1266</v>
+      </c>
+      <c r="D680" t="s">
         <v>1267</v>
-      </c>
-      <c r="D680" t="s">
-        <v>1268</v>
       </c>
       <c r="E680">
         <v>34.99</v>
@@ -15086,13 +15216,13 @@
         <v>261519</v>
       </c>
       <c r="B681" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="C681" t="s">
+        <v>1268</v>
+      </c>
+      <c r="D681" t="s">
         <v>1269</v>
-      </c>
-      <c r="D681" t="s">
-        <v>1270</v>
       </c>
     </row>
     <row r="682" spans="1:5" x14ac:dyDescent="0.25">
@@ -15100,13 +15230,13 @@
         <v>106249</v>
       </c>
       <c r="B682" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="C682" t="s">
+        <v>1270</v>
+      </c>
+      <c r="D682" t="s">
         <v>1271</v>
-      </c>
-      <c r="D682" t="s">
-        <v>1272</v>
       </c>
     </row>
     <row r="683" spans="1:5" x14ac:dyDescent="0.25">
@@ -15114,13 +15244,13 @@
         <v>286549</v>
       </c>
       <c r="B683" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C683" t="s">
         <v>1273</v>
       </c>
-      <c r="C683" t="s">
+      <c r="D683" t="s">
         <v>1274</v>
-      </c>
-      <c r="D683" t="s">
-        <v>1275</v>
       </c>
     </row>
     <row r="684" spans="1:5" x14ac:dyDescent="0.25">
@@ -15128,13 +15258,13 @@
         <v>305039</v>
       </c>
       <c r="B684" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="C684" t="s">
+        <v>1275</v>
+      </c>
+      <c r="D684" t="s">
         <v>1276</v>
-      </c>
-      <c r="D684" t="s">
-        <v>1277</v>
       </c>
     </row>
     <row r="685" spans="1:5" x14ac:dyDescent="0.25">
@@ -15142,13 +15272,13 @@
         <v>189031</v>
       </c>
       <c r="B685" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="C685" t="s">
+        <v>1277</v>
+      </c>
+      <c r="D685" t="s">
         <v>1278</v>
-      </c>
-      <c r="D685" t="s">
-        <v>1279</v>
       </c>
     </row>
     <row r="686" spans="1:5" x14ac:dyDescent="0.25">
@@ -15156,13 +15286,13 @@
         <v>123758</v>
       </c>
       <c r="B686" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="C686" t="s">
+        <v>1279</v>
+      </c>
+      <c r="D686" t="s">
         <v>1280</v>
-      </c>
-      <c r="D686" t="s">
-        <v>1281</v>
       </c>
       <c r="E686">
         <v>22.99</v>
@@ -15173,13 +15303,13 @@
         <v>117117</v>
       </c>
       <c r="B687" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="C687" t="s">
+        <v>1281</v>
+      </c>
+      <c r="D687" t="s">
         <v>1282</v>
-      </c>
-      <c r="D687" t="s">
-        <v>1283</v>
       </c>
     </row>
     <row r="688" spans="1:5" x14ac:dyDescent="0.25">
@@ -15187,13 +15317,13 @@
         <v>289127</v>
       </c>
       <c r="B688" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="C688" t="s">
+        <v>1283</v>
+      </c>
+      <c r="D688" t="s">
         <v>1284</v>
-      </c>
-      <c r="D688" t="s">
-        <v>1285</v>
       </c>
     </row>
     <row r="689" spans="1:5" x14ac:dyDescent="0.25">
@@ -15201,13 +15331,13 @@
         <v>129515</v>
       </c>
       <c r="B689" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="C689" t="s">
+        <v>1285</v>
+      </c>
+      <c r="D689" t="s">
         <v>1286</v>
-      </c>
-      <c r="D689" t="s">
-        <v>1287</v>
       </c>
     </row>
     <row r="690" spans="1:5" x14ac:dyDescent="0.25">
@@ -15215,13 +15345,13 @@
         <v>228422</v>
       </c>
       <c r="B690" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="C690" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D690" t="s">
         <v>1288</v>
-      </c>
-      <c r="D690" t="s">
-        <v>1289</v>
       </c>
     </row>
     <row r="691" spans="1:5" x14ac:dyDescent="0.25">
@@ -15229,13 +15359,13 @@
         <v>105770</v>
       </c>
       <c r="B691" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="C691" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D691" t="s">
         <v>1290</v>
-      </c>
-      <c r="D691" t="s">
-        <v>1291</v>
       </c>
     </row>
     <row r="692" spans="1:5" x14ac:dyDescent="0.25">
@@ -15243,13 +15373,13 @@
         <v>105765</v>
       </c>
       <c r="B692" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="C692" t="s">
+        <v>1291</v>
+      </c>
+      <c r="D692" t="s">
         <v>1292</v>
-      </c>
-      <c r="D692" t="s">
-        <v>1293</v>
       </c>
     </row>
     <row r="693" spans="1:5" x14ac:dyDescent="0.25">
@@ -15257,13 +15387,13 @@
         <v>116251</v>
       </c>
       <c r="B693" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="C693" t="s">
+        <v>1293</v>
+      </c>
+      <c r="D693" t="s">
         <v>1294</v>
-      </c>
-      <c r="D693" t="s">
-        <v>1295</v>
       </c>
       <c r="E693">
         <v>10.99</v>
@@ -15274,13 +15404,13 @@
         <v>173405</v>
       </c>
       <c r="B694" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="C694" t="s">
+        <v>1295</v>
+      </c>
+      <c r="D694" t="s">
         <v>1296</v>
-      </c>
-      <c r="D694" t="s">
-        <v>1297</v>
       </c>
     </row>
     <row r="695" spans="1:5" x14ac:dyDescent="0.25">
@@ -15288,13 +15418,13 @@
         <v>111741</v>
       </c>
       <c r="B695" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="C695" t="s">
+        <v>1297</v>
+      </c>
+      <c r="D695" t="s">
         <v>1298</v>
-      </c>
-      <c r="D695" t="s">
-        <v>1299</v>
       </c>
     </row>
     <row r="696" spans="1:5" x14ac:dyDescent="0.25">
@@ -15302,13 +15432,13 @@
         <v>286228</v>
       </c>
       <c r="B696" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="C696" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="D696" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="697" spans="1:5" x14ac:dyDescent="0.25">
@@ -15316,13 +15446,13 @@
         <v>138538</v>
       </c>
       <c r="B697" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C697" t="s">
         <v>1301</v>
       </c>
-      <c r="C697" t="s">
-        <v>1302</v>
-      </c>
       <c r="D697" t="s">
-        <v>1303</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="698" spans="1:5" x14ac:dyDescent="0.25">
@@ -15330,13 +15460,13 @@
         <v>127328</v>
       </c>
       <c r="B698" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="C698" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
       <c r="D698" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="699" spans="1:5" x14ac:dyDescent="0.25">
@@ -15344,13 +15474,13 @@
         <v>284246</v>
       </c>
       <c r="B699" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="C699" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="D699" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="700" spans="1:5" x14ac:dyDescent="0.25">
@@ -15358,13 +15488,13 @@
         <v>323487</v>
       </c>
       <c r="B700" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C700" t="s">
+        <v>1307</v>
+      </c>
+      <c r="D700" t="s">
         <v>1308</v>
-      </c>
-      <c r="C700" t="s">
-        <v>1309</v>
-      </c>
-      <c r="D700" t="s">
-        <v>1310</v>
       </c>
       <c r="E700">
         <v>29.99</v>
@@ -15375,13 +15505,13 @@
         <v>303488</v>
       </c>
       <c r="B701" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="C701" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="D701" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="E701">
         <v>115.99</v>
@@ -15392,13 +15522,13 @@
         <v>323489</v>
       </c>
       <c r="B702" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="C702" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="D702" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="E702">
         <v>25.99</v>
@@ -15409,13 +15539,13 @@
         <v>311307</v>
       </c>
       <c r="B703" t="s">
+        <v>1313</v>
+      </c>
+      <c r="C703" t="s">
+        <v>1314</v>
+      </c>
+      <c r="D703" t="s">
         <v>1315</v>
-      </c>
-      <c r="C703" t="s">
-        <v>1316</v>
-      </c>
-      <c r="D703" t="s">
-        <v>1317</v>
       </c>
       <c r="E703">
         <v>15.99</v>
@@ -15426,13 +15556,13 @@
         <v>262170</v>
       </c>
       <c r="B704" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="C704" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
       <c r="D704" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
       <c r="E704">
         <v>29.99</v>
@@ -15443,13 +15573,13 @@
         <v>254014</v>
       </c>
       <c r="B705" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="C705" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="D705" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="E705">
         <v>35.99</v>
@@ -15460,13 +15590,13 @@
         <v>141831</v>
       </c>
       <c r="B706" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="C706" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="D706" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
       <c r="E706">
         <v>44.99</v>
@@ -15477,13 +15607,13 @@
         <v>323501</v>
       </c>
       <c r="B707" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="C707" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="D707" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="E707">
         <v>48.99</v>
@@ -15494,13 +15624,13 @@
         <v>315711</v>
       </c>
       <c r="B708" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="C708" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
       <c r="D708" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="E708">
         <v>32.99</v>
@@ -15511,13 +15641,13 @@
         <v>203263</v>
       </c>
       <c r="B709" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="C709" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="D709" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="E709">
         <v>49.99</v>
@@ -15528,13 +15658,13 @@
         <v>284245</v>
       </c>
       <c r="B710" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="C710" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="D710" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="E710">
         <v>10.99</v>
@@ -15545,13 +15675,13 @@
         <v>298215</v>
       </c>
       <c r="B711" t="s">
+        <v>1329</v>
+      </c>
+      <c r="C711" t="s">
+        <v>1330</v>
+      </c>
+      <c r="D711" t="s">
         <v>1331</v>
-      </c>
-      <c r="C711" t="s">
-        <v>1332</v>
-      </c>
-      <c r="D711" t="s">
-        <v>1333</v>
       </c>
     </row>
     <row r="712" spans="1:5" x14ac:dyDescent="0.25">
@@ -15559,13 +15689,13 @@
         <v>106053</v>
       </c>
       <c r="B712" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="C712" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="D712" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="713" spans="1:5" x14ac:dyDescent="0.25">
@@ -15573,13 +15703,13 @@
         <v>105062</v>
       </c>
       <c r="B713" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="C713" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
       <c r="D713" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="714" spans="1:5" x14ac:dyDescent="0.25">
@@ -15587,13 +15717,13 @@
         <v>320822</v>
       </c>
       <c r="B714" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="C714" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
       <c r="D714" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
       <c r="E714">
         <v>21.99</v>
@@ -15604,13 +15734,13 @@
         <v>105433</v>
       </c>
       <c r="B715" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="C715" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
       <c r="D715" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="E715">
         <v>19.989999999999998</v>
@@ -15621,13 +15751,13 @@
         <v>106008</v>
       </c>
       <c r="B716" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="C716" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
       <c r="D716" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
       <c r="E716">
         <v>19.989999999999998</v>
@@ -15638,13 +15768,13 @@
         <v>106054</v>
       </c>
       <c r="B717" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="C717" t="s">
-        <v>1344</v>
+        <v>1342</v>
       </c>
       <c r="D717" t="s">
-        <v>1345</v>
+        <v>1343</v>
       </c>
       <c r="E717">
         <v>19.989999999999998</v>
@@ -15655,13 +15785,13 @@
         <v>258810</v>
       </c>
       <c r="B718" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="C718" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="D718" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="719" spans="1:5" x14ac:dyDescent="0.25">
@@ -15669,13 +15799,13 @@
         <v>106050</v>
       </c>
       <c r="B719" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="C719" t="s">
-        <v>1348</v>
+        <v>1346</v>
       </c>
       <c r="D719" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
       <c r="E719">
         <v>9.99</v>
@@ -15686,13 +15816,13 @@
         <v>106052</v>
       </c>
       <c r="B720" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="C720" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
       <c r="D720" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="E720">
         <v>12.99</v>
@@ -15703,13 +15833,13 @@
         <v>106034</v>
       </c>
       <c r="B721" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="C721" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="D721" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="722" spans="1:5" x14ac:dyDescent="0.25">
@@ -15717,13 +15847,13 @@
         <v>106032</v>
       </c>
       <c r="B722" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="C722" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
       <c r="D722" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="E722">
         <v>18.989999999999998</v>
@@ -15734,13 +15864,13 @@
         <v>110086</v>
       </c>
       <c r="B723" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="C723" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="D723" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="724" spans="1:5" x14ac:dyDescent="0.25">
@@ -15748,13 +15878,13 @@
         <v>114556</v>
       </c>
       <c r="B724" t="s">
+        <v>1354</v>
+      </c>
+      <c r="C724" t="s">
         <v>1356</v>
       </c>
-      <c r="C724" t="s">
-        <v>1358</v>
-      </c>
       <c r="D724" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="725" spans="1:5" x14ac:dyDescent="0.25">
@@ -15762,13 +15892,13 @@
         <v>113301</v>
       </c>
       <c r="B725" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="C725" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="D725" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="726" spans="1:5" x14ac:dyDescent="0.25">
@@ -15776,13 +15906,13 @@
         <v>171272</v>
       </c>
       <c r="B726" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="C726" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="D726" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="727" spans="1:5" x14ac:dyDescent="0.25">
@@ -15790,13 +15920,13 @@
         <v>302448</v>
       </c>
       <c r="B727" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="C727" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="D727" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="728" spans="1:5" x14ac:dyDescent="0.25">
@@ -15804,13 +15934,13 @@
         <v>121635</v>
       </c>
       <c r="B728" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="C728" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D728" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="729" spans="1:5" x14ac:dyDescent="0.25">
@@ -15818,13 +15948,13 @@
         <v>229361</v>
       </c>
       <c r="B729" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="C729" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
       <c r="D729" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="730" spans="1:5" x14ac:dyDescent="0.25">
@@ -15832,13 +15962,13 @@
         <v>311249</v>
       </c>
       <c r="B730" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="C730" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="D730" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="731" spans="1:5" x14ac:dyDescent="0.25">
@@ -15846,13 +15976,13 @@
         <v>104937</v>
       </c>
       <c r="B731" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="C731" t="s">
-        <v>1373</v>
+        <v>1371</v>
       </c>
       <c r="D731" t="s">
-        <v>1373</v>
+        <v>1371</v>
       </c>
       <c r="E731">
         <v>31.99</v>
@@ -15863,13 +15993,13 @@
         <v>104998</v>
       </c>
       <c r="B732" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C732" t="s">
         <v>1372</v>
       </c>
-      <c r="C732" t="s">
-        <v>1374</v>
-      </c>
       <c r="D732" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="E732">
         <v>7.99</v>
@@ -15880,13 +16010,13 @@
         <v>105023</v>
       </c>
       <c r="B733" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="C733" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="D733" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="E733">
         <v>5.99</v>
@@ -15897,13 +16027,13 @@
         <v>105010</v>
       </c>
       <c r="B734" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="C734" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="D734" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="E734">
         <v>4.8899999999999997</v>
@@ -15914,13 +16044,13 @@
         <v>105001</v>
       </c>
       <c r="B735" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="C735" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="D735" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="E735">
         <v>4.99</v>
@@ -15931,13 +16061,13 @@
         <v>104919</v>
       </c>
       <c r="B736" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="C736" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="D736" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="E736">
         <v>4.59</v>
@@ -15948,13 +16078,13 @@
         <v>104862</v>
       </c>
       <c r="B737" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="C737" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="D737" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="E737">
         <v>4.99</v>
@@ -15965,13 +16095,13 @@
         <v>104931</v>
       </c>
       <c r="B738" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="C738" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="D738" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="E738">
         <v>9.99</v>
@@ -15982,13 +16112,13 @@
         <v>104855</v>
       </c>
       <c r="B739" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="C739" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="D739" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="740" spans="1:5" x14ac:dyDescent="0.25">
@@ -15996,13 +16126,13 @@
         <v>104944</v>
       </c>
       <c r="B740" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="C740" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="D740" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="E740">
         <v>11.99</v>
@@ -16013,13 +16143,13 @@
         <v>104928</v>
       </c>
       <c r="B741" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="C741" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="D741" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="E741">
         <v>6.99</v>
@@ -16030,13 +16160,13 @@
         <v>104962</v>
       </c>
       <c r="B742" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="C742" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="D742" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="743" spans="1:5" x14ac:dyDescent="0.25">
@@ -16044,13 +16174,13 @@
         <v>108982</v>
       </c>
       <c r="B743" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="C743" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="D743" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="E743">
         <v>12.69</v>
@@ -16061,13 +16191,13 @@
         <v>104947</v>
       </c>
       <c r="B744" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="C744" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
       <c r="D744" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
       <c r="E744">
         <v>2.99</v>
@@ -16078,13 +16208,13 @@
         <v>104996</v>
       </c>
       <c r="B745" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="C745" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="D745" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="E745">
         <v>7.19</v>
@@ -16095,13 +16225,13 @@
         <v>239921</v>
       </c>
       <c r="B746" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="C746" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="D746" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
       <c r="E746">
         <v>23.7</v>
@@ -16112,13 +16242,13 @@
         <v>104992</v>
       </c>
       <c r="B747" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="C747" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="D747" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="E747">
         <v>3.99</v>
@@ -16129,13 +16259,13 @@
         <v>104961</v>
       </c>
       <c r="B748" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="C748" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="D748" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="E748">
         <v>7.99</v>
@@ -16146,13 +16276,13 @@
         <v>104863</v>
       </c>
       <c r="B749" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="C749" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="D749" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="E749">
         <v>9.49</v>
@@ -16163,13 +16293,13 @@
         <v>323495</v>
       </c>
       <c r="B750" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="C750" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="D750" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="E750">
         <v>36.99</v>
@@ -16180,13 +16310,13 @@
         <v>164651</v>
       </c>
       <c r="B751" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="C751" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="D751" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="E751">
         <v>27.99</v>
@@ -16197,13 +16327,13 @@
         <v>320788</v>
       </c>
       <c r="B752" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="C752" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="D752" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="E752">
         <v>7.69</v>
@@ -16214,13 +16344,13 @@
         <v>260606</v>
       </c>
       <c r="B753" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="C753" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="D753" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="E753">
         <v>4.3899999999999997</v>
@@ -16231,13 +16361,13 @@
         <v>146785</v>
       </c>
       <c r="B754" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="C754" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="D754" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="E754">
         <v>28.99</v>
@@ -16248,13 +16378,13 @@
         <v>167154</v>
       </c>
       <c r="B755" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="C755" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="D755" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="E755">
         <v>26.99</v>
@@ -16265,13 +16395,13 @@
         <v>236674</v>
       </c>
       <c r="B756" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="C756" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="D756" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="E756">
         <v>44.99</v>
@@ -16282,13 +16412,13 @@
         <v>236672</v>
       </c>
       <c r="B757" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="C757" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="D757" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="E757">
         <v>44.99</v>
@@ -16299,13 +16429,13 @@
         <v>236671</v>
       </c>
       <c r="B758" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="C758" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="D758" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="E758">
         <v>44.99</v>
@@ -16316,13 +16446,13 @@
         <v>236673</v>
       </c>
       <c r="B759" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="C759" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="D759" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="E759">
         <v>44.99</v>
@@ -16333,13 +16463,13 @@
         <v>171895</v>
       </c>
       <c r="B760" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="C760" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="D760" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="E760">
         <v>4.59</v>
@@ -16350,13 +16480,13 @@
         <v>102036</v>
       </c>
       <c r="B761" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="C761" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="D761" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="E761">
         <v>25.99</v>
@@ -16370,10 +16500,10 @@
         <v>78</v>
       </c>
       <c r="C762" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="D762" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="E762">
         <v>8.99</v>
@@ -16387,10 +16517,10 @@
         <v>78</v>
       </c>
       <c r="C763" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="D763" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="E763">
         <v>40.99</v>
@@ -16401,13 +16531,13 @@
         <v>170464</v>
       </c>
       <c r="B764" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="C764" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
       <c r="D764" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
       <c r="E764">
         <v>2.19</v>
@@ -16421,10 +16551,10 @@
         <v>525</v>
       </c>
       <c r="C765" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="D765" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
       <c r="E765">
         <v>2.69</v>
@@ -16438,7 +16568,7 @@
         <v>525</v>
       </c>
       <c r="C766" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
       <c r="D766" t="s">
         <v>617</v>
@@ -16455,10 +16585,10 @@
         <v>78</v>
       </c>
       <c r="C767" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
       <c r="D767" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
       <c r="E767">
         <v>3.29</v>
@@ -16472,10 +16602,10 @@
         <v>78</v>
       </c>
       <c r="C768" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="D768" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="E768">
         <v>2.4900000000000002</v>
@@ -16489,10 +16619,10 @@
         <v>78</v>
       </c>
       <c r="C769" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
       <c r="D769" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
       <c r="E769">
         <v>3.19</v>
@@ -16506,10 +16636,10 @@
         <v>78</v>
       </c>
       <c r="C770" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="D770" t="s">
-        <v>1435</v>
+        <v>1433</v>
       </c>
       <c r="E770">
         <v>20.99</v>
@@ -16520,13 +16650,13 @@
         <v>105007</v>
       </c>
       <c r="B771" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="C771" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
       <c r="D771" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
       <c r="E771">
         <v>4.49</v>
@@ -16537,13 +16667,13 @@
         <v>104903</v>
       </c>
       <c r="B772" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="C772" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
       <c r="D772" t="s">
-        <v>1439</v>
+        <v>1437</v>
       </c>
       <c r="E772">
         <v>3.99</v>
@@ -16554,13 +16684,13 @@
         <v>104883</v>
       </c>
       <c r="B773" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="C773" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
       <c r="D773" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="E773">
         <v>6.99</v>
@@ -16571,13 +16701,13 @@
         <v>113290</v>
       </c>
       <c r="B774" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="C774" t="s">
-        <v>1442</v>
+        <v>1440</v>
       </c>
       <c r="D774" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
       <c r="E774">
         <v>14.99</v>
@@ -16588,16 +16718,424 @@
         <v>104890</v>
       </c>
       <c r="B775" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="C775" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
       <c r="D775" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="E775">
         <v>21.99</v>
+      </c>
+    </row>
+    <row r="776" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A776">
+        <v>130107</v>
+      </c>
+      <c r="B776" t="s">
+        <v>78</v>
+      </c>
+      <c r="C776" t="s">
+        <v>1444</v>
+      </c>
+      <c r="D776" t="s">
+        <v>1445</v>
+      </c>
+      <c r="E776">
+        <v>52.99</v>
+      </c>
+    </row>
+    <row r="777" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A777">
+        <v>305475</v>
+      </c>
+      <c r="B777" t="s">
+        <v>78</v>
+      </c>
+      <c r="C777" t="s">
+        <v>1446</v>
+      </c>
+      <c r="D777" t="s">
+        <v>1447</v>
+      </c>
+      <c r="E777">
+        <v>16.989999999999998</v>
+      </c>
+    </row>
+    <row r="778" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A778">
+        <v>235809</v>
+      </c>
+      <c r="B778" t="s">
+        <v>662</v>
+      </c>
+      <c r="C778" t="s">
+        <v>1448</v>
+      </c>
+      <c r="D778" t="s">
+        <v>1449</v>
+      </c>
+      <c r="E778">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="779" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A779">
+        <v>248717</v>
+      </c>
+      <c r="B779" t="s">
+        <v>525</v>
+      </c>
+      <c r="C779" t="s">
+        <v>1450</v>
+      </c>
+      <c r="D779" t="s">
+        <v>1451</v>
+      </c>
+      <c r="E779">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="780" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A780">
+        <v>110507</v>
+      </c>
+      <c r="B780" t="s">
+        <v>525</v>
+      </c>
+      <c r="C780" t="s">
+        <v>1452</v>
+      </c>
+      <c r="D780" t="s">
+        <v>1452</v>
+      </c>
+      <c r="E780">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="781" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A781">
+        <v>100275</v>
+      </c>
+      <c r="B781" t="s">
+        <v>525</v>
+      </c>
+      <c r="C781" t="s">
+        <v>1453</v>
+      </c>
+      <c r="D781" t="s">
+        <v>1454</v>
+      </c>
+      <c r="E781">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="782" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A782">
+        <v>248716</v>
+      </c>
+      <c r="B782" t="s">
+        <v>525</v>
+      </c>
+      <c r="C782" t="s">
+        <v>1455</v>
+      </c>
+      <c r="D782" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E782">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="783" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A783">
+        <v>100277</v>
+      </c>
+      <c r="B783" t="s">
+        <v>525</v>
+      </c>
+      <c r="C783" t="s">
+        <v>1457</v>
+      </c>
+      <c r="D783" t="s">
+        <v>1458</v>
+      </c>
+      <c r="E783">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="784" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A784">
+        <v>100274</v>
+      </c>
+      <c r="B784" t="s">
+        <v>525</v>
+      </c>
+      <c r="C784" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D784" t="s">
+        <v>1460</v>
+      </c>
+      <c r="E784">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="785" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A785">
+        <v>110571</v>
+      </c>
+      <c r="B785" t="s">
+        <v>525</v>
+      </c>
+      <c r="C785" t="s">
+        <v>1461</v>
+      </c>
+      <c r="D785" t="s">
+        <v>1462</v>
+      </c>
+      <c r="E785">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="786" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A786">
+        <v>106624</v>
+      </c>
+      <c r="B786" t="s">
+        <v>525</v>
+      </c>
+      <c r="C786" t="s">
+        <v>1463</v>
+      </c>
+      <c r="D786" t="s">
+        <v>1464</v>
+      </c>
+      <c r="E786">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="787" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A787">
+        <v>100281</v>
+      </c>
+      <c r="B787" t="s">
+        <v>525</v>
+      </c>
+      <c r="C787" t="s">
+        <v>1465</v>
+      </c>
+      <c r="D787" t="s">
+        <v>1466</v>
+      </c>
+      <c r="E787">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="788" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A788">
+        <v>315650</v>
+      </c>
+      <c r="B788" t="s">
+        <v>975</v>
+      </c>
+      <c r="C788" t="s">
+        <v>1467</v>
+      </c>
+      <c r="D788" t="s">
+        <v>1467</v>
+      </c>
+      <c r="E788">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="789" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A789">
+        <v>305260</v>
+      </c>
+      <c r="B789" t="s">
+        <v>975</v>
+      </c>
+      <c r="C789" t="s">
+        <v>1468</v>
+      </c>
+      <c r="D789" t="s">
+        <v>1468</v>
+      </c>
+      <c r="E789">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="790" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A790">
+        <v>324143</v>
+      </c>
+      <c r="B790" t="s">
+        <v>78</v>
+      </c>
+      <c r="C790" t="s">
+        <v>1469</v>
+      </c>
+      <c r="D790" t="s">
+        <v>1470</v>
+      </c>
+      <c r="E790">
+        <v>8.69</v>
+      </c>
+    </row>
+    <row r="791" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A791">
+        <v>219003</v>
+      </c>
+      <c r="B791" t="s">
+        <v>78</v>
+      </c>
+      <c r="C791" t="s">
+        <v>1471</v>
+      </c>
+      <c r="D791" t="s">
+        <v>1472</v>
+      </c>
+      <c r="E791">
+        <v>6.49</v>
+      </c>
+    </row>
+    <row r="792" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A792">
+        <v>260659</v>
+      </c>
+      <c r="B792" t="s">
+        <v>525</v>
+      </c>
+      <c r="C792" t="s">
+        <v>1473</v>
+      </c>
+      <c r="D792" t="s">
+        <v>1473</v>
+      </c>
+      <c r="E792">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="793" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A793">
+        <v>322795</v>
+      </c>
+      <c r="B793" t="s">
+        <v>662</v>
+      </c>
+      <c r="C793" t="s">
+        <v>1474</v>
+      </c>
+      <c r="D793" t="s">
+        <v>1475</v>
+      </c>
+      <c r="E793">
+        <v>12.99</v>
+      </c>
+    </row>
+    <row r="794" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A794">
+        <v>320166</v>
+      </c>
+      <c r="B794" t="s">
+        <v>525</v>
+      </c>
+      <c r="C794" t="s">
+        <v>1476</v>
+      </c>
+      <c r="D794" t="s">
+        <v>1477</v>
+      </c>
+      <c r="E794">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="795" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A795">
+        <v>104414</v>
+      </c>
+      <c r="B795" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C795" t="s">
+        <v>1478</v>
+      </c>
+      <c r="D795" t="s">
+        <v>1479</v>
+      </c>
+      <c r="E795">
+        <v>7.49</v>
+      </c>
+    </row>
+    <row r="796" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A796">
+        <v>263553</v>
+      </c>
+      <c r="B796" t="s">
+        <v>78</v>
+      </c>
+      <c r="C796" t="s">
+        <v>1480</v>
+      </c>
+      <c r="D796" t="s">
+        <v>1481</v>
+      </c>
+      <c r="E796">
+        <v>7.49</v>
+      </c>
+    </row>
+    <row r="797" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A797">
+        <v>292093</v>
+      </c>
+      <c r="B797" t="s">
+        <v>525</v>
+      </c>
+      <c r="C797" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D797" t="s">
+        <v>1483</v>
+      </c>
+      <c r="E797">
+        <v>10.99</v>
+      </c>
+    </row>
+    <row r="798" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A798">
+        <v>296910</v>
+      </c>
+      <c r="B798" t="s">
+        <v>525</v>
+      </c>
+      <c r="C798" t="s">
+        <v>1484</v>
+      </c>
+      <c r="D798" t="s">
+        <v>1485</v>
+      </c>
+      <c r="E798">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="799" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A799">
+        <v>114072</v>
+      </c>
+      <c r="B799" t="s">
+        <v>662</v>
+      </c>
+      <c r="C799" t="s">
+        <v>1486</v>
+      </c>
+      <c r="D799" t="s">
+        <v>1487</v>
+      </c>
+      <c r="E799">
+        <v>9.99</v>
       </c>
     </row>
   </sheetData>
